--- a/exercices/exercices_gini_afc2022.xlsx
+++ b/exercices/exercices_gini_afc2022.xlsx
@@ -1,45 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gueney\Documents\GitHub\les-mesures-de-l-conomie\exercices\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celal\Documents\GitHub\les-mesures-de-l-conomie\exercices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{989207DF-CA5C-42E1-85C4-591C7C461E8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E043B6D5-4988-4CD4-9593-01CA2A6C0DE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="2" xr2:uid="{0A857FEE-5B62-478B-B26F-1439DD0DBBE3}"/>
+    <workbookView xWindow="315" yWindow="510" windowWidth="28485" windowHeight="14970" activeTab="3" xr2:uid="{0A857FEE-5B62-478B-B26F-1439DD0DBBE3}"/>
   </bookViews>
   <sheets>
     <sheet name="source" sheetId="2" r:id="rId1"/>
     <sheet name="CH" sheetId="1" r:id="rId2"/>
-    <sheet name="GE" sheetId="3" r:id="rId3"/>
-    <sheet name="alpha coef GE" sheetId="6" r:id="rId4"/>
+    <sheet name="CH theil" sheetId="7" r:id="rId3"/>
+    <sheet name="GE" sheetId="3" r:id="rId4"/>
+    <sheet name="alpha coef GE" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="72">
   <si>
     <t>seuil inférieur du groupe</t>
   </si>
@@ -232,6 +222,33 @@
   <si>
     <t>Part du 1%: interpolation de Pareto</t>
   </si>
+  <si>
+    <t>Proportion de la population du groupe</t>
+  </si>
+  <si>
+    <t>Proportion de revenu du groupe</t>
+  </si>
+  <si>
+    <t>Indice theil du groupe</t>
+  </si>
+  <si>
+    <t>Indice de Theil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'indice de Theil mesure les écarts entre la distribution des revenus et la distribution de la population entre les groupes.
+Essentiellement, l’indice de Theil compare les structures de distribution du revenu et de la population en additionnant, pour l’ensemble des groupes, le logarithme pondéré du rapport entre la part de revenu et la part de population de chaque groupe.
+Lorsque ce rapport est égal à 1 pour un groupe donné, alors la contribution de ce groupe à l’inégalité est nulle. Lorsque tous les groupes ont une part de revenu égale à leur part dans la population, l'indice (du groupe) est nulle.
+</t>
+  </si>
+  <si>
+    <t>theil</t>
+  </si>
+  <si>
+    <t>Aire des trapèzes sous la courbe</t>
+  </si>
+  <si>
+    <t>Somme aires trapèzes</t>
+  </si>
 </sst>
 </file>
 
@@ -281,7 +298,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -318,8 +335,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCE3C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -356,13 +385,127 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -410,6 +553,29 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -425,8 +591,26 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -448,6 +632,434 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="LID4096"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'CH theil'!$K$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>theil</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'CH theil'!$J$3:$J$28</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="26"/>
+                <c:pt idx="0">
+                  <c:v>0.17295308935382017</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.21124514245499026</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.25126795809408137</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.2903156698301102</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.33461714719900937</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.38602235757574871</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.44145114800301682</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.49648251950676708</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.54822387918798166</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.59499406372415498</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.63690644275052244</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.67411523231501425</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.70737900865339587</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.73721147792532737</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.76402673105950802</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.7884214174413765</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.81043304908259162</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.87757246434952196</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.93209909089639742</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.96891942274015663</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.98876306850756168</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.99430859423111106</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.99657161053445653</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.99918390534635781</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.99976680032752152</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'CH theil'!$K$3:$K$28</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="26"/>
+                <c:pt idx="0">
+                  <c:v>-4.2088632053942511E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-5.6081521688101613E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-7.0757626964163836E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-8.460819555237914E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-9.9297393306532547E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-0.11467075089766376</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-0.12897446806858248</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-0.14052067323656281</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-0.14850495731840962</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-0.15284397652921164</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-0.15390350320953805</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-0.15212988745864936</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-0.14795235654122926</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-0.14174405137397261</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-0.13382981631130622</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-0.12441158187800709</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-0.11382131937629252</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-6.5562941053542489E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2.9681188067023218E-3</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>8.4618344218928748E-2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.16858720120654686</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.21222818257633932</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.23912618337416464</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.2952196130953868</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.32856457637534486</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.39660361967801816</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-84E7-4383-9BA4-14EDE0CCED42}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="319335279"/>
+        <c:axId val="319335759"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="319335279"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="LID4096"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="319335759"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="319335759"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="LID4096"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="319335279"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="LID4096"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="fr-FR"/>
@@ -1399,7 +2011,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="fr-FR"/>
@@ -1418,8 +2030,8 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.11813138686131387"/>
-          <c:y val="7.1111091202494155E-3"/>
+          <c:x val="0.12072964473794849"/>
+          <c:y val="1.4818321120264591E-2"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -1854,7 +2466,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="fr-FR"/>
@@ -2441,8 +3053,48 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -2469,8 +3121,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -2550,6 +3202,11 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -2560,6 +3217,11 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
@@ -2571,7 +3233,7 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="19050" cap="rnd">
+      <a:ln w="28575" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -2591,6 +3253,9 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2603,10 +3268,10 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
+    <cs:fillRef idx="1"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -2646,23 +3311,22 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -2767,8 +3431,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -2900,20 +3564,19 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -2927,17 +3590,6 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
@@ -3473,20 +4125,577 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>569116</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>2230438</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>616742</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>238124</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>574673</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>28576</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>616742</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>76199</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Graphique 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B181F903-4530-230A-8E6E-8E32EA2FB05C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>11903</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>120650</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>17460</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>90488</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3513,16 +4722,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>427037</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>84137</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>4057650</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>785812</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3550,7 +4759,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -3592,9 +4801,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office 2013 – 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3632,7 +4841,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -3738,7 +4947,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3880,7 +5089,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3889,14 +5098,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ACE9D6E-E496-4D38-B54C-DA7BD6147D63}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A2" s="19" t="s">
         <v>27</v>
       </c>
@@ -3912,41 +5121,41 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CB256E1-B0FC-48AE-8D60-3C9A253EE1A6}">
   <dimension ref="A1:Q35"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="3" max="3" width="25.36328125" customWidth="1"/>
-    <col min="5" max="5" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="29.6328125" customWidth="1"/>
-    <col min="7" max="7" width="39.36328125" customWidth="1"/>
-    <col min="8" max="8" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.6328125" customWidth="1"/>
-    <col min="10" max="10" width="20.26953125" customWidth="1"/>
-    <col min="12" max="12" width="67.36328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="27.26953125" customWidth="1"/>
+    <col min="3" max="3" width="25.33203125" customWidth="1"/>
+    <col min="5" max="5" width="11.19921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="29.59765625" customWidth="1"/>
+    <col min="7" max="7" width="39.33203125" customWidth="1"/>
+    <col min="8" max="8" width="11.19921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.59765625" customWidth="1"/>
+    <col min="10" max="10" width="20.265625" customWidth="1"/>
+    <col min="12" max="12" width="67.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="27.265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="F1" s="25" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="F1" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="26" t="s">
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="K1" s="27"/>
-      <c r="L1" s="28" t="s">
+      <c r="K1" s="40"/>
+      <c r="L1" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="29"/>
-    </row>
-    <row r="2" spans="1:17" ht="174" x14ac:dyDescent="0.35">
+      <c r="M1" s="42"/>
+      <c r="N1" s="42"/>
+      <c r="O1" s="42"/>
+      <c r="P1" s="42"/>
+      <c r="Q1" s="42"/>
+    </row>
+    <row r="2" spans="1:17" ht="171" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -3993,7 +5202,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -4018,7 +5227,7 @@
       <c r="N3" s="5"/>
       <c r="O3" s="2"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>0</v>
       </c>
@@ -4073,7 +5282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>20001</v>
       </c>
@@ -4131,7 +5340,7 @@
         <v>0.98089585309539973</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>25001</v>
       </c>
@@ -4189,7 +5398,7 @@
         <v>0.96840446418151849</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>30001</v>
       </c>
@@ -4247,7 +5456,7 @@
         <v>0.95248291794930184</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>35001</v>
       </c>
@@ -4305,7 +5514,7 @@
         <v>0.93410636653431389</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>40001</v>
       </c>
@@ -4363,7 +5572,7 @@
         <v>0.91004984352954654</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>45001</v>
       </c>
@@ -4421,7 +5630,7 @@
         <v>0.87844468918359042</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>50001</v>
       </c>
@@ -4479,7 +5688,7 @@
         <v>0.84037767239906014</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>55001</v>
       </c>
@@ -4537,7 +5746,7 @@
         <v>0.79864797463644943</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>60001</v>
       </c>
@@ -4595,7 +5804,7 @@
         <v>0.75568089851946385</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>65001</v>
       </c>
@@ -4653,7 +5862,7 @@
         <v>0.71348064754011409</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>70001</v>
       </c>
@@ -4711,7 +5920,7 @@
         <v>0.67264165900827766</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A16">
         <v>75001</v>
       </c>
@@ -4769,7 +5978,7 @@
         <v>0.63369903651969928</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A17">
         <v>80001</v>
       </c>
@@ -4827,7 +6036,7 @@
         <v>0.59648366659516738</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>85001</v>
       </c>
@@ -4885,7 +6094,7 @@
         <v>0.56095505372039822</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>90001</v>
       </c>
@@ -4943,7 +6152,7 @@
         <v>0.52708213649413505</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>95001</v>
       </c>
@@ -5001,7 +6210,7 @@
         <v>0.49450853049247107</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>100001</v>
       </c>
@@ -5059,7 +6268,7 @@
         <v>0.46352688881679166</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>120001</v>
       </c>
@@ -5117,7 +6326,7 @@
         <v>0.35762880548821618</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>150001</v>
       </c>
@@ -5175,7 +6384,7 @@
         <v>0.25279345891274818</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>200001</v>
       </c>
@@ -5233,7 +6442,7 @@
         <v>0.16215472373056269</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>300001</v>
       </c>
@@ -5291,7 +6500,7 @@
         <v>9.4056873898511625E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>400001</v>
       </c>
@@ -5349,7 +6558,7 @@
         <v>6.6707682992984421E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>500001</v>
       </c>
@@ -5407,7 +6616,7 @@
         <v>5.2219942358268129E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A28">
         <v>1000001</v>
       </c>
@@ -5465,7 +6674,7 @@
         <v>2.7334407515904005E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>2000001</v>
       </c>
@@ -5523,7 +6732,7 @@
         <v>1.6073385443575998E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
         <v>23</v>
       </c>
@@ -5544,7 +6753,7 @@
       <c r="J30" s="8"/>
       <c r="K30" s="8"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.45">
       <c r="N31" t="s">
         <v>25</v>
       </c>
@@ -5553,7 +6762,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.45">
       <c r="B32" t="s">
         <v>14</v>
       </c>
@@ -5580,7 +6789,7 @@
         <v>9.4291132404414987E-2</v>
       </c>
     </row>
-    <row r="33" spans="9:10" x14ac:dyDescent="0.35">
+    <row r="33" spans="9:10" x14ac:dyDescent="0.45">
       <c r="I33" t="s">
         <v>16</v>
       </c>
@@ -5589,7 +6798,7 @@
         <v>0.25720121848286576</v>
       </c>
     </row>
-    <row r="34" spans="9:10" x14ac:dyDescent="0.35">
+    <row r="34" spans="9:10" x14ac:dyDescent="0.45">
       <c r="I34" t="s">
         <v>18</v>
       </c>
@@ -5598,7 +6807,7 @@
         <v>0.27657368234858093</v>
       </c>
     </row>
-    <row r="35" spans="9:10" x14ac:dyDescent="0.35">
+    <row r="35" spans="9:10" x14ac:dyDescent="0.45">
       <c r="I35" t="s">
         <v>19</v>
       </c>
@@ -5618,39 +6827,1252 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{071C79C0-D56A-4054-A52D-D30424BA6045}">
+  <dimension ref="A1:X32"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="3" max="3" width="14.1328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.6640625" customWidth="1"/>
+    <col min="9" max="9" width="12.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:24" ht="57.4" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="43" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1" s="44"/>
+      <c r="I1" s="45"/>
+    </row>
+    <row r="2" spans="1:24" ht="43.15" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="G2" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="H2" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="I2" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="K2" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="R2" s="46" t="s">
+        <v>68</v>
+      </c>
+      <c r="S2" s="46"/>
+      <c r="T2" s="46"/>
+      <c r="U2" s="46"/>
+      <c r="V2" s="46"/>
+      <c r="W2" s="46"/>
+      <c r="X2" s="46"/>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="A3" s="1">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1">
+        <v>20000</v>
+      </c>
+      <c r="C3" s="11">
+        <v>6349766510</v>
+      </c>
+      <c r="D3" s="1">
+        <v>829909</v>
+      </c>
+      <c r="E3" s="1">
+        <f>C3/D3</f>
+        <v>7651.1599585014746</v>
+      </c>
+      <c r="G3" s="35">
+        <f>D3/D$29</f>
+        <v>0.17295308935382017</v>
+      </c>
+      <c r="H3" s="35">
+        <f>C3/C$29</f>
+        <v>1.9104146904600303E-2</v>
+      </c>
+      <c r="I3" s="34">
+        <f>H3*(LN(H3)- LN(G3))</f>
+        <v>-4.2088632053942511E-2</v>
+      </c>
+      <c r="J3">
+        <f>D3/D29</f>
+        <v>0.17295308935382017</v>
+      </c>
+      <c r="K3">
+        <f>I3</f>
+        <v>-4.2088632053942511E-2</v>
+      </c>
+      <c r="R3" s="46"/>
+      <c r="S3" s="46"/>
+      <c r="T3" s="46"/>
+      <c r="U3" s="46"/>
+      <c r="V3" s="46"/>
+      <c r="W3" s="46"/>
+      <c r="X3" s="46"/>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="A4">
+        <v>20001</v>
+      </c>
+      <c r="B4">
+        <v>25000</v>
+      </c>
+      <c r="C4" s="6">
+        <v>4151842183</v>
+      </c>
+      <c r="D4" s="6">
+        <v>183743</v>
+      </c>
+      <c r="E4" s="7">
+        <f>C4/D4</f>
+        <v>22595.920296283395</v>
+      </c>
+      <c r="G4" s="36">
+        <f>D4/D$29</f>
+        <v>3.8292053101170107E-2</v>
+      </c>
+      <c r="H4" s="36">
+        <f t="shared" ref="H4:H27" si="0">C4/C$29</f>
+        <v>1.2491388913881246E-2</v>
+      </c>
+      <c r="I4" s="29">
+        <f t="shared" ref="I4:I28" si="1">H4*(LN(H4)- LN(G4))</f>
+        <v>-1.3992889634159102E-2</v>
+      </c>
+      <c r="J4">
+        <f>SUM(D$3:D4)/D$29</f>
+        <v>0.21124514245499026</v>
+      </c>
+      <c r="K4">
+        <f>SUM($I$3:I4)</f>
+        <v>-5.6081521688101613E-2</v>
+      </c>
+      <c r="R4" s="46"/>
+      <c r="S4" s="46"/>
+      <c r="T4" s="46"/>
+      <c r="U4" s="46"/>
+      <c r="V4" s="46"/>
+      <c r="W4" s="46"/>
+      <c r="X4" s="46"/>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="A5">
+        <v>25001</v>
+      </c>
+      <c r="B5">
+        <v>30000</v>
+      </c>
+      <c r="C5" s="6">
+        <v>5291945333</v>
+      </c>
+      <c r="D5" s="6">
+        <v>192048</v>
+      </c>
+      <c r="E5" s="7">
+        <f>C5/D5</f>
+        <v>27555.326444430561</v>
+      </c>
+      <c r="G5" s="36">
+        <f t="shared" ref="G5:G27" si="2">D5/D$29</f>
+        <v>4.0022815639091103E-2</v>
+      </c>
+      <c r="H5" s="36">
+        <f t="shared" si="0"/>
+        <v>1.592154623221665E-2</v>
+      </c>
+      <c r="I5" s="29">
+        <f>H5*(LN(H5)- LN(G5))</f>
+        <v>-1.4676105276062229E-2</v>
+      </c>
+      <c r="J5">
+        <f>SUM(D$3:D5)/D$29</f>
+        <v>0.25126795809408137</v>
+      </c>
+      <c r="K5">
+        <f>SUM($I$3:I5)</f>
+        <v>-7.0757626964163836E-2</v>
+      </c>
+      <c r="R5" s="46"/>
+      <c r="S5" s="46"/>
+      <c r="T5" s="46"/>
+      <c r="U5" s="46"/>
+      <c r="V5" s="46"/>
+      <c r="W5" s="46"/>
+      <c r="X5" s="46"/>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="A6">
+        <v>30001</v>
+      </c>
+      <c r="B6">
+        <v>35000</v>
+      </c>
+      <c r="C6" s="6">
+        <v>6107930981</v>
+      </c>
+      <c r="D6" s="6">
+        <v>187369</v>
+      </c>
+      <c r="E6" s="7">
+        <f t="shared" ref="E6:E28" si="3">C6/D6</f>
+        <v>32598.407319247046</v>
+      </c>
+      <c r="G6" s="36">
+        <f t="shared" si="2"/>
+        <v>3.9047711736028806E-2</v>
+      </c>
+      <c r="H6" s="36">
+        <f t="shared" si="0"/>
+        <v>1.8376551414987924E-2</v>
+      </c>
+      <c r="I6" s="29">
+        <f t="shared" si="1"/>
+        <v>-1.3850568588215303E-2</v>
+      </c>
+      <c r="J6">
+        <f>SUM(D$3:D6)/D$29</f>
+        <v>0.2903156698301102</v>
+      </c>
+      <c r="K6">
+        <f>SUM($I$3:I6)</f>
+        <v>-8.460819555237914E-2</v>
+      </c>
+      <c r="R6" s="46"/>
+      <c r="S6" s="46"/>
+      <c r="T6" s="46"/>
+      <c r="U6" s="46"/>
+      <c r="V6" s="46"/>
+      <c r="W6" s="46"/>
+      <c r="X6" s="46"/>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="A7">
+        <v>35001</v>
+      </c>
+      <c r="B7">
+        <v>40000</v>
+      </c>
+      <c r="C7" s="6">
+        <v>7995819174</v>
+      </c>
+      <c r="D7" s="6">
+        <v>212579</v>
+      </c>
+      <c r="E7" s="7">
+        <f t="shared" si="3"/>
+        <v>37613.401013270362</v>
+      </c>
+      <c r="G7" s="36">
+        <f t="shared" si="2"/>
+        <v>4.4301477368899167E-2</v>
+      </c>
+      <c r="H7" s="36">
+        <f t="shared" si="0"/>
+        <v>2.405652300476728E-2</v>
+      </c>
+      <c r="I7" s="29">
+        <f t="shared" si="1"/>
+        <v>-1.4689197754153411E-2</v>
+      </c>
+      <c r="J7">
+        <f>SUM(D$3:D7)/D$29</f>
+        <v>0.33461714719900937</v>
+      </c>
+      <c r="K7">
+        <f>SUM($I$3:I7)</f>
+        <v>-9.9297393306532547E-2</v>
+      </c>
+      <c r="R7" s="46"/>
+      <c r="S7" s="46"/>
+      <c r="T7" s="46"/>
+      <c r="U7" s="46"/>
+      <c r="V7" s="46"/>
+      <c r="W7" s="46"/>
+      <c r="X7" s="46"/>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="A8">
+        <v>40001</v>
+      </c>
+      <c r="B8">
+        <v>45000</v>
+      </c>
+      <c r="C8" s="6">
+        <v>10504805664</v>
+      </c>
+      <c r="D8" s="6">
+        <v>246666</v>
+      </c>
+      <c r="E8" s="7">
+        <f>C8/D8</f>
+        <v>42587.165089635375</v>
+      </c>
+      <c r="G8" s="36">
+        <f t="shared" si="2"/>
+        <v>5.1405210376739383E-2</v>
+      </c>
+      <c r="H8" s="36">
+        <f t="shared" si="0"/>
+        <v>3.1605154345956149E-2</v>
+      </c>
+      <c r="I8" s="29">
+        <f t="shared" si="1"/>
+        <v>-1.5373357591131214E-2</v>
+      </c>
+      <c r="J8">
+        <f>SUM(D$3:D8)/D$29</f>
+        <v>0.38602235757574871</v>
+      </c>
+      <c r="K8">
+        <f>SUM($I$3:I8)</f>
+        <v>-0.11467075089766376</v>
+      </c>
+      <c r="R8" s="46"/>
+      <c r="S8" s="46"/>
+      <c r="T8" s="46"/>
+      <c r="U8" s="46"/>
+      <c r="V8" s="46"/>
+      <c r="W8" s="46"/>
+      <c r="X8" s="46"/>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="A9">
+        <v>45001</v>
+      </c>
+      <c r="B9">
+        <v>50000</v>
+      </c>
+      <c r="C9" s="6">
+        <v>12652575879</v>
+      </c>
+      <c r="D9" s="6">
+        <v>265973</v>
+      </c>
+      <c r="E9" s="7">
+        <f t="shared" si="3"/>
+        <v>47570.903358611591</v>
+      </c>
+      <c r="G9" s="36">
+        <f t="shared" si="2"/>
+        <v>5.5428790427268067E-2</v>
+      </c>
+      <c r="H9" s="36">
+        <f t="shared" si="0"/>
+        <v>3.8067016784530283E-2</v>
+      </c>
+      <c r="I9" s="29">
+        <f t="shared" si="1"/>
+        <v>-1.4303717170918728E-2</v>
+      </c>
+      <c r="J9">
+        <f>SUM(D$3:D9)/D$29</f>
+        <v>0.44145114800301682</v>
+      </c>
+      <c r="K9">
+        <f>SUM($I$3:I9)</f>
+        <v>-0.12897446806858248</v>
+      </c>
+      <c r="R9" s="46"/>
+      <c r="S9" s="46"/>
+      <c r="T9" s="46"/>
+      <c r="U9" s="46"/>
+      <c r="V9" s="46"/>
+      <c r="W9" s="46"/>
+      <c r="X9" s="46"/>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="A10">
+        <v>50001</v>
+      </c>
+      <c r="B10">
+        <v>55000</v>
+      </c>
+      <c r="C10" s="6">
+        <v>13869964393</v>
+      </c>
+      <c r="D10" s="6">
+        <v>264066</v>
+      </c>
+      <c r="E10" s="7">
+        <f t="shared" si="3"/>
+        <v>52524.612759688869</v>
+      </c>
+      <c r="G10" s="36">
+        <f t="shared" si="2"/>
+        <v>5.5031371503750266E-2</v>
+      </c>
+      <c r="H10" s="36">
+        <f t="shared" si="0"/>
+        <v>4.17296977626107E-2</v>
+      </c>
+      <c r="I10" s="29">
+        <f t="shared" si="1"/>
+        <v>-1.1546205167980323E-2</v>
+      </c>
+      <c r="J10">
+        <f>SUM(D$3:D10)/D$29</f>
+        <v>0.49648251950676708</v>
+      </c>
+      <c r="K10">
+        <f>SUM($I$3:I10)</f>
+        <v>-0.14052067323656281</v>
+      </c>
+      <c r="R10" s="46"/>
+      <c r="S10" s="46"/>
+      <c r="T10" s="46"/>
+      <c r="U10" s="46"/>
+      <c r="V10" s="46"/>
+      <c r="W10" s="46"/>
+      <c r="X10" s="46"/>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="A11">
+        <v>55001</v>
+      </c>
+      <c r="B11">
+        <v>60000</v>
+      </c>
+      <c r="C11" s="6">
+        <v>14281239687</v>
+      </c>
+      <c r="D11" s="6">
+        <v>248279</v>
+      </c>
+      <c r="E11" s="7">
+        <f t="shared" si="3"/>
+        <v>57520.93284973759</v>
+      </c>
+      <c r="G11" s="36">
+        <f t="shared" si="2"/>
+        <v>5.1741359681214592E-2</v>
+      </c>
+      <c r="H11" s="36">
+        <f t="shared" si="0"/>
+        <v>4.2967076116985602E-2</v>
+      </c>
+      <c r="I11" s="29">
+        <f t="shared" si="1"/>
+        <v>-7.9842840818468257E-3</v>
+      </c>
+      <c r="J11">
+        <f>SUM(D$3:D11)/D$29</f>
+        <v>0.54822387918798166</v>
+      </c>
+      <c r="K11">
+        <f>SUM($I$3:I11)</f>
+        <v>-0.14850495731840962</v>
+      </c>
+      <c r="R11" s="46"/>
+      <c r="S11" s="46"/>
+      <c r="T11" s="46"/>
+      <c r="U11" s="46"/>
+      <c r="V11" s="46"/>
+      <c r="W11" s="46"/>
+      <c r="X11" s="46"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="A12">
+        <v>60001</v>
+      </c>
+      <c r="B12">
+        <v>65000</v>
+      </c>
+      <c r="C12" s="6">
+        <v>14026365151</v>
+      </c>
+      <c r="D12" s="6">
+        <v>224425</v>
+      </c>
+      <c r="E12" s="7">
+        <f t="shared" si="3"/>
+        <v>62499.12064609558</v>
+      </c>
+      <c r="G12" s="36">
+        <f t="shared" si="2"/>
+        <v>4.6770184536173355E-2</v>
+      </c>
+      <c r="H12" s="36">
+        <f t="shared" si="0"/>
+        <v>4.2200250979349818E-2</v>
+      </c>
+      <c r="I12" s="29">
+        <f t="shared" si="1"/>
+        <v>-4.3390192108020186E-3</v>
+      </c>
+      <c r="J12">
+        <f>SUM(D$3:D12)/D$29</f>
+        <v>0.59499406372415498</v>
+      </c>
+      <c r="K12">
+        <f>SUM($I$3:I12)</f>
+        <v>-0.15284397652921164</v>
+      </c>
+      <c r="R12" s="46"/>
+      <c r="S12" s="46"/>
+      <c r="T12" s="46"/>
+      <c r="U12" s="46"/>
+      <c r="V12" s="46"/>
+      <c r="W12" s="46"/>
+      <c r="X12" s="46"/>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="A13">
+        <v>65001</v>
+      </c>
+      <c r="B13">
+        <v>70000</v>
+      </c>
+      <c r="C13" s="6">
+        <v>13573913715</v>
+      </c>
+      <c r="D13" s="6">
+        <v>201115</v>
+      </c>
+      <c r="E13" s="7">
+        <f t="shared" si="3"/>
+        <v>67493.293463938549</v>
+      </c>
+      <c r="G13" s="36">
+        <f t="shared" si="2"/>
+        <v>4.1912379026367401E-2</v>
+      </c>
+      <c r="H13" s="36">
+        <f t="shared" si="0"/>
+        <v>4.0838988531836401E-2</v>
+      </c>
+      <c r="I13" s="29">
+        <f t="shared" si="1"/>
+        <v>-1.0595266803264201E-3</v>
+      </c>
+      <c r="J13">
+        <f>SUM(D$3:D13)/D$29</f>
+        <v>0.63690644275052244</v>
+      </c>
+      <c r="K13">
+        <f>SUM($I$3:I13)</f>
+        <v>-0.15390350320953805</v>
+      </c>
+      <c r="R13" s="46"/>
+      <c r="S13" s="46"/>
+      <c r="T13" s="46"/>
+      <c r="U13" s="46"/>
+      <c r="V13" s="46"/>
+      <c r="W13" s="46"/>
+      <c r="X13" s="46"/>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="A14">
+        <v>70001</v>
+      </c>
+      <c r="B14">
+        <v>75000</v>
+      </c>
+      <c r="C14" s="6">
+        <v>12943606502</v>
+      </c>
+      <c r="D14" s="6">
+        <v>178545</v>
+      </c>
+      <c r="E14" s="7">
+        <f t="shared" si="3"/>
+        <v>72494.92566019771</v>
+      </c>
+      <c r="G14" s="36">
+        <f t="shared" si="2"/>
+        <v>3.72087895644918E-2</v>
+      </c>
+      <c r="H14" s="36">
+        <f t="shared" si="0"/>
+        <v>3.8942622488578348E-2</v>
+      </c>
+      <c r="I14" s="29">
+        <f t="shared" si="1"/>
+        <v>1.7736157508887016E-3</v>
+      </c>
+      <c r="J14">
+        <f>SUM(D$3:D14)/D$29</f>
+        <v>0.67411523231501425</v>
+      </c>
+      <c r="K14">
+        <f>SUM($I$3:I14)</f>
+        <v>-0.15212988745864936</v>
+      </c>
+      <c r="R14" s="46"/>
+      <c r="S14" s="46"/>
+      <c r="T14" s="46"/>
+      <c r="U14" s="46"/>
+      <c r="V14" s="46"/>
+      <c r="W14" s="46"/>
+      <c r="X14" s="46"/>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="A15">
+        <v>75001</v>
+      </c>
+      <c r="B15">
+        <v>80000</v>
+      </c>
+      <c r="C15" s="6">
+        <v>12369508609</v>
+      </c>
+      <c r="D15" s="6">
+        <v>159615</v>
+      </c>
+      <c r="E15" s="7">
+        <f t="shared" si="3"/>
+        <v>77495.903323622464</v>
+      </c>
+      <c r="G15" s="36">
+        <f t="shared" si="2"/>
+        <v>3.3263776338381686E-2</v>
+      </c>
+      <c r="H15" s="36">
+        <f t="shared" si="0"/>
+        <v>3.7215369924531942E-2</v>
+      </c>
+      <c r="I15" s="29">
+        <f t="shared" si="1"/>
+        <v>4.1775309174201074E-3</v>
+      </c>
+      <c r="J15">
+        <f>SUM(D$3:D15)/D$29</f>
+        <v>0.70737900865339587</v>
+      </c>
+      <c r="K15">
+        <f>SUM($I$3:I15)</f>
+        <v>-0.14795235654122926</v>
+      </c>
+      <c r="R15" s="46"/>
+      <c r="S15" s="46"/>
+      <c r="T15" s="46"/>
+      <c r="U15" s="46"/>
+      <c r="V15" s="46"/>
+      <c r="W15" s="46"/>
+      <c r="X15" s="46"/>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="A16">
+        <v>80001</v>
+      </c>
+      <c r="B16">
+        <v>85000</v>
+      </c>
+      <c r="C16" s="6">
+        <v>11808870467</v>
+      </c>
+      <c r="D16" s="6">
+        <v>143150</v>
+      </c>
+      <c r="E16" s="7">
+        <f t="shared" si="3"/>
+        <v>82492.98265455816</v>
+      </c>
+      <c r="G16" s="36">
+        <f t="shared" si="2"/>
+        <v>2.983246927193145E-2</v>
+      </c>
+      <c r="H16" s="36">
+        <f t="shared" si="0"/>
+        <v>3.5528612874769147E-2</v>
+      </c>
+      <c r="I16" s="29">
+        <f t="shared" si="1"/>
+        <v>6.2083051672566624E-3</v>
+      </c>
+      <c r="J16">
+        <f>SUM(D$3:D16)/D$29</f>
+        <v>0.73721147792532737</v>
+      </c>
+      <c r="K16">
+        <f>SUM($I$3:I16)</f>
+        <v>-0.14174405137397261</v>
+      </c>
+      <c r="R16" s="46"/>
+      <c r="S16" s="46"/>
+      <c r="T16" s="46"/>
+      <c r="U16" s="46"/>
+      <c r="V16" s="46"/>
+      <c r="W16" s="46"/>
+      <c r="X16" s="46"/>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="A17">
+        <v>85001</v>
+      </c>
+      <c r="B17">
+        <v>90000</v>
+      </c>
+      <c r="C17" s="6">
+        <v>11258556400</v>
+      </c>
+      <c r="D17" s="6">
+        <v>128672</v>
+      </c>
+      <c r="E17" s="7">
+        <f t="shared" si="3"/>
+        <v>87498.106814225321</v>
+      </c>
+      <c r="G17" s="36">
+        <f t="shared" si="2"/>
+        <v>2.6815253134180674E-2</v>
+      </c>
+      <c r="H17" s="36">
+        <f t="shared" si="0"/>
+        <v>3.3872917226263163E-2</v>
+      </c>
+      <c r="I17" s="29">
+        <f t="shared" si="1"/>
+        <v>7.9142350626663863E-3</v>
+      </c>
+      <c r="J17">
+        <f>SUM(D$3:D17)/D$29</f>
+        <v>0.76402673105950802</v>
+      </c>
+      <c r="K17">
+        <f>SUM($I$3:I17)</f>
+        <v>-0.13382981631130622</v>
+      </c>
+      <c r="R17" s="46"/>
+      <c r="S17" s="46"/>
+      <c r="T17" s="46"/>
+      <c r="U17" s="46"/>
+      <c r="V17" s="46"/>
+      <c r="W17" s="46"/>
+      <c r="X17" s="46"/>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="A18">
+        <v>90001</v>
+      </c>
+      <c r="B18">
+        <v>95000</v>
+      </c>
+      <c r="C18" s="6">
+        <v>10826696085</v>
+      </c>
+      <c r="D18" s="6">
+        <v>117057</v>
+      </c>
+      <c r="E18" s="7">
+        <f t="shared" si="3"/>
+        <v>92490.804351726081</v>
+      </c>
+      <c r="G18" s="36">
+        <f t="shared" si="2"/>
+        <v>2.4394686381868529E-2</v>
+      </c>
+      <c r="H18" s="36">
+        <f t="shared" si="0"/>
+        <v>3.2573606001663979E-2</v>
+      </c>
+      <c r="I18" s="29">
+        <f t="shared" si="1"/>
+        <v>9.4182344332991354E-3</v>
+      </c>
+      <c r="J18">
+        <f>SUM(D$3:D18)/D$29</f>
+        <v>0.7884214174413765</v>
+      </c>
+      <c r="K18">
+        <f>SUM($I$3:I18)</f>
+        <v>-0.12441158187800709</v>
+      </c>
+      <c r="R18" s="46"/>
+      <c r="S18" s="46"/>
+      <c r="T18" s="46"/>
+      <c r="U18" s="46"/>
+      <c r="V18" s="46"/>
+      <c r="W18" s="46"/>
+      <c r="X18" s="46"/>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="A19">
+        <v>95001</v>
+      </c>
+      <c r="B19">
+        <v>100000</v>
+      </c>
+      <c r="C19" s="6">
+        <v>10297564802</v>
+      </c>
+      <c r="D19" s="6">
+        <v>105622</v>
+      </c>
+      <c r="E19" s="7">
+        <f t="shared" si="3"/>
+        <v>97494.50684516484</v>
+      </c>
+      <c r="G19" s="36">
+        <f>D19/D$29</f>
+        <v>2.2011631641215113E-2</v>
+      </c>
+      <c r="H19" s="36">
+        <f t="shared" si="0"/>
+        <v>3.0981641675679399E-2</v>
+      </c>
+      <c r="I19" s="29">
+        <f t="shared" si="1"/>
+        <v>1.0590262501714576E-2</v>
+      </c>
+      <c r="J19">
+        <f>SUM(D$3:D19)/D$29</f>
+        <v>0.81043304908259162</v>
+      </c>
+      <c r="K19">
+        <f>SUM($I$3:I19)</f>
+        <v>-0.11382131937629252</v>
+      </c>
+      <c r="R19" s="46"/>
+      <c r="S19" s="46"/>
+      <c r="T19" s="46"/>
+      <c r="U19" s="46"/>
+      <c r="V19" s="46"/>
+      <c r="W19" s="46"/>
+      <c r="X19" s="46"/>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="A20">
+        <v>100001</v>
+      </c>
+      <c r="B20">
+        <v>120000</v>
+      </c>
+      <c r="C20" s="6">
+        <v>35198017810</v>
+      </c>
+      <c r="D20" s="6">
+        <v>322166</v>
+      </c>
+      <c r="E20" s="7">
+        <f t="shared" si="3"/>
+        <v>109254.29067623524</v>
+      </c>
+      <c r="G20" s="36">
+        <f t="shared" si="2"/>
+        <v>6.7139415266930264E-2</v>
+      </c>
+      <c r="H20" s="36">
+        <f t="shared" si="0"/>
+        <v>0.10589808332857546</v>
+      </c>
+      <c r="I20" s="29">
+        <f t="shared" si="1"/>
+        <v>4.8258378322750033E-2</v>
+      </c>
+      <c r="J20">
+        <f>SUM(D$3:D20)/D$29</f>
+        <v>0.87757246434952196</v>
+      </c>
+      <c r="K20">
+        <f>SUM($I$3:I20)</f>
+        <v>-6.5562941053542489E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="A21">
+        <v>120001</v>
+      </c>
+      <c r="B21">
+        <v>150000</v>
+      </c>
+      <c r="C21" s="6">
+        <v>34844789253</v>
+      </c>
+      <c r="D21" s="6">
+        <v>261644</v>
+      </c>
+      <c r="E21" s="7">
+        <f t="shared" si="3"/>
+        <v>133176.33598706638</v>
+      </c>
+      <c r="G21" s="36">
+        <f t="shared" si="2"/>
+        <v>5.4526626546875533E-2</v>
+      </c>
+      <c r="H21" s="36">
+        <f t="shared" si="0"/>
+        <v>0.10483534657546799</v>
+      </c>
+      <c r="I21" s="29">
+        <f t="shared" si="1"/>
+        <v>6.8531059860244811E-2</v>
+      </c>
+      <c r="J21">
+        <f>SUM(D$3:D21)/D$29</f>
+        <v>0.93209909089639742</v>
+      </c>
+      <c r="K21">
+        <f>SUM($I$3:I21)</f>
+        <v>2.9681188067023218E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="A22">
+        <v>150001</v>
+      </c>
+      <c r="B22">
+        <v>200000</v>
+      </c>
+      <c r="C22" s="6">
+        <v>30126171456</v>
+      </c>
+      <c r="D22" s="6">
+        <v>176681</v>
+      </c>
+      <c r="E22" s="7">
+        <f t="shared" si="3"/>
+        <v>170511.66484228638</v>
+      </c>
+      <c r="G22" s="36">
+        <f t="shared" si="2"/>
+        <v>3.6820331843759137E-2</v>
+      </c>
+      <c r="H22" s="36">
+        <f t="shared" si="0"/>
+        <v>9.0638735182185529E-2</v>
+      </c>
+      <c r="I22" s="29">
+        <f t="shared" si="1"/>
+        <v>8.1650225412226426E-2</v>
+      </c>
+      <c r="J22">
+        <f>SUM(D$3:D22)/D$29</f>
+        <v>0.96891942274015663</v>
+      </c>
+      <c r="K22">
+        <f>SUM($I$3:I22)</f>
+        <v>8.4618344218928748E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="A23">
+        <v>200001</v>
+      </c>
+      <c r="B23">
+        <v>300000</v>
+      </c>
+      <c r="C23" s="6">
+        <v>22634114385</v>
+      </c>
+      <c r="D23" s="6">
+        <v>95219</v>
+      </c>
+      <c r="E23" s="7">
+        <f t="shared" si="3"/>
+        <v>237705.86106764406</v>
+      </c>
+      <c r="G23" s="36">
+        <f t="shared" si="2"/>
+        <v>1.9843645767405105E-2</v>
+      </c>
+      <c r="H23" s="36">
+        <f t="shared" si="0"/>
+        <v>6.8097849832051055E-2</v>
+      </c>
+      <c r="I23" s="29">
+        <f t="shared" si="1"/>
+        <v>8.3968856987618093E-2</v>
+      </c>
+      <c r="J23">
+        <f>SUM(D$3:D23)/D$29</f>
+        <v>0.98876306850756168</v>
+      </c>
+      <c r="K23">
+        <f>SUM($I$3:I23)</f>
+        <v>0.16858720120654686</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="A24">
+        <v>300001</v>
+      </c>
+      <c r="B24">
+        <v>400000</v>
+      </c>
+      <c r="C24" s="6">
+        <v>9090224094</v>
+      </c>
+      <c r="D24" s="6">
+        <v>26610</v>
+      </c>
+      <c r="E24" s="7">
+        <f t="shared" si="3"/>
+        <v>341609.32333709131</v>
+      </c>
+      <c r="G24" s="36">
+        <f t="shared" si="2"/>
+        <v>5.5455257235493948E-3</v>
+      </c>
+      <c r="H24" s="36">
+        <f t="shared" si="0"/>
+        <v>2.7349190905527201E-2</v>
+      </c>
+      <c r="I24" s="29">
+        <f t="shared" si="1"/>
+        <v>4.3640981369792477E-2</v>
+      </c>
+      <c r="J24">
+        <f>SUM(D$3:D24)/D$29</f>
+        <v>0.99430859423111106</v>
+      </c>
+      <c r="K24">
+        <f>SUM($I$3:I24)</f>
+        <v>0.21222818257633932</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="A25">
+        <v>400001</v>
+      </c>
+      <c r="B25">
+        <v>500000</v>
+      </c>
+      <c r="C25" s="6">
+        <v>4815382270</v>
+      </c>
+      <c r="D25" s="6">
+        <v>10859</v>
+      </c>
+      <c r="E25" s="7">
+        <f t="shared" si="3"/>
+        <v>443446.19854498573</v>
+      </c>
+      <c r="G25" s="36">
+        <f t="shared" si="2"/>
+        <v>2.2630163033454669E-3</v>
+      </c>
+      <c r="H25" s="36">
+        <f t="shared" si="0"/>
+        <v>1.4487740634716296E-2</v>
+      </c>
+      <c r="I25" s="29">
+        <f t="shared" si="1"/>
+        <v>2.6898000797825308E-2</v>
+      </c>
+      <c r="J25">
+        <f>SUM(D$3:D25)/D$29</f>
+        <v>0.99657161053445653</v>
+      </c>
+      <c r="K25">
+        <f>SUM($I$3:I25)</f>
+        <v>0.23912618337416464</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="A26">
+        <v>500001</v>
+      </c>
+      <c r="B26">
+        <v>1000000</v>
+      </c>
+      <c r="C26" s="6">
+        <v>8271363098</v>
+      </c>
+      <c r="D26" s="6">
+        <v>12535</v>
+      </c>
+      <c r="E26" s="7">
+        <f t="shared" si="3"/>
+        <v>659861.43581970478</v>
+      </c>
+      <c r="G26" s="36">
+        <f t="shared" si="2"/>
+        <v>2.6122948119012275E-3</v>
+      </c>
+      <c r="H26" s="36">
+        <f t="shared" si="0"/>
+        <v>2.4885534842364127E-2</v>
+      </c>
+      <c r="I26" s="29">
+        <f t="shared" si="1"/>
+        <v>5.6093429721222138E-2</v>
+      </c>
+      <c r="J26">
+        <f>SUM(D$3:D26)/D$29</f>
+        <v>0.99918390534635781</v>
+      </c>
+      <c r="K26">
+        <f>SUM($I$3:I26)</f>
+        <v>0.2952196130953868</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="A27">
+        <v>1000001</v>
+      </c>
+      <c r="B27">
+        <v>2000000</v>
+      </c>
+      <c r="C27" s="6">
+        <v>3742897350</v>
+      </c>
+      <c r="D27" s="6">
+        <v>2797</v>
+      </c>
+      <c r="E27" s="7">
+        <f t="shared" si="3"/>
+        <v>1338182.8208795139</v>
+      </c>
+      <c r="G27" s="36">
+        <f t="shared" si="2"/>
+        <v>5.8289498116376019E-4</v>
+      </c>
+      <c r="H27" s="36">
+        <f t="shared" si="0"/>
+        <v>1.1261022072328007E-2</v>
+      </c>
+      <c r="I27" s="29">
+        <f t="shared" si="1"/>
+        <v>3.3344963279958083E-2</v>
+      </c>
+      <c r="J27">
+        <f>SUM(D$3:D27)/D$29</f>
+        <v>0.99976680032752152</v>
+      </c>
+      <c r="K27">
+        <f>SUM($I$3:I27)</f>
+        <v>0.32856457637534486</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A28">
+        <v>2000001</v>
+      </c>
+      <c r="B28" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" s="6">
+        <v>5342413095</v>
+      </c>
+      <c r="D28" s="6">
+        <v>1119</v>
+      </c>
+      <c r="E28" s="7">
+        <f t="shared" si="3"/>
+        <v>4774274.4369973186</v>
+      </c>
+      <c r="G28" s="37">
+        <f>D28/D$29</f>
+        <v>2.3319967247845821E-4</v>
+      </c>
+      <c r="H28" s="37">
+        <f>C28/C$29</f>
+        <v>1.6073385443575998E-2</v>
+      </c>
+      <c r="I28" s="30">
+        <f t="shared" si="1"/>
+        <v>6.8039043302673324E-2</v>
+      </c>
+      <c r="J28">
+        <f>SUM(D$3:D28)/D$29</f>
+        <v>1</v>
+      </c>
+      <c r="K28">
+        <f>SUM($I$3:I28)</f>
+        <v>0.39660361967801816</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B29" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" s="6">
+        <v>332376344346</v>
+      </c>
+      <c r="D29" s="6">
+        <v>4798463</v>
+      </c>
+      <c r="E29" s="7">
+        <f>C29/D29</f>
+        <v>69267.251689968223</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="I30" s="26" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="I31" s="27">
+        <f>SUM(I3:I28)</f>
+        <v>0.39660361967801816</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="I32">
+        <f>LN(D29)</f>
+        <v>15.383806216267152</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="R2:X19"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{988134C0-BA93-4AA9-AB60-815506C21888}">
   <dimension ref="A1:Q95"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="17.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="58.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.36328125" customWidth="1"/>
-    <col min="5" max="5" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.26953125" customWidth="1"/>
-    <col min="14" max="14" width="13.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.59765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="58.59765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" customWidth="1"/>
+    <col min="5" max="5" width="11.19921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.265625" customWidth="1"/>
+    <col min="12" max="12" width="67.3984375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.06640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="F1" s="25" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="F1" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="26" t="s">
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="K1" s="27"/>
-      <c r="L1" s="28" t="s">
+      <c r="K1" s="40"/>
+      <c r="L1" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="29"/>
-    </row>
-    <row r="2" spans="1:17" ht="203" x14ac:dyDescent="0.35">
+      <c r="M1" s="42"/>
+      <c r="N1" s="42"/>
+      <c r="O1" s="42"/>
+      <c r="P1" s="42"/>
+      <c r="Q1" s="42"/>
+    </row>
+    <row r="2" spans="1:17" ht="199.5" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -5678,12 +8100,10 @@
       <c r="I2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="J2" s="48" t="s">
+        <v>70</v>
+      </c>
+      <c r="K2" s="49"/>
       <c r="L2" s="4" t="s">
         <v>10</v>
       </c>
@@ -5697,7 +8117,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -5722,7 +8142,7 @@
       <c r="N3" s="5"/>
       <c r="O3" s="2"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A4" s="20">
         <v>0</v>
       </c>
@@ -5756,7 +8176,7 @@
         <v>3.8461538461538464E-2</v>
       </c>
       <c r="J4" s="13">
-        <f>F4*G4/2</f>
+        <f>((G3+G4)*(F4-F3))/2</f>
         <v>3.6431800019435167E-3</v>
       </c>
       <c r="K4" s="14"/>
@@ -5773,11 +8193,11 @@
         <v>16114546981</v>
       </c>
       <c r="O4" s="17">
-        <f>N4/C$32</f>
+        <f t="shared" ref="O4:O29" si="0">N4/C$32</f>
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>20001</v>
       </c>
@@ -5803,27 +8223,24 @@
         <v>4.0123222561722724E-2</v>
       </c>
       <c r="H5" s="13">
-        <f t="shared" ref="H5:I29" si="0">H4+1/26</f>
+        <f t="shared" ref="H5:I29" si="1">H4+1/26</f>
         <v>7.6923076923076927E-2</v>
       </c>
       <c r="I5" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="J5" s="8">
-        <f>((F5-F4)*(G5-G4))/2</f>
-        <v>2.8694306344413439E-4</v>
-      </c>
-      <c r="K5" s="8">
-        <f>(F5-F4)*G4</f>
-        <v>1.0447179624853218E-3</v>
-      </c>
+      <c r="J5" s="13">
+        <f>((G4+G5)*(F5-F4))/2</f>
+        <v>1.3316610259294563E-3</v>
+      </c>
+      <c r="K5" s="14"/>
       <c r="L5" s="18">
         <f>SUM(D5:$D$29)</f>
         <v>180067</v>
       </c>
       <c r="M5" s="16">
-        <f t="shared" ref="M5:M29" si="1">L5/$D$32</f>
+        <f t="shared" ref="M5:M29" si="2">L5/$D$32</f>
         <v>0.71864386486540421</v>
       </c>
       <c r="N5" s="9">
@@ -5831,11 +8248,11 @@
         <v>15697223966</v>
       </c>
       <c r="O5" s="17">
-        <f t="shared" ref="O5:O29" si="2">N5/C$32</f>
+        <f t="shared" si="0"/>
         <v>0.97410271505044177</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>25001</v>
       </c>
@@ -5861,27 +8278,24 @@
         <v>5.9077249526311083E-2</v>
       </c>
       <c r="H6" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.11538461538461539</v>
       </c>
       <c r="I6" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.11538461538461539</v>
       </c>
-      <c r="J6" s="8">
-        <f t="shared" ref="J6:J28" si="3">((F6-F5)*(G6-G5))/2</f>
-        <v>4.1831767850327714E-4</v>
-      </c>
-      <c r="K6" s="8">
-        <f t="shared" ref="K6:K29" si="4">(F6-F5)*G5</f>
-        <v>1.7710487958519879E-3</v>
-      </c>
+      <c r="J6" s="13">
+        <f t="shared" ref="J6:J29" si="3">((G5+G6)*(F6-F5))/2</f>
+        <v>2.189366474355265E-3</v>
+      </c>
+      <c r="K6" s="14"/>
       <c r="L6" s="18">
         <f>SUM(D6:$D$29)</f>
         <v>169959</v>
       </c>
       <c r="M6" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.67830303514058232</v>
       </c>
       <c r="N6" s="9">
@@ -5889,11 +8303,11 @@
         <v>15467979426</v>
       </c>
       <c r="O6" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.95987677743827726</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>30001</v>
       </c>
@@ -5907,7 +8321,7 @@
         <v>9424</v>
       </c>
       <c r="E7" s="7">
-        <f t="shared" ref="E7:E29" si="5">C7/D7</f>
+        <f t="shared" ref="E7:E29" si="4">C7/D7</f>
         <v>32605.774193548386</v>
       </c>
       <c r="F7" s="8">
@@ -5919,27 +8333,24 @@
         <v>7.8145537102890031E-2</v>
       </c>
       <c r="H7" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.15384615384615385</v>
       </c>
       <c r="I7" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.15384615384615385</v>
       </c>
-      <c r="J7" s="8">
+      <c r="J7" s="13">
         <f t="shared" si="3"/>
-        <v>3.585886738404805E-4</v>
-      </c>
-      <c r="K7" s="8">
-        <f t="shared" si="4"/>
-        <v>2.2219543812422153E-3</v>
-      </c>
+        <v>2.5805430550826956E-3</v>
+      </c>
+      <c r="K7" s="14"/>
       <c r="L7" s="18">
         <f>SUM(D7:$D$29)</f>
         <v>158899</v>
       </c>
       <c r="M7" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.63416279208987691</v>
       </c>
       <c r="N7" s="9">
@@ -5947,11 +8358,11 @@
         <v>15162543868</v>
       </c>
       <c r="O7" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.9409227504736889</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>35001</v>
       </c>
@@ -5965,7 +8376,7 @@
         <v>9839</v>
       </c>
       <c r="E8" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>37622.962699461328</v>
       </c>
       <c r="F8" s="8">
@@ -5977,27 +8388,24 @@
         <v>0.10111685180608677</v>
       </c>
       <c r="H8" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.19230769230769232</v>
       </c>
       <c r="I8" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.19230769230769232</v>
       </c>
-      <c r="J8" s="8">
+      <c r="J8" s="13">
         <f t="shared" si="3"/>
-        <v>4.5101024756999684E-4</v>
-      </c>
-      <c r="K8" s="8">
-        <f t="shared" si="4"/>
-        <v>3.0685608107889539E-3</v>
-      </c>
+        <v>3.5195710583589509E-3</v>
+      </c>
+      <c r="K8" s="14"/>
       <c r="L8" s="18">
         <f>SUM(D8:$D$29)</f>
         <v>149475</v>
       </c>
       <c r="M8" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.5965517929479377</v>
       </c>
       <c r="N8" s="9">
@@ -6005,11 +8413,11 @@
         <v>14855267052</v>
       </c>
       <c r="O8" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.92185446289710993</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>40001</v>
       </c>
@@ -6035,27 +8443,24 @@
         <v>0.1279567556215622</v>
       </c>
       <c r="H9" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.23076923076923078</v>
       </c>
       <c r="I9" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.23076923076923078</v>
       </c>
-      <c r="J9" s="8">
+      <c r="J9" s="13">
         <f t="shared" si="3"/>
-        <v>5.4388925677200176E-4</v>
-      </c>
-      <c r="K9" s="8">
-        <f t="shared" si="4"/>
-        <v>4.0981048035073232E-3</v>
-      </c>
+        <v>4.6419940602793249E-3</v>
+      </c>
+      <c r="K9" s="14"/>
       <c r="L9" s="18">
         <f>SUM(D9:$D$29)</f>
         <v>139636</v>
       </c>
       <c r="M9" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.55728453694650093</v>
       </c>
       <c r="N9" s="9">
@@ -6063,11 +8468,11 @@
         <v>14485094722</v>
       </c>
       <c r="O9" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.89888314819391324</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>45001</v>
       </c>
@@ -6081,7 +8486,7 @@
         <v>10235</v>
       </c>
       <c r="E10" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>47614.893795798729</v>
       </c>
       <c r="F10" s="8">
@@ -6093,27 +8498,24 @@
         <v>0.15819889885863866</v>
       </c>
       <c r="H10" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.26923076923076927</v>
       </c>
       <c r="I10" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.26923076923076927</v>
       </c>
-      <c r="J10" s="8">
+      <c r="J10" s="13">
         <f t="shared" si="3"/>
-        <v>6.1766075874818366E-4</v>
-      </c>
-      <c r="K10" s="8">
-        <f t="shared" si="4"/>
-        <v>5.2267371491895812E-3</v>
-      </c>
+        <v>5.8443979079377652E-3</v>
+      </c>
+      <c r="K10" s="14"/>
       <c r="L10" s="18">
         <f>SUM(D10:$D$29)</f>
         <v>129481</v>
       </c>
       <c r="M10" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.5167561311436154</v>
       </c>
       <c r="N10" s="9">
@@ -6121,11 +8523,11 @@
         <v>14052581831</v>
       </c>
       <c r="O10" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.87204324437843783</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>50001</v>
       </c>
@@ -6139,7 +8541,7 @@
         <v>9919</v>
       </c>
       <c r="E11" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>52561.418187317271</v>
       </c>
       <c r="F11" s="8">
@@ -6151,27 +8553,24 @@
         <v>0.19055207066140237</v>
       </c>
       <c r="H11" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.30769230769230771</v>
       </c>
       <c r="I11" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.30769230769230771</v>
       </c>
-      <c r="J11" s="8">
+      <c r="J11" s="13">
         <f t="shared" si="3"/>
-        <v>6.4037497478022353E-4</v>
-      </c>
-      <c r="K11" s="8">
-        <f t="shared" si="4"/>
-        <v>6.2625461568009818E-3</v>
-      </c>
+        <v>6.9029211315812054E-3</v>
+      </c>
+      <c r="K11" s="14"/>
       <c r="L11" s="18">
         <f>SUM(D11:$D$29)</f>
         <v>119246</v>
       </c>
       <c r="M11" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.47590844690998346</v>
       </c>
       <c r="N11" s="9">
@@ -6179,11 +8578,11 @@
         <v>13565243393</v>
       </c>
       <c r="O11" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.84180110114136131</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>55001</v>
       </c>
@@ -6197,7 +8596,7 @@
         <v>10198</v>
       </c>
       <c r="E12" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>57571.528829182193</v>
       </c>
       <c r="F12" s="8">
@@ -6209,27 +8608,24 @@
         <v>0.22698588736703129</v>
       </c>
       <c r="H12" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.34615384615384615</v>
       </c>
       <c r="I12" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.34615384615384615</v>
       </c>
-      <c r="J12" s="8">
+      <c r="J12" s="13">
         <f t="shared" si="3"/>
-        <v>7.4142849712450555E-4</v>
-      </c>
-      <c r="K12" s="8">
-        <f t="shared" si="4"/>
-        <v>7.7554726981221627E-3</v>
-      </c>
+        <v>8.4969011952466672E-3</v>
+      </c>
+      <c r="K12" s="14"/>
       <c r="L12" s="18">
         <f>SUM(D12:$D$29)</f>
         <v>109327</v>
       </c>
       <c r="M12" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.43632191247780017</v>
       </c>
       <c r="N12" s="9">
@@ -6237,11 +8633,11 @@
         <v>13043886686</v>
       </c>
       <c r="O12" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.80944792933859766</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>60001</v>
       </c>
@@ -6255,7 +8651,7 @@
         <v>9244</v>
       </c>
       <c r="E13" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>62549.824967546519</v>
       </c>
       <c r="F13" s="8">
@@ -6267,27 +8663,24 @@
         <v>0.26286716796907017</v>
       </c>
       <c r="H13" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.38461538461538458</v>
       </c>
       <c r="I13" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.38461538461538458</v>
       </c>
-      <c r="J13" s="8">
+      <c r="J13" s="13">
         <f t="shared" si="3"/>
-        <v>6.6187727313321456E-4</v>
-      </c>
-      <c r="K13" s="8">
-        <f t="shared" si="4"/>
-        <v>8.3741046946733989E-3</v>
-      </c>
+        <v>9.0359819678066128E-3</v>
+      </c>
+      <c r="K13" s="14"/>
       <c r="L13" s="18">
         <f>SUM(D13:$D$29)</f>
         <v>99129</v>
       </c>
       <c r="M13" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.39562189451838842</v>
       </c>
       <c r="N13" s="9">
@@ -6295,11 +8688,11 @@
         <v>12456772235</v>
       </c>
       <c r="O13" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.77301411263296871</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>65001</v>
       </c>
@@ -6313,7 +8706,7 @@
         <v>8567</v>
       </c>
       <c r="E14" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>67522.061048208241</v>
       </c>
       <c r="F14" s="8">
@@ -6325,27 +8718,24 @@
         <v>0.2987640192849676</v>
       </c>
       <c r="H14" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.42307692307692302</v>
       </c>
       <c r="I14" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.42307692307692302</v>
       </c>
-      <c r="J14" s="8">
+      <c r="J14" s="13">
         <f t="shared" si="3"/>
-        <v>6.1366975679622601E-4</v>
-      </c>
-      <c r="K14" s="8">
-        <f t="shared" si="4"/>
-        <v>8.9876200905594176E-3</v>
-      </c>
+        <v>9.6012898473556447E-3</v>
+      </c>
+      <c r="K14" s="14"/>
       <c r="L14" s="18">
         <f>SUM(D14:$D$29)</f>
         <v>89885</v>
       </c>
       <c r="M14" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.35872927184562886</v>
       </c>
       <c r="N14" s="9">
@@ -6353,11 +8743,11 @@
         <v>11878561653</v>
       </c>
       <c r="O14" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.73713283203092983</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>70001</v>
       </c>
@@ -6371,7 +8761,7 @@
         <v>7974</v>
       </c>
       <c r="E15" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>72512.12528216705</v>
       </c>
       <c r="F15" s="8">
@@ -6383,27 +8773,24 @@
         <v>0.33464536845858972</v>
       </c>
       <c r="H15" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.46153846153846145</v>
       </c>
       <c r="I15" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.46153846153846145</v>
       </c>
-      <c r="J15" s="8">
+      <c r="J15" s="13">
         <f t="shared" si="3"/>
-        <v>5.7094541997178923E-4</v>
-      </c>
-      <c r="K15" s="8">
-        <f t="shared" si="4"/>
-        <v>9.5078893292292656E-3</v>
-      </c>
+        <v>1.0078834749201055E-2</v>
+      </c>
+      <c r="K15" s="14"/>
       <c r="L15" s="18">
         <f>SUM(D15:$D$29)</f>
         <v>81318</v>
       </c>
       <c r="M15" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.32453854289306167</v>
       </c>
       <c r="N15" s="9">
@@ -6411,11 +8798,11 @@
         <v>11300100156</v>
       </c>
       <c r="O15" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.70123598071503246</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A16">
         <v>75001</v>
       </c>
@@ -6429,7 +8816,7 @@
         <v>7069</v>
       </c>
       <c r="E16" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>77530.009053614369</v>
       </c>
       <c r="F16" s="8">
@@ -6441,27 +8828,24 @@
         <v>0.36865560992837443</v>
       </c>
       <c r="H16" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.49999999999999989</v>
       </c>
       <c r="I16" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.49999999999999989</v>
       </c>
-      <c r="J16" s="8">
+      <c r="J16" s="13">
         <f t="shared" si="3"/>
-        <v>4.7975255312974357E-4</v>
-      </c>
-      <c r="K16" s="8">
-        <f t="shared" si="4"/>
-        <v>9.4410955625637005E-3</v>
-      </c>
+        <v>9.9208481156934439E-3</v>
+      </c>
+      <c r="K16" s="14"/>
       <c r="L16" s="18">
         <f>SUM(D16:$D$29)</f>
         <v>73344</v>
       </c>
       <c r="M16" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.292714465308403</v>
       </c>
       <c r="N16" s="9">
@@ -6469,11 +8853,11 @@
         <v>10721888469</v>
       </c>
       <c r="O16" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.66535463154141028</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A17">
         <v>80001</v>
       </c>
@@ -6487,7 +8871,7 @@
         <v>6375</v>
       </c>
       <c r="E17" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>82516.261176470594</v>
       </c>
       <c r="F17" s="8">
@@ -6499,27 +8883,24 @@
         <v>0.40129947919880654</v>
       </c>
       <c r="H17" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.53846153846153832</v>
       </c>
       <c r="I17" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.53846153846153832</v>
       </c>
-      <c r="J17" s="8">
+      <c r="J17" s="13">
         <f t="shared" si="3"/>
-        <v>4.1527082114222754E-4</v>
-      </c>
-      <c r="K17" s="8">
-        <f t="shared" si="4"/>
-        <v>9.3795203372114399E-3</v>
-      </c>
+        <v>9.7947911583536676E-3</v>
+      </c>
+      <c r="K17" s="14"/>
       <c r="L17" s="18">
         <f>SUM(D17:$D$29)</f>
         <v>66275</v>
       </c>
       <c r="M17" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.26450222497156428</v>
       </c>
       <c r="N17" s="9">
@@ -6527,11 +8908,11 @@
         <v>10173828835</v>
       </c>
       <c r="O17" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.63134439007162557</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>85001</v>
       </c>
@@ -6545,7 +8926,7 @@
         <v>5745</v>
       </c>
       <c r="E18" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>87542.377371627503</v>
       </c>
       <c r="F18" s="8">
@@ -6557,27 +8938,24 @@
         <v>0.43250922766973687</v>
       </c>
       <c r="H18" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.57692307692307676</v>
       </c>
       <c r="I18" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.57692307692307676</v>
       </c>
-      <c r="J18" s="8">
+      <c r="J18" s="13">
         <f t="shared" si="3"/>
-        <v>3.5779140136390765E-4</v>
-      </c>
-      <c r="K18" s="8">
-        <f t="shared" si="4"/>
-        <v>9.2010676191692665E-3</v>
-      </c>
+        <v>9.5588590205331718E-3</v>
+      </c>
+      <c r="K18" s="14"/>
       <c r="L18" s="18">
         <f>SUM(D18:$D$29)</f>
         <v>59900</v>
       </c>
       <c r="M18" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.23905972502145151</v>
       </c>
       <c r="N18" s="9">
@@ -6585,11 +8963,11 @@
         <v>9647787670</v>
       </c>
       <c r="O18" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.59870052080119351</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>90001</v>
       </c>
@@ -6603,7 +8981,7 @@
         <v>5086</v>
       </c>
       <c r="E19" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>92488.991545418801</v>
       </c>
       <c r="F19" s="8">
@@ -6615,27 +8993,24 @@
         <v>0.46170018237387023</v>
       </c>
       <c r="H19" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.6153846153846152</v>
       </c>
       <c r="I19" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.6153846153846152</v>
       </c>
-      <c r="J19" s="8">
+      <c r="J19" s="13">
         <f t="shared" si="3"/>
-        <v>2.9626084174809458E-4</v>
-      </c>
-      <c r="K19" s="8">
-        <f t="shared" si="4"/>
-        <v>8.7791269009170787E-3</v>
-      </c>
+        <v>9.0753877426651731E-3</v>
+      </c>
+      <c r="K19" s="14"/>
       <c r="L19" s="18">
         <f>SUM(D19:$D$29)</f>
         <v>54155</v>
       </c>
       <c r="M19" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.21613154271346757</v>
       </c>
       <c r="N19" s="9">
@@ -6643,11 +9018,11 @@
         <v>9144856712</v>
       </c>
       <c r="O19" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.56749077233026313</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>95001</v>
       </c>
@@ -6661,7 +9036,7 @@
         <v>4513</v>
       </c>
       <c r="E20" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>97537.841568801246</v>
       </c>
       <c r="F20" s="8">
@@ -6673,27 +9048,24 @@
         <v>0.48901638800589997</v>
       </c>
       <c r="H20" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.65384615384615363</v>
       </c>
       <c r="I20" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.65384615384615363</v>
       </c>
-      <c r="J20" s="8">
+      <c r="J20" s="13">
         <f t="shared" si="3"/>
-        <v>2.4600011178207179E-4</v>
-      </c>
-      <c r="K20" s="8">
-        <f t="shared" si="4"/>
-        <v>8.3158179436603925E-3</v>
-      </c>
+        <v>8.5618180554424654E-3</v>
+      </c>
+      <c r="K20" s="14"/>
       <c r="L20" s="18">
         <f>SUM(D20:$D$29)</f>
         <v>49069</v>
       </c>
       <c r="M20" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.19583341647875802</v>
       </c>
       <c r="N20" s="9">
@@ -6701,11 +9073,11 @@
         <v>8674457701</v>
       </c>
       <c r="O20" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.53829981762612977</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>100001</v>
       </c>
@@ -6719,7 +9091,7 @@
         <v>13781</v>
       </c>
       <c r="E21" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>109355.8318699659</v>
       </c>
       <c r="F21" s="8">
@@ -6731,27 +9103,24 @@
         <v>0.58253640571268872</v>
       </c>
       <c r="H21" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.69230769230769207</v>
       </c>
       <c r="I21" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.69230769230769207</v>
       </c>
-      <c r="J21" s="8">
+      <c r="J21" s="13">
         <f t="shared" si="3"/>
-        <v>2.5717864905658336E-3</v>
-      </c>
-      <c r="K21" s="8">
-        <f t="shared" si="4"/>
-        <v>2.68957549662136E-2</v>
-      </c>
+        <v>2.946754145677943E-2</v>
+      </c>
+      <c r="K21" s="14"/>
       <c r="L21" s="18">
         <f>SUM(D21:$D$29)</f>
         <v>44556</v>
       </c>
       <c r="M21" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.17782212200427036</v>
       </c>
       <c r="N21" s="9">
@@ -6759,11 +9128,11 @@
         <v>8234269422</v>
       </c>
       <c r="O21" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.51098361199410003</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>120001</v>
       </c>
@@ -6777,7 +9146,7 @@
         <v>11850</v>
       </c>
       <c r="E22" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>133432.28413502109</v>
       </c>
       <c r="F22" s="8">
@@ -6789,27 +9158,24 @@
         <v>0.68065722591720934</v>
       </c>
       <c r="H22" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.7307692307692305</v>
       </c>
       <c r="I22" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.7307692307692305</v>
       </c>
-      <c r="J22" s="8">
+      <c r="J22" s="13">
         <f t="shared" si="3"/>
-        <v>2.3202197422296979E-3</v>
-      </c>
-      <c r="K22" s="8">
-        <f t="shared" si="4"/>
-        <v>2.7549962715045426E-2</v>
-      </c>
+        <v>2.9870182457275123E-2</v>
+      </c>
+      <c r="K22" s="14"/>
       <c r="L22" s="18">
         <f>SUM(D22:$D$29)</f>
         <v>30775</v>
       </c>
       <c r="M22" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.12282242132779918</v>
       </c>
       <c r="N22" s="9">
@@ -6817,11 +9183,11 @@
         <v>6727236703</v>
       </c>
       <c r="O22" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.41746359428731122</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>150001</v>
       </c>
@@ -6835,7 +9201,7 @@
         <v>9431</v>
       </c>
       <c r="E23" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>171263.42434524442</v>
       </c>
       <c r="F23" s="8">
@@ -6847,27 +9213,24 @@
         <v>0.78088873455995289</v>
       </c>
       <c r="H23" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.76923076923076894</v>
       </c>
       <c r="I23" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.76923076923076894</v>
       </c>
-      <c r="J23" s="8">
+      <c r="J23" s="13">
         <f t="shared" si="3"/>
-        <v>1.8863036697258481E-3</v>
-      </c>
-      <c r="K23" s="8">
-        <f t="shared" si="4"/>
-        <v>2.5619213767386507E-2</v>
-      </c>
+        <v>2.7505517437112357E-2</v>
+      </c>
+      <c r="K23" s="14"/>
       <c r="L23" s="18">
         <f>SUM(D23:$D$29)</f>
         <v>18925</v>
       </c>
       <c r="M23" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7.5529303773471959E-2</v>
       </c>
       <c r="N23" s="9">
@@ -6875,11 +9238,11 @@
         <v>5146064136</v>
       </c>
       <c r="O23" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.31934277408279071</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>200001</v>
       </c>
@@ -6893,7 +9256,7 @@
         <v>5946</v>
       </c>
       <c r="E24" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>238481.54860410359</v>
       </c>
       <c r="F24" s="8">
@@ -6905,27 +9268,24 @@
         <v>0.86888446225071081</v>
       </c>
       <c r="H24" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.80769230769230738</v>
       </c>
       <c r="I24" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.80769230769230738</v>
       </c>
-      <c r="J24" s="8">
+      <c r="J24" s="13">
         <f t="shared" si="3"/>
-        <v>1.0440855603321461E-3</v>
-      </c>
-      <c r="K24" s="8">
-        <f t="shared" si="4"/>
-        <v>1.8530778104258357E-2</v>
-      </c>
+        <v>1.9574863664590506E-2</v>
+      </c>
+      <c r="K24" s="14"/>
       <c r="L24" s="18">
         <f>SUM(D24:$D$29)</f>
         <v>9494</v>
       </c>
       <c r="M24" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.7890367768842415E-2</v>
       </c>
       <c r="N24" s="9">
@@ -6933,11 +9293,11 @@
         <v>3530878781</v>
       </c>
       <c r="O24" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.21911126544004705</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>300001</v>
       </c>
@@ -6951,7 +9311,7 @@
         <v>1766</v>
       </c>
       <c r="E25" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>341667.32559456397</v>
       </c>
       <c r="F25" s="8">
@@ -6963,27 +9323,24 @@
         <v>0.90632792856170452</v>
       </c>
       <c r="H25" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.84615384615384581</v>
       </c>
       <c r="I25" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.84615384615384581</v>
       </c>
-      <c r="J25" s="8">
+      <c r="J25" s="13">
         <f t="shared" si="3"/>
-        <v>1.3195211123902828E-4</v>
-      </c>
-      <c r="K25" s="8">
-        <f t="shared" si="4"/>
-        <v>6.1239596924340597E-3</v>
-      </c>
+        <v>6.2559118036730876E-3</v>
+      </c>
+      <c r="K25" s="14"/>
       <c r="L25" s="18">
         <f>SUM(D25:$D$29)</f>
         <v>3548</v>
       </c>
       <c r="M25" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.4159998403607847E-2</v>
       </c>
       <c r="N25" s="9">
@@ -6991,11 +9348,11 @@
         <v>2112867493</v>
       </c>
       <c r="O25" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.13111553774928922</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>400001</v>
       </c>
@@ -7009,7 +9366,7 @@
         <v>738</v>
       </c>
       <c r="E26" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>443893.62466124661</v>
       </c>
       <c r="F26" s="8">
@@ -7021,27 +9378,24 @@
         <v>0.92665698251440032</v>
       </c>
       <c r="H26" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.88461538461538425</v>
       </c>
       <c r="I26" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.88461538461538425</v>
       </c>
-      <c r="J26" s="8">
-        <f>((F26-F25)*(G26-G25))/2</f>
-        <v>2.9938023700616031E-5</v>
-      </c>
-      <c r="K26" s="8">
-        <f t="shared" si="4"/>
-        <v>2.6694470946802126E-3</v>
-      </c>
+      <c r="J26" s="13">
+        <f t="shared" si="3"/>
+        <v>2.6993851183808289E-3</v>
+      </c>
+      <c r="K26" s="14"/>
       <c r="L26" s="18">
         <f>SUM(D26:$D$29)</f>
         <v>1782</v>
       </c>
       <c r="M26" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7.1119270448785745E-3</v>
       </c>
       <c r="N26" s="9">
@@ -7049,11 +9403,11 @@
         <v>1509482996</v>
       </c>
       <c r="O26" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>9.3672071438295437E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>500001</v>
       </c>
@@ -7067,7 +9421,7 @@
         <v>821</v>
       </c>
       <c r="E27" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>667638.88550548116</v>
       </c>
       <c r="F27" s="8">
@@ -7079,27 +9433,24 @@
         <v>0.96067168523277524</v>
       </c>
       <c r="H27" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.92307692307692268</v>
       </c>
       <c r="I27" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.92307692307692268</v>
       </c>
-      <c r="J27" s="8">
+      <c r="J27" s="13">
         <f t="shared" si="3"/>
-        <v>5.5726200650102783E-5</v>
-      </c>
-      <c r="K27" s="8">
-        <f t="shared" si="4"/>
-        <v>3.0362795388195795E-3</v>
-      </c>
+        <v>3.0920057394696822E-3</v>
+      </c>
+      <c r="K27" s="14"/>
       <c r="L27" s="18">
         <f>SUM(D27:$D$29)</f>
         <v>1044</v>
       </c>
       <c r="M27" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.1665835212419929E-3</v>
       </c>
       <c r="N27" s="9">
@@ -7107,11 +9458,11 @@
         <v>1181889501</v>
       </c>
       <c r="O27" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>7.334301748559964E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A28">
         <v>1000001</v>
       </c>
@@ -7125,7 +9476,7 @@
         <v>162</v>
       </c>
       <c r="E28" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>1338356.8148148148</v>
       </c>
       <c r="F28" s="8">
@@ -7137,27 +9488,24 @@
         <v>0.97412622442991403</v>
       </c>
       <c r="H28" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.96153846153846112</v>
       </c>
       <c r="I28" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.96153846153846112</v>
       </c>
-      <c r="J28" s="8">
+      <c r="J28" s="13">
         <f t="shared" si="3"/>
-        <v>4.3494409632954721E-6</v>
-      </c>
-      <c r="K28" s="8">
-        <f t="shared" si="4"/>
-        <v>6.2111153995048616E-4</v>
-      </c>
+        <v>6.2546098091378162E-4</v>
+      </c>
+      <c r="K28" s="14"/>
       <c r="L28" s="18">
         <f>SUM(D28:$D$29)</f>
         <v>223</v>
       </c>
       <c r="M28" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8.8998862570590471E-4</v>
       </c>
       <c r="N28" s="9">
@@ -7165,11 +9513,11 @@
         <v>633757976</v>
       </c>
       <c r="O28" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>3.9328314767224794E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>2000001</v>
       </c>
@@ -7183,7 +9531,7 @@
         <v>61</v>
       </c>
       <c r="E29" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>6835150.360655738</v>
       </c>
       <c r="F29" s="8">
@@ -7195,27 +9543,24 @@
         <v>1</v>
       </c>
       <c r="H29" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.99999999999999956</v>
       </c>
       <c r="I29" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.99999999999999956</v>
       </c>
-      <c r="J29" s="8">
-        <f>((F29-F28)*(G29-G28))/2</f>
-        <v>3.1494827884491916E-6</v>
-      </c>
-      <c r="K29" s="8">
-        <f t="shared" si="4"/>
-        <v>2.3715083786736389E-4</v>
-      </c>
+      <c r="J29" s="13">
+        <f t="shared" si="3"/>
+        <v>2.4030032065581306E-4</v>
+      </c>
+      <c r="K29" s="14"/>
       <c r="L29" s="18">
         <f>SUM(D29:$D$29)</f>
         <v>61</v>
       </c>
       <c r="M29" s="16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.4344980344421607E-4</v>
       </c>
       <c r="N29" s="9">
@@ -7223,11 +9568,11 @@
         <v>416944172</v>
       </c>
       <c r="O29" s="17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2.5873775570085945E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
         <v>23</v>
       </c>
@@ -7248,7 +9593,7 @@
       <c r="J30" s="8"/>
       <c r="K30" s="8"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.45">
       <c r="N31" t="s">
         <v>25</v>
       </c>
@@ -7257,7 +9602,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.45">
       <c r="B32" t="s">
         <v>14</v>
       </c>
@@ -7270,11 +9615,11 @@
         <v>250565</v>
       </c>
       <c r="I32" t="s">
-        <v>15</v>
+        <v>71</v>
       </c>
       <c r="J32" s="8">
-        <f>SUM(J5:J30)</f>
-        <v>1.5747292052045093E-2</v>
+        <f>SUM(J4:J29)</f>
+        <v>0.23410951554661666</v>
       </c>
       <c r="N32" t="s">
         <v>17</v>
@@ -7284,40 +9629,22 @@
         <v>0.10901519963532298</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.45">
       <c r="I33" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J33" s="8">
-        <f>SUM(K5:K30)</f>
-        <v>0.21471904349262805</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="I34" t="s">
-        <v>18</v>
-      </c>
-      <c r="J34" s="8">
-        <f>J32+J33</f>
-        <v>0.23046633554467313</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="I35" t="s">
-        <v>19</v>
-      </c>
-      <c r="J35" s="8">
-        <f>1-(2*J34)</f>
-        <v>0.53906732891065379</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A39" s="30" t="s">
+        <f>1-(2*J32)</f>
+        <v>0.53178096890676674</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A39" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="B39" s="30"/>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B39" s="47"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>54</v>
       </c>
@@ -7325,9 +9652,9 @@
         <v>53</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A41">
-        <f t="shared" ref="A41:A65" si="6">LOG(E4)</f>
+        <f t="shared" ref="A41:A65" si="5">LOG(E4)</f>
         <v>3.7722955399279523</v>
       </c>
       <c r="B41">
@@ -7335,110 +9662,131 @@
         <v>-0.14348627768580327</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A42">
+        <f t="shared" si="5"/>
+        <v>4.3556337674688406</v>
+      </c>
+      <c r="B42">
+        <f t="shared" ref="B42:B65" si="6" xml:space="preserve"> LOG(1-F5)</f>
+        <v>-0.16857623963281418</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A43">
+        <f t="shared" si="5"/>
+        <v>4.4411644681101272</v>
+      </c>
+      <c r="B43">
         <f t="shared" si="6"/>
-        <v>4.3556337674688406</v>
-      </c>
-      <c r="B42">
-        <f t="shared" ref="B42:B65" si="7" xml:space="preserve"> LOG(1-F5)</f>
-        <v>-0.16857623963281418</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A43">
+        <v>-0.19779924270011631</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A44">
+        <f t="shared" si="5"/>
+        <v>4.5132945165813325</v>
+      </c>
+      <c r="B44">
         <f t="shared" si="6"/>
-        <v>4.4411644681101272</v>
-      </c>
-      <c r="B43">
-        <f t="shared" si="7"/>
-        <v>-0.19779924270011631</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A44">
+        <v>-0.22435184467592204</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A45">
+        <f t="shared" si="5"/>
+        <v>4.5754529919949274</v>
+      </c>
+      <c r="B45">
         <f t="shared" si="6"/>
-        <v>4.5132945165813325</v>
-      </c>
-      <c r="B44">
-        <f t="shared" si="7"/>
-        <v>-0.22435184467592204</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A45">
+        <v>-0.25392300720752736</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A46">
+        <f t="shared" si="5"/>
+        <v>4.6293191283530346</v>
+      </c>
+      <c r="B46">
         <f t="shared" si="6"/>
-        <v>4.5754529919949274</v>
-      </c>
-      <c r="B45">
-        <f t="shared" si="7"/>
-        <v>-0.25392300720752736</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A46">
+        <v>-0.28671436190716915</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A47">
+        <f t="shared" si="5"/>
+        <v>4.6777428199808533</v>
+      </c>
+      <c r="B47">
         <f t="shared" si="6"/>
-        <v>4.6293191283530346</v>
-      </c>
-      <c r="B46">
-        <f t="shared" si="7"/>
-        <v>-0.28671436190716915</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A47">
-        <f t="shared" si="6"/>
-        <v>4.6777428199808533</v>
-      </c>
-      <c r="B47">
-        <f t="shared" si="7"/>
         <v>-0.32247658683007402</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A48">
-        <f t="shared" si="6"/>
+        <f>LOG(E11)</f>
         <v>4.7206670746380448</v>
       </c>
       <c r="B48">
         <f xml:space="preserve"> LOG(1-F11)</f>
         <v>-0.36019297580706788</v>
       </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="H48" s="25"/>
+      <c r="I48" s="25"/>
+      <c r="J48" s="25"/>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A49">
+        <f t="shared" si="5"/>
+        <v>4.7602077624282391</v>
+      </c>
+      <c r="B49">
         <f t="shared" si="6"/>
-        <v>4.7602077624282391</v>
-      </c>
-      <c r="B49">
-        <f t="shared" si="7"/>
         <v>-0.40271968167192423</v>
       </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="H49" t="s">
+        <v>60</v>
+      </c>
+      <c r="I49" t="s">
+        <v>62</v>
+      </c>
+      <c r="J49" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A50">
+        <f t="shared" si="5"/>
+        <v>4.7962260987499015</v>
+      </c>
+      <c r="B50">
         <f t="shared" si="6"/>
-        <v>4.7962260987499015</v>
-      </c>
-      <c r="B50">
-        <f t="shared" si="7"/>
         <v>-0.44523318400886275</v>
       </c>
-      <c r="F50" s="30" t="s">
+      <c r="F50" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="G50" s="30"/>
-      <c r="H50" s="30"/>
-      <c r="I50" s="30"/>
-      <c r="J50" s="30"/>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="G50" s="25"/>
+      <c r="H50">
+        <f>A29*((D29/D30)^(1/G52))</f>
+        <v>5556.4227026976187</v>
+      </c>
+      <c r="I50">
+        <f>H50/(0.01^(1/G52))</f>
+        <v>144405.83496934638</v>
+      </c>
+      <c r="J50">
+        <f>I50*F52*0.01*D32</f>
+        <v>1236582250.9790702</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A51">
+        <f t="shared" si="5"/>
+        <v>4.8294456902556702</v>
+      </c>
+      <c r="B51">
         <f t="shared" si="6"/>
-        <v>4.8294456902556702</v>
-      </c>
-      <c r="B51">
-        <f t="shared" si="7"/>
         <v>-0.48873371805696725</v>
       </c>
       <c r="F51" t="s">
@@ -7447,23 +9795,18 @@
       <c r="G51" t="s">
         <v>59</v>
       </c>
-      <c r="H51" t="s">
-        <v>60</v>
-      </c>
-      <c r="I51" t="s">
-        <v>62</v>
-      </c>
-      <c r="J51" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="J51">
+        <f>J50/C30</f>
+        <v>7.6737016090931601E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A52">
+        <f t="shared" si="5"/>
+        <v>4.8604106341962865</v>
+      </c>
+      <c r="B52">
         <f t="shared" si="6"/>
-        <v>4.8604106341962865</v>
-      </c>
-      <c r="B52">
-        <f t="shared" si="7"/>
         <v>-0.53355581515285122</v>
       </c>
       <c r="F52">
@@ -7474,160 +9817,144 @@
         <f>F52/(F52-1)</f>
         <v>1.4136378942653307</v>
       </c>
-      <c r="H52">
-        <f>A29*((D29/D30)^(1/G52))</f>
-        <v>5556.4227026976187</v>
-      </c>
-      <c r="I52">
-        <f>H52/(0.01^(1/G52))</f>
-        <v>144405.83496934638</v>
-      </c>
-      <c r="J52">
-        <f>I52*F52*0.01*D32</f>
-        <v>1236582250.9790702</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A53">
+        <f t="shared" si="5"/>
+        <v>4.8894698346845153</v>
+      </c>
+      <c r="B53">
         <f t="shared" si="6"/>
-        <v>4.8894698346845153</v>
-      </c>
-      <c r="B53">
-        <f t="shared" si="7"/>
         <v>-0.5775706703629786</v>
       </c>
-      <c r="J53">
-        <f>J52/C30</f>
-        <v>7.6737016090931601E-2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A54">
+        <f t="shared" si="5"/>
+        <v>4.9165395418021651</v>
+      </c>
+      <c r="B54">
         <f t="shared" si="6"/>
-        <v>4.9165395418021651</v>
-      </c>
-      <c r="B54">
-        <f t="shared" si="7"/>
         <v>-0.6214935843787982</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A55">
+        <f t="shared" si="5"/>
+        <v>4.9422183364895664</v>
+      </c>
+      <c r="B55">
         <f t="shared" si="6"/>
-        <v>4.9422183364895664</v>
-      </c>
-      <c r="B55">
-        <f t="shared" si="7"/>
         <v>-0.66528184659785017</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A56">
+        <f t="shared" si="5"/>
+        <v>4.9660900441380562</v>
+      </c>
+      <c r="B56">
         <f t="shared" si="6"/>
-        <v>4.9660900441380562</v>
-      </c>
-      <c r="B56">
-        <f t="shared" si="7"/>
         <v>-0.70811319938648543</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A57">
+        <f t="shared" si="5"/>
+        <v>4.9891731407867042</v>
+      </c>
+      <c r="B57">
         <f t="shared" si="6"/>
-        <v>4.9891731407867042</v>
-      </c>
-      <c r="B57">
-        <f t="shared" si="7"/>
         <v>-0.75001421149432579</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A58">
+        <f t="shared" si="5"/>
+        <v>5.0388419486119664</v>
+      </c>
+      <c r="B58">
         <f t="shared" si="6"/>
-        <v>5.0388419486119664</v>
-      </c>
-      <c r="B58">
-        <f t="shared" si="7"/>
         <v>-0.9107223451647557</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A59">
+        <f t="shared" si="5"/>
+        <v>5.1252609204754087</v>
+      </c>
+      <c r="B59">
         <f t="shared" si="6"/>
-        <v>5.1252609204754087</v>
-      </c>
-      <c r="B59">
-        <f t="shared" si="7"/>
         <v>-1.1218845185959989</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A60">
+        <f t="shared" si="5"/>
+        <v>5.2336646233210313</v>
+      </c>
+      <c r="B60">
         <f t="shared" si="6"/>
-        <v>5.2336646233210313</v>
-      </c>
-      <c r="B60">
-        <f t="shared" si="7"/>
         <v>-1.4214711793857677</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A61">
+        <f t="shared" si="5"/>
+        <v>5.3774547831689601</v>
+      </c>
+      <c r="B61">
         <f t="shared" si="6"/>
-        <v>5.3774547831689601</v>
-      </c>
-      <c r="B61">
-        <f t="shared" si="7"/>
         <v>-1.8489367956084217</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A62">
+        <f t="shared" si="5"/>
+        <v>5.5336034482383756</v>
+      </c>
+      <c r="B62">
         <f t="shared" si="6"/>
-        <v>5.5336034482383756</v>
-      </c>
-      <c r="B62">
-        <f t="shared" si="7"/>
         <v>-2.148012707067251</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A63">
+        <f t="shared" si="5"/>
+        <v>5.6472789075972889</v>
+      </c>
+      <c r="B63">
         <f t="shared" si="6"/>
-        <v>5.6472789075972889</v>
-      </c>
-      <c r="B63">
-        <f t="shared" si="7"/>
         <v>-2.380219908101866</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A64">
+        <f t="shared" si="5"/>
+        <v>5.8245416234964953</v>
+      </c>
+      <c r="B64">
         <f t="shared" si="6"/>
-        <v>5.8245416234964953</v>
-      </c>
-      <c r="B64">
-        <f t="shared" si="7"/>
         <v>-3.0506155437199589</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A65">
+        <f t="shared" si="5"/>
+        <v>6.1265719146621898</v>
+      </c>
+      <c r="B65">
         <f t="shared" si="6"/>
-        <v>6.1265719146621898</v>
-      </c>
-      <c r="B65">
-        <f t="shared" si="7"/>
         <v>-3.6135905717572601</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B69" s="30" t="s">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B69" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="C69" s="30"/>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C69" s="47"/>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B70" t="s">
         <v>54</v>
       </c>
@@ -7635,7 +9962,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B71">
         <f>LOG(A5)</f>
         <v>4.3010517098452263</v>
@@ -7645,237 +9972,237 @@
         <v>-0.16857623963281418</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B72">
-        <f t="shared" ref="B72:B94" si="8">LOG(A6)</f>
+        <f t="shared" ref="B72:B94" si="7">LOG(A6)</f>
         <v>4.3979573801038878</v>
       </c>
       <c r="C72">
-        <f t="shared" ref="C72:C94" si="9">LOG(1-F6)</f>
+        <f t="shared" ref="C72:C94" si="8">LOG(1-F6)</f>
         <v>-0.19779924270011631</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B73">
+        <f t="shared" si="7"/>
+        <v>4.4771357309611233</v>
+      </c>
+      <c r="C73">
         <f t="shared" si="8"/>
-        <v>4.4771357309611233</v>
-      </c>
-      <c r="C73">
-        <f t="shared" si="9"/>
         <v>-0.22435184467592204</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B74">
+        <f t="shared" si="7"/>
+        <v>4.5440804525867851</v>
+      </c>
+      <c r="C74">
         <f t="shared" si="8"/>
-        <v>4.5440804525867851</v>
-      </c>
-      <c r="C74">
-        <f t="shared" si="9"/>
         <v>-0.25392300720752736</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B75">
+        <f t="shared" si="7"/>
+        <v>4.6020708485542956</v>
+      </c>
+      <c r="C75">
         <f t="shared" si="8"/>
-        <v>4.6020708485542956</v>
-      </c>
-      <c r="C75">
-        <f t="shared" si="9"/>
         <v>-0.28671436190716915</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B76">
+        <f t="shared" si="7"/>
+        <v>4.653222164656599</v>
+      </c>
+      <c r="C76">
         <f t="shared" si="8"/>
-        <v>4.653222164656599</v>
-      </c>
-      <c r="C76">
-        <f t="shared" si="9"/>
         <v>-0.32247658683007402</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B77">
+        <f t="shared" si="7"/>
+        <v>4.6989786901387989</v>
+      </c>
+      <c r="C77">
         <f t="shared" si="8"/>
-        <v>4.6989786901387989</v>
-      </c>
-      <c r="C77">
-        <f t="shared" si="9"/>
         <v>-0.36019297580706788</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B78">
+        <f t="shared" si="7"/>
+        <v>4.7403705856857679</v>
+      </c>
+      <c r="C78">
         <f t="shared" si="8"/>
-        <v>4.7403705856857679</v>
-      </c>
-      <c r="C78">
-        <f t="shared" si="9"/>
         <v>-0.40271968167192423</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B79">
+        <f t="shared" si="7"/>
+        <v>4.7781584885646904</v>
+      </c>
+      <c r="C79">
         <f t="shared" si="8"/>
-        <v>4.7781584885646904</v>
-      </c>
-      <c r="C79">
-        <f t="shared" si="9"/>
         <v>-0.44523318400886275</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B80">
+        <f t="shared" si="7"/>
+        <v>4.8129200380450277</v>
+      </c>
+      <c r="C80">
         <f t="shared" si="8"/>
-        <v>4.8129200380450277</v>
-      </c>
-      <c r="C80">
-        <f t="shared" si="9"/>
         <v>-0.48873371805696725</v>
       </c>
     </row>
-    <row r="81" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B81">
+        <f t="shared" si="7"/>
+        <v>4.8451042441768255</v>
+      </c>
+      <c r="C81">
         <f t="shared" si="8"/>
-        <v>4.8451042441768255</v>
-      </c>
-      <c r="C81">
-        <f t="shared" si="9"/>
         <v>-0.53355581515285122</v>
       </c>
     </row>
-    <row r="82" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B82">
+        <f t="shared" si="7"/>
+        <v>4.8750670539461884</v>
+      </c>
+      <c r="C82">
         <f t="shared" si="8"/>
-        <v>4.8750670539461884</v>
-      </c>
-      <c r="C82">
-        <f t="shared" si="9"/>
         <v>-0.5775706703629786</v>
       </c>
     </row>
-    <row r="83" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B83">
+        <f t="shared" si="7"/>
+        <v>4.9030954156390383</v>
+      </c>
+      <c r="C83">
         <f t="shared" si="8"/>
-        <v>4.9030954156390383</v>
-      </c>
-      <c r="C83">
-        <f t="shared" si="9"/>
         <v>-0.6214935843787982</v>
       </c>
     </row>
-    <row r="84" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B84">
+        <f t="shared" si="7"/>
+        <v>4.9294240350310838</v>
+      </c>
+      <c r="C84">
         <f t="shared" si="8"/>
-        <v>4.9294240350310838</v>
-      </c>
-      <c r="C84">
-        <f t="shared" si="9"/>
         <v>-0.66528184659785017</v>
       </c>
     </row>
-    <row r="85" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B85">
+        <f t="shared" si="7"/>
+        <v>4.9542473349067597</v>
+      </c>
+      <c r="C85">
         <f t="shared" si="8"/>
-        <v>4.9542473349067597</v>
-      </c>
-      <c r="C85">
-        <f t="shared" si="9"/>
         <v>-0.70811319938648543</v>
       </c>
     </row>
-    <row r="86" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B86">
+        <f t="shared" si="7"/>
+        <v>4.9777281767856492</v>
+      </c>
+      <c r="C86">
         <f t="shared" si="8"/>
-        <v>4.9777281767856492</v>
-      </c>
-      <c r="C86">
-        <f t="shared" si="9"/>
         <v>-0.75001421149432579</v>
       </c>
     </row>
-    <row r="87" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B87">
+        <f t="shared" si="7"/>
+        <v>5.0000043429231047</v>
+      </c>
+      <c r="C87">
         <f t="shared" si="8"/>
-        <v>5.0000043429231047</v>
-      </c>
-      <c r="C87">
-        <f t="shared" si="9"/>
         <v>-0.9107223451647557</v>
       </c>
     </row>
-    <row r="88" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B88">
+        <f t="shared" si="7"/>
+        <v>5.0791848651532279</v>
+      </c>
+      <c r="C88">
         <f t="shared" si="8"/>
-        <v>5.0791848651532279</v>
-      </c>
-      <c r="C88">
-        <f t="shared" si="9"/>
         <v>-1.1218845185959989</v>
       </c>
     </row>
-    <row r="89" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B89">
+        <f t="shared" si="7"/>
+        <v>5.176094154342576</v>
+      </c>
+      <c r="C89">
         <f t="shared" si="8"/>
-        <v>5.176094154342576</v>
-      </c>
-      <c r="C89">
-        <f t="shared" si="9"/>
         <v>-1.4214711793857677</v>
       </c>
     </row>
-    <row r="90" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B90">
+        <f t="shared" si="7"/>
+        <v>5.3010321671309617</v>
+      </c>
+      <c r="C90">
         <f t="shared" si="8"/>
-        <v>5.3010321671309617</v>
-      </c>
-      <c r="C90">
-        <f t="shared" si="9"/>
         <v>-1.8489367956084217</v>
       </c>
     </row>
-    <row r="91" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="91" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B91">
+        <f t="shared" si="7"/>
+        <v>5.4771227023655227</v>
+      </c>
+      <c r="C91">
         <f t="shared" si="8"/>
-        <v>5.4771227023655227</v>
-      </c>
-      <c r="C91">
-        <f t="shared" si="9"/>
         <v>-2.148012707067251</v>
       </c>
     </row>
-    <row r="92" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B92">
+        <f t="shared" si="7"/>
+        <v>5.6020610770628103</v>
+      </c>
+      <c r="C92">
         <f t="shared" si="8"/>
-        <v>5.6020610770628103</v>
-      </c>
-      <c r="C92">
-        <f t="shared" si="9"/>
         <v>-2.380219908101866</v>
       </c>
     </row>
-    <row r="93" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="93" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B93">
+        <f t="shared" si="7"/>
+        <v>5.6989708729241144</v>
+      </c>
+      <c r="C93">
         <f t="shared" si="8"/>
-        <v>5.6989708729241144</v>
-      </c>
-      <c r="C93">
-        <f t="shared" si="9"/>
         <v>-3.0506155437199589</v>
       </c>
     </row>
-    <row r="94" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B94">
+        <f t="shared" si="7"/>
+        <v>6.0000004342942646</v>
+      </c>
+      <c r="C94">
         <f t="shared" si="8"/>
-        <v>6.0000004342942646</v>
-      </c>
-      <c r="C94">
-        <f t="shared" si="9"/>
         <v>-3.6135905717572601</v>
       </c>
     </row>
-    <row r="95" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B95">
         <f>LOG(A29)</f>
         <v>6.3010302128111677</v>
@@ -7892,31 +10219,31 @@
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="L1:Q1"/>
     <mergeCell ref="B69:C69"/>
-    <mergeCell ref="F50:J50"/>
+    <mergeCell ref="J2:K2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C100B010-F934-41A3-88FF-308B180726C1}">
   <dimension ref="A1:I49"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="24" t="s">
         <v>29</v>
       </c>
       <c r="B3" s="24"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>30</v>
       </c>
@@ -7924,7 +10251,7 @@
         <v>0.92313721029489104</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -7932,7 +10259,7 @@
         <v>0.85218230903103387</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>31</v>
       </c>
@@ -7940,7 +10267,7 @@
         <v>0.84575545290194842</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>32</v>
       </c>
@@ -7948,7 +10275,7 @@
         <v>0.37116301518184985</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A8" s="22" t="s">
         <v>33</v>
       </c>
@@ -7956,12 +10283,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A10" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" s="23"/>
       <c r="B11" s="23" t="s">
         <v>39</v>
@@ -7979,7 +10306,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>35</v>
       </c>
@@ -7999,7 +10326,7 @@
         <v>5.0116133691544345E-11</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -8013,7 +10340,7 @@
         <v>0.13776198383888211</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A14" s="22" t="s">
         <v>37</v>
       </c>
@@ -8027,8 +10354,8 @@
       <c r="E14" s="22"/>
       <c r="F14" s="22"/>
     </row>
-    <row r="15" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16" s="23"/>
       <c r="B16" s="23" t="s">
         <v>44</v>
@@ -8055,7 +10382,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -8084,7 +10411,7 @@
         <v>9.2977414194617349</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A18" s="22" t="s">
         <v>51</v>
       </c>
@@ -8113,13 +10440,13 @@
         <v>-1.4404650823910896</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A24" s="23" t="s">
         <v>56</v>
       </c>
@@ -8130,7 +10457,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>1</v>
       </c>
@@ -8141,7 +10468,7 @@
         <v>-1.2510329258531978</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>2</v>
       </c>
@@ -8152,7 +10479,7 @@
         <v>-0.25183327226711361</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>3</v>
       </c>
@@ -8163,7 +10490,7 @@
         <v>-0.1308720351459072</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A28">
         <v>4</v>
       </c>
@@ -8174,7 +10501,7 @@
         <v>-3.0770740413433612E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>5</v>
       </c>
@@ -8185,7 +10512,7 @@
         <v>4.8802805694943885E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>6</v>
       </c>
@@ -8196,7 +10523,7 @@
         <v>0.11059555588603043</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>7</v>
       </c>
@@ -8207,7 +10534,7 @@
         <v>0.15986099096964451</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>8</v>
       </c>
@@ -8218,7 +10545,7 @@
         <v>0.19751574385181736</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A33">
         <v>9</v>
       </c>
@@ -8229,7 +10556,7 @@
         <v>0.2244189398558441</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A34">
         <v>10</v>
       </c>
@@ -8240,7 +10567,7 @@
         <v>0.24515040608299948</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>11</v>
       </c>
@@ -8251,7 +10578,7 @@
         <v>0.2599804956853487</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>12</v>
       </c>
@@ -8262,7 +10589,7 @@
         <v>0.26953006330556528</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A37">
         <v>13</v>
       </c>
@@ -8273,7 +10600,7 @@
         <v>0.27654055821052248</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A38">
         <v>14</v>
       </c>
@@ -8284,7 +10611,7 @@
         <v>0.28014962236287089</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A39">
         <v>15</v>
       </c>
@@ -8295,7 +10622,7 @@
         <v>0.28145102081733919</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A40">
         <v>16</v>
       </c>
@@ -8306,7 +10633,7 @@
         <v>0.28053624591606019</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A41">
         <v>17</v>
       </c>
@@ -8317,7 +10644,7 @@
         <v>0.27916708150013259</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A42">
         <v>18</v>
       </c>
@@ -8328,7 +10655,7 @@
         <v>0.20567292022063155</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A43">
         <v>19</v>
       </c>
@@ -8339,7 +10666,7 @@
         <v>0.14625471158649428</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A44">
         <v>20</v>
       </c>
@@ -8350,7 +10677,7 @@
         <v>3.7015231673575899E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A45">
         <v>21</v>
       </c>
@@ -8361,7 +10688,7 @@
         <v>-0.13796775852787468</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A46">
         <v>22</v>
       </c>
@@ -8372,7 +10699,7 @@
         <v>-0.16286061707038124</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A47">
         <v>23</v>
       </c>
@@ -8383,7 +10710,7 @@
         <v>-0.1954639055461751</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A48">
         <v>24</v>
       </c>
@@ -8394,7 +10721,7 @@
         <v>-0.55460210843580215</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:3" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A49" s="22">
         <v>25</v>
       </c>

--- a/exercices/exercices_gini_afc2022.xlsx
+++ b/exercices/exercices_gini_afc2022.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celal\Documents\GitHub\les-mesures-de-l-conomie\exercices\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gueney\Documents\GitHub\les-mesures-de-l-conomie\exercices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E043B6D5-4988-4CD4-9593-01CA2A6C0DE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F616831B-DB21-4BDD-B3CC-3A76C685CFC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="315" yWindow="510" windowWidth="28485" windowHeight="14970" activeTab="3" xr2:uid="{0A857FEE-5B62-478B-B26F-1439DD0DBBE3}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{0A857FEE-5B62-478B-B26F-1439DD0DBBE3}"/>
   </bookViews>
   <sheets>
     <sheet name="source" sheetId="2" r:id="rId1"/>
@@ -23,6 +23,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -576,6 +587,9 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -591,6 +605,12 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -602,15 +622,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -4722,16 +4733,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>84137</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>896937</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>785812</xdr:colOff>
-      <xdr:row>53</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>481012</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4801,9 +4812,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office 2013 – 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4841,7 +4852,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -4947,7 +4958,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -5089,7 +5100,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -5098,14 +5109,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ACE9D6E-E496-4D38-B54C-DA7BD6147D63}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="19" t="s">
         <v>27</v>
       </c>
@@ -5121,41 +5132,41 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CB256E1-B0FC-48AE-8D60-3C9A253EE1A6}">
   <dimension ref="A1:Q35"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="25.33203125" customWidth="1"/>
-    <col min="5" max="5" width="11.19921875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="29.59765625" customWidth="1"/>
-    <col min="7" max="7" width="39.33203125" customWidth="1"/>
-    <col min="8" max="8" width="11.19921875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.59765625" customWidth="1"/>
-    <col min="10" max="10" width="20.265625" customWidth="1"/>
-    <col min="12" max="12" width="67.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="27.265625" customWidth="1"/>
+    <col min="3" max="3" width="25.36328125" customWidth="1"/>
+    <col min="5" max="5" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="29.6328125" customWidth="1"/>
+    <col min="7" max="7" width="39.36328125" customWidth="1"/>
+    <col min="8" max="8" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.6328125" customWidth="1"/>
+    <col min="10" max="10" width="20.26953125" customWidth="1"/>
+    <col min="12" max="12" width="67.36328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="27.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="F1" s="38" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="F1" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="39" t="s">
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="K1" s="40"/>
-      <c r="L1" s="41" t="s">
+      <c r="K1" s="41"/>
+      <c r="L1" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="M1" s="42"/>
-      <c r="N1" s="42"/>
-      <c r="O1" s="42"/>
-      <c r="P1" s="42"/>
-      <c r="Q1" s="42"/>
-    </row>
-    <row r="2" spans="1:17" ht="171" x14ac:dyDescent="0.45">
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="43"/>
+      <c r="Q1" s="43"/>
+    </row>
+    <row r="2" spans="1:17" ht="174" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -5202,7 +5213,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -5227,7 +5238,7 @@
       <c r="N3" s="5"/>
       <c r="O3" s="2"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>0</v>
       </c>
@@ -5282,7 +5293,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>20001</v>
       </c>
@@ -5340,7 +5351,7 @@
         <v>0.98089585309539973</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>25001</v>
       </c>
@@ -5398,7 +5409,7 @@
         <v>0.96840446418151849</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>30001</v>
       </c>
@@ -5456,7 +5467,7 @@
         <v>0.95248291794930184</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>35001</v>
       </c>
@@ -5514,7 +5525,7 @@
         <v>0.93410636653431389</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>40001</v>
       </c>
@@ -5572,7 +5583,7 @@
         <v>0.91004984352954654</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>45001</v>
       </c>
@@ -5630,7 +5641,7 @@
         <v>0.87844468918359042</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>50001</v>
       </c>
@@ -5688,7 +5699,7 @@
         <v>0.84037767239906014</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>55001</v>
       </c>
@@ -5746,7 +5757,7 @@
         <v>0.79864797463644943</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>60001</v>
       </c>
@@ -5804,7 +5815,7 @@
         <v>0.75568089851946385</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>65001</v>
       </c>
@@ -5862,7 +5873,7 @@
         <v>0.71348064754011409</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>70001</v>
       </c>
@@ -5920,7 +5931,7 @@
         <v>0.67264165900827766</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>75001</v>
       </c>
@@ -5978,7 +5989,7 @@
         <v>0.63369903651969928</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>80001</v>
       </c>
@@ -6036,7 +6047,7 @@
         <v>0.59648366659516738</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>85001</v>
       </c>
@@ -6094,7 +6105,7 @@
         <v>0.56095505372039822</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>90001</v>
       </c>
@@ -6152,7 +6163,7 @@
         <v>0.52708213649413505</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>95001</v>
       </c>
@@ -6210,7 +6221,7 @@
         <v>0.49450853049247107</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>100001</v>
       </c>
@@ -6268,7 +6279,7 @@
         <v>0.46352688881679166</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>120001</v>
       </c>
@@ -6326,7 +6337,7 @@
         <v>0.35762880548821618</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>150001</v>
       </c>
@@ -6384,7 +6395,7 @@
         <v>0.25279345891274818</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>200001</v>
       </c>
@@ -6442,7 +6453,7 @@
         <v>0.16215472373056269</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>300001</v>
       </c>
@@ -6500,7 +6511,7 @@
         <v>9.4056873898511625E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>400001</v>
       </c>
@@ -6558,7 +6569,7 @@
         <v>6.6707682992984421E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>500001</v>
       </c>
@@ -6616,7 +6627,7 @@
         <v>5.2219942358268129E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>1000001</v>
       </c>
@@ -6674,7 +6685,7 @@
         <v>2.7334407515904005E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>2000001</v>
       </c>
@@ -6732,7 +6743,7 @@
         <v>1.6073385443575998E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B30" t="s">
         <v>23</v>
       </c>
@@ -6753,7 +6764,7 @@
       <c r="J30" s="8"/>
       <c r="K30" s="8"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
       <c r="N31" t="s">
         <v>25</v>
       </c>
@@ -6762,7 +6773,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B32" t="s">
         <v>14</v>
       </c>
@@ -6789,7 +6800,7 @@
         <v>9.4291132404414987E-2</v>
       </c>
     </row>
-    <row r="33" spans="9:10" x14ac:dyDescent="0.45">
+    <row r="33" spans="9:10" x14ac:dyDescent="0.35">
       <c r="I33" t="s">
         <v>16</v>
       </c>
@@ -6798,7 +6809,7 @@
         <v>0.25720121848286576</v>
       </c>
     </row>
-    <row r="34" spans="9:10" x14ac:dyDescent="0.45">
+    <row r="34" spans="9:10" x14ac:dyDescent="0.35">
       <c r="I34" t="s">
         <v>18</v>
       </c>
@@ -6807,7 +6818,7 @@
         <v>0.27657368234858093</v>
       </c>
     </row>
-    <row r="35" spans="9:10" x14ac:dyDescent="0.45">
+    <row r="35" spans="9:10" x14ac:dyDescent="0.35">
       <c r="I35" t="s">
         <v>19</v>
       </c>
@@ -6829,14 +6840,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{071C79C0-D56A-4054-A52D-D30424BA6045}">
   <dimension ref="A1:X32"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="14.1328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.6640625" customWidth="1"/>
-    <col min="9" max="9" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.6328125" customWidth="1"/>
+    <col min="9" max="9" width="12.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="57.4" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:24" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6852,13 +6863,13 @@
       <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="43" t="s">
+      <c r="G1" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="H1" s="44"/>
-      <c r="I1" s="45"/>
-    </row>
-    <row r="2" spans="1:24" ht="43.15" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="H1" s="47"/>
+      <c r="I1" s="48"/>
+    </row>
+    <row r="2" spans="1:24" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -6876,17 +6887,17 @@
       <c r="K2" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="R2" s="46" t="s">
+      <c r="R2" s="49" t="s">
         <v>68</v>
       </c>
-      <c r="S2" s="46"/>
-      <c r="T2" s="46"/>
-      <c r="U2" s="46"/>
-      <c r="V2" s="46"/>
-      <c r="W2" s="46"/>
-      <c r="X2" s="46"/>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="S2" s="49"/>
+      <c r="T2" s="49"/>
+      <c r="U2" s="49"/>
+      <c r="V2" s="49"/>
+      <c r="W2" s="49"/>
+      <c r="X2" s="49"/>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>0</v>
       </c>
@@ -6923,15 +6934,15 @@
         <f>I3</f>
         <v>-4.2088632053942511E-2</v>
       </c>
-      <c r="R3" s="46"/>
-      <c r="S3" s="46"/>
-      <c r="T3" s="46"/>
-      <c r="U3" s="46"/>
-      <c r="V3" s="46"/>
-      <c r="W3" s="46"/>
-      <c r="X3" s="46"/>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="R3" s="49"/>
+      <c r="S3" s="49"/>
+      <c r="T3" s="49"/>
+      <c r="U3" s="49"/>
+      <c r="V3" s="49"/>
+      <c r="W3" s="49"/>
+      <c r="X3" s="49"/>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>20001</v>
       </c>
@@ -6968,15 +6979,15 @@
         <f>SUM($I$3:I4)</f>
         <v>-5.6081521688101613E-2</v>
       </c>
-      <c r="R4" s="46"/>
-      <c r="S4" s="46"/>
-      <c r="T4" s="46"/>
-      <c r="U4" s="46"/>
-      <c r="V4" s="46"/>
-      <c r="W4" s="46"/>
-      <c r="X4" s="46"/>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="R4" s="49"/>
+      <c r="S4" s="49"/>
+      <c r="T4" s="49"/>
+      <c r="U4" s="49"/>
+      <c r="V4" s="49"/>
+      <c r="W4" s="49"/>
+      <c r="X4" s="49"/>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>25001</v>
       </c>
@@ -7013,15 +7024,15 @@
         <f>SUM($I$3:I5)</f>
         <v>-7.0757626964163836E-2</v>
       </c>
-      <c r="R5" s="46"/>
-      <c r="S5" s="46"/>
-      <c r="T5" s="46"/>
-      <c r="U5" s="46"/>
-      <c r="V5" s="46"/>
-      <c r="W5" s="46"/>
-      <c r="X5" s="46"/>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="R5" s="49"/>
+      <c r="S5" s="49"/>
+      <c r="T5" s="49"/>
+      <c r="U5" s="49"/>
+      <c r="V5" s="49"/>
+      <c r="W5" s="49"/>
+      <c r="X5" s="49"/>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>30001</v>
       </c>
@@ -7058,15 +7069,15 @@
         <f>SUM($I$3:I6)</f>
         <v>-8.460819555237914E-2</v>
       </c>
-      <c r="R6" s="46"/>
-      <c r="S6" s="46"/>
-      <c r="T6" s="46"/>
-      <c r="U6" s="46"/>
-      <c r="V6" s="46"/>
-      <c r="W6" s="46"/>
-      <c r="X6" s="46"/>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="R6" s="49"/>
+      <c r="S6" s="49"/>
+      <c r="T6" s="49"/>
+      <c r="U6" s="49"/>
+      <c r="V6" s="49"/>
+      <c r="W6" s="49"/>
+      <c r="X6" s="49"/>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>35001</v>
       </c>
@@ -7103,15 +7114,15 @@
         <f>SUM($I$3:I7)</f>
         <v>-9.9297393306532547E-2</v>
       </c>
-      <c r="R7" s="46"/>
-      <c r="S7" s="46"/>
-      <c r="T7" s="46"/>
-      <c r="U7" s="46"/>
-      <c r="V7" s="46"/>
-      <c r="W7" s="46"/>
-      <c r="X7" s="46"/>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="R7" s="49"/>
+      <c r="S7" s="49"/>
+      <c r="T7" s="49"/>
+      <c r="U7" s="49"/>
+      <c r="V7" s="49"/>
+      <c r="W7" s="49"/>
+      <c r="X7" s="49"/>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>40001</v>
       </c>
@@ -7148,15 +7159,15 @@
         <f>SUM($I$3:I8)</f>
         <v>-0.11467075089766376</v>
       </c>
-      <c r="R8" s="46"/>
-      <c r="S8" s="46"/>
-      <c r="T8" s="46"/>
-      <c r="U8" s="46"/>
-      <c r="V8" s="46"/>
-      <c r="W8" s="46"/>
-      <c r="X8" s="46"/>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="R8" s="49"/>
+      <c r="S8" s="49"/>
+      <c r="T8" s="49"/>
+      <c r="U8" s="49"/>
+      <c r="V8" s="49"/>
+      <c r="W8" s="49"/>
+      <c r="X8" s="49"/>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>45001</v>
       </c>
@@ -7193,15 +7204,15 @@
         <f>SUM($I$3:I9)</f>
         <v>-0.12897446806858248</v>
       </c>
-      <c r="R9" s="46"/>
-      <c r="S9" s="46"/>
-      <c r="T9" s="46"/>
-      <c r="U9" s="46"/>
-      <c r="V9" s="46"/>
-      <c r="W9" s="46"/>
-      <c r="X9" s="46"/>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="R9" s="49"/>
+      <c r="S9" s="49"/>
+      <c r="T9" s="49"/>
+      <c r="U9" s="49"/>
+      <c r="V9" s="49"/>
+      <c r="W9" s="49"/>
+      <c r="X9" s="49"/>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>50001</v>
       </c>
@@ -7238,15 +7249,15 @@
         <f>SUM($I$3:I10)</f>
         <v>-0.14052067323656281</v>
       </c>
-      <c r="R10" s="46"/>
-      <c r="S10" s="46"/>
-      <c r="T10" s="46"/>
-      <c r="U10" s="46"/>
-      <c r="V10" s="46"/>
-      <c r="W10" s="46"/>
-      <c r="X10" s="46"/>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="R10" s="49"/>
+      <c r="S10" s="49"/>
+      <c r="T10" s="49"/>
+      <c r="U10" s="49"/>
+      <c r="V10" s="49"/>
+      <c r="W10" s="49"/>
+      <c r="X10" s="49"/>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>55001</v>
       </c>
@@ -7283,15 +7294,15 @@
         <f>SUM($I$3:I11)</f>
         <v>-0.14850495731840962</v>
       </c>
-      <c r="R11" s="46"/>
-      <c r="S11" s="46"/>
-      <c r="T11" s="46"/>
-      <c r="U11" s="46"/>
-      <c r="V11" s="46"/>
-      <c r="W11" s="46"/>
-      <c r="X11" s="46"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="R11" s="49"/>
+      <c r="S11" s="49"/>
+      <c r="T11" s="49"/>
+      <c r="U11" s="49"/>
+      <c r="V11" s="49"/>
+      <c r="W11" s="49"/>
+      <c r="X11" s="49"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>60001</v>
       </c>
@@ -7328,15 +7339,15 @@
         <f>SUM($I$3:I12)</f>
         <v>-0.15284397652921164</v>
       </c>
-      <c r="R12" s="46"/>
-      <c r="S12" s="46"/>
-      <c r="T12" s="46"/>
-      <c r="U12" s="46"/>
-      <c r="V12" s="46"/>
-      <c r="W12" s="46"/>
-      <c r="X12" s="46"/>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="R12" s="49"/>
+      <c r="S12" s="49"/>
+      <c r="T12" s="49"/>
+      <c r="U12" s="49"/>
+      <c r="V12" s="49"/>
+      <c r="W12" s="49"/>
+      <c r="X12" s="49"/>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>65001</v>
       </c>
@@ -7373,15 +7384,15 @@
         <f>SUM($I$3:I13)</f>
         <v>-0.15390350320953805</v>
       </c>
-      <c r="R13" s="46"/>
-      <c r="S13" s="46"/>
-      <c r="T13" s="46"/>
-      <c r="U13" s="46"/>
-      <c r="V13" s="46"/>
-      <c r="W13" s="46"/>
-      <c r="X13" s="46"/>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="R13" s="49"/>
+      <c r="S13" s="49"/>
+      <c r="T13" s="49"/>
+      <c r="U13" s="49"/>
+      <c r="V13" s="49"/>
+      <c r="W13" s="49"/>
+      <c r="X13" s="49"/>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>70001</v>
       </c>
@@ -7418,15 +7429,15 @@
         <f>SUM($I$3:I14)</f>
         <v>-0.15212988745864936</v>
       </c>
-      <c r="R14" s="46"/>
-      <c r="S14" s="46"/>
-      <c r="T14" s="46"/>
-      <c r="U14" s="46"/>
-      <c r="V14" s="46"/>
-      <c r="W14" s="46"/>
-      <c r="X14" s="46"/>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="R14" s="49"/>
+      <c r="S14" s="49"/>
+      <c r="T14" s="49"/>
+      <c r="U14" s="49"/>
+      <c r="V14" s="49"/>
+      <c r="W14" s="49"/>
+      <c r="X14" s="49"/>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>75001</v>
       </c>
@@ -7463,15 +7474,15 @@
         <f>SUM($I$3:I15)</f>
         <v>-0.14795235654122926</v>
       </c>
-      <c r="R15" s="46"/>
-      <c r="S15" s="46"/>
-      <c r="T15" s="46"/>
-      <c r="U15" s="46"/>
-      <c r="V15" s="46"/>
-      <c r="W15" s="46"/>
-      <c r="X15" s="46"/>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="R15" s="49"/>
+      <c r="S15" s="49"/>
+      <c r="T15" s="49"/>
+      <c r="U15" s="49"/>
+      <c r="V15" s="49"/>
+      <c r="W15" s="49"/>
+      <c r="X15" s="49"/>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>80001</v>
       </c>
@@ -7508,15 +7519,15 @@
         <f>SUM($I$3:I16)</f>
         <v>-0.14174405137397261</v>
       </c>
-      <c r="R16" s="46"/>
-      <c r="S16" s="46"/>
-      <c r="T16" s="46"/>
-      <c r="U16" s="46"/>
-      <c r="V16" s="46"/>
-      <c r="W16" s="46"/>
-      <c r="X16" s="46"/>
-    </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="R16" s="49"/>
+      <c r="S16" s="49"/>
+      <c r="T16" s="49"/>
+      <c r="U16" s="49"/>
+      <c r="V16" s="49"/>
+      <c r="W16" s="49"/>
+      <c r="X16" s="49"/>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>85001</v>
       </c>
@@ -7553,15 +7564,15 @@
         <f>SUM($I$3:I17)</f>
         <v>-0.13382981631130622</v>
       </c>
-      <c r="R17" s="46"/>
-      <c r="S17" s="46"/>
-      <c r="T17" s="46"/>
-      <c r="U17" s="46"/>
-      <c r="V17" s="46"/>
-      <c r="W17" s="46"/>
-      <c r="X17" s="46"/>
-    </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="R17" s="49"/>
+      <c r="S17" s="49"/>
+      <c r="T17" s="49"/>
+      <c r="U17" s="49"/>
+      <c r="V17" s="49"/>
+      <c r="W17" s="49"/>
+      <c r="X17" s="49"/>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>90001</v>
       </c>
@@ -7598,15 +7609,15 @@
         <f>SUM($I$3:I18)</f>
         <v>-0.12441158187800709</v>
       </c>
-      <c r="R18" s="46"/>
-      <c r="S18" s="46"/>
-      <c r="T18" s="46"/>
-      <c r="U18" s="46"/>
-      <c r="V18" s="46"/>
-      <c r="W18" s="46"/>
-      <c r="X18" s="46"/>
-    </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="R18" s="49"/>
+      <c r="S18" s="49"/>
+      <c r="T18" s="49"/>
+      <c r="U18" s="49"/>
+      <c r="V18" s="49"/>
+      <c r="W18" s="49"/>
+      <c r="X18" s="49"/>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>95001</v>
       </c>
@@ -7643,15 +7654,15 @@
         <f>SUM($I$3:I19)</f>
         <v>-0.11382131937629252</v>
       </c>
-      <c r="R19" s="46"/>
-      <c r="S19" s="46"/>
-      <c r="T19" s="46"/>
-      <c r="U19" s="46"/>
-      <c r="V19" s="46"/>
-      <c r="W19" s="46"/>
-      <c r="X19" s="46"/>
-    </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="R19" s="49"/>
+      <c r="S19" s="49"/>
+      <c r="T19" s="49"/>
+      <c r="U19" s="49"/>
+      <c r="V19" s="49"/>
+      <c r="W19" s="49"/>
+      <c r="X19" s="49"/>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>100001</v>
       </c>
@@ -7689,7 +7700,7 @@
         <v>-6.5562941053542489E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>120001</v>
       </c>
@@ -7727,7 +7738,7 @@
         <v>2.9681188067023218E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>150001</v>
       </c>
@@ -7765,7 +7776,7 @@
         <v>8.4618344218928748E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>200001</v>
       </c>
@@ -7803,7 +7814,7 @@
         <v>0.16858720120654686</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>300001</v>
       </c>
@@ -7841,7 +7852,7 @@
         <v>0.21222818257633932</v>
       </c>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>400001</v>
       </c>
@@ -7879,7 +7890,7 @@
         <v>0.23912618337416464</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>500001</v>
       </c>
@@ -7917,7 +7928,7 @@
         <v>0.2952196130953868</v>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>1000001</v>
       </c>
@@ -7955,7 +7966,7 @@
         <v>0.32856457637534486</v>
       </c>
     </row>
-    <row r="28" spans="1:24" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>2000001</v>
       </c>
@@ -7993,7 +8004,7 @@
         <v>0.39660361967801816</v>
       </c>
     </row>
-    <row r="29" spans="1:24" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B29" t="s">
         <v>23</v>
       </c>
@@ -8008,12 +8019,12 @@
         <v>69267.251689968223</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.35">
       <c r="I30" s="26" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="31" spans="1:24" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="I31" s="27">
@@ -8021,7 +8032,7 @@
         <v>0.39660361967801816</v>
       </c>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.35">
       <c r="I32">
         <f>LN(D29)</f>
         <v>15.383806216267152</v>
@@ -8040,39 +8051,40 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{988134C0-BA93-4AA9-AB60-815506C21888}">
   <dimension ref="A1:Q95"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.59765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="58.59765625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" customWidth="1"/>
-    <col min="5" max="5" width="11.19921875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.3984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.265625" customWidth="1"/>
-    <col min="12" max="12" width="67.3984375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.06640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="58.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.36328125" customWidth="1"/>
+    <col min="5" max="5" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.36328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.26953125" customWidth="1"/>
+    <col min="12" max="12" width="20.6328125" customWidth="1"/>
+    <col min="14" max="14" width="13.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="F1" s="38" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="F1" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="39" t="s">
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="K1" s="40"/>
-      <c r="L1" s="41" t="s">
+      <c r="K1" s="41"/>
+      <c r="L1" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="M1" s="42"/>
-      <c r="N1" s="42"/>
-      <c r="O1" s="42"/>
-      <c r="P1" s="42"/>
-      <c r="Q1" s="42"/>
-    </row>
-    <row r="2" spans="1:17" ht="199.5" x14ac:dyDescent="0.45">
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="43"/>
+      <c r="Q1" s="43"/>
+    </row>
+    <row r="2" spans="1:17" ht="203" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -8100,11 +8112,11 @@
       <c r="I2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="48" t="s">
+      <c r="J2" s="44" t="s">
         <v>70</v>
       </c>
-      <c r="K2" s="49"/>
-      <c r="L2" s="4" t="s">
+      <c r="K2" s="45"/>
+      <c r="L2" s="3" t="s">
         <v>10</v>
       </c>
       <c r="M2" s="2" t="s">
@@ -8117,7 +8129,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -8142,7 +8154,7 @@
       <c r="N3" s="5"/>
       <c r="O3" s="2"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4" s="20">
         <v>0</v>
       </c>
@@ -8197,7 +8209,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>20001</v>
       </c>
@@ -8223,11 +8235,11 @@
         <v>4.0123222561722724E-2</v>
       </c>
       <c r="H5" s="13">
-        <f t="shared" ref="H5:I29" si="1">H4+1/26</f>
+        <f>H4+1/26</f>
         <v>7.6923076923076927E-2</v>
       </c>
       <c r="I5" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="H5:I29" si="1">I4+1/26</f>
         <v>7.6923076923076927E-2</v>
       </c>
       <c r="J5" s="13">
@@ -8252,7 +8264,7 @@
         <v>0.97410271505044177</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>25001</v>
       </c>
@@ -8278,7 +8290,7 @@
         <v>5.9077249526311083E-2</v>
       </c>
       <c r="H6" s="13">
-        <f t="shared" si="1"/>
+        <f>H5+1/26</f>
         <v>0.11538461538461539</v>
       </c>
       <c r="I6" s="13">
@@ -8307,7 +8319,7 @@
         <v>0.95987677743827726</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>30001</v>
       </c>
@@ -8321,7 +8333,7 @@
         <v>9424</v>
       </c>
       <c r="E7" s="7">
-        <f t="shared" ref="E7:E29" si="4">C7/D7</f>
+        <f>C7/D7</f>
         <v>32605.774193548386</v>
       </c>
       <c r="F7" s="8">
@@ -8362,7 +8374,7 @@
         <v>0.9409227504736889</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>35001</v>
       </c>
@@ -8376,7 +8388,7 @@
         <v>9839</v>
       </c>
       <c r="E8" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="E7:E29" si="4">C8/D8</f>
         <v>37622.962699461328</v>
       </c>
       <c r="F8" s="8">
@@ -8417,7 +8429,7 @@
         <v>0.92185446289710993</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>40001</v>
       </c>
@@ -8472,7 +8484,7 @@
         <v>0.89888314819391324</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>45001</v>
       </c>
@@ -8527,7 +8539,7 @@
         <v>0.87204324437843783</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>50001</v>
       </c>
@@ -8582,7 +8594,7 @@
         <v>0.84180110114136131</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>55001</v>
       </c>
@@ -8637,7 +8649,7 @@
         <v>0.80944792933859766</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>60001</v>
       </c>
@@ -8692,7 +8704,7 @@
         <v>0.77301411263296871</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>65001</v>
       </c>
@@ -8747,7 +8759,7 @@
         <v>0.73713283203092983</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>70001</v>
       </c>
@@ -8802,7 +8814,7 @@
         <v>0.70123598071503246</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>75001</v>
       </c>
@@ -8857,7 +8869,7 @@
         <v>0.66535463154141028</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>80001</v>
       </c>
@@ -8912,7 +8924,7 @@
         <v>0.63134439007162557</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>85001</v>
       </c>
@@ -8967,7 +8979,7 @@
         <v>0.59870052080119351</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>90001</v>
       </c>
@@ -9022,7 +9034,7 @@
         <v>0.56749077233026313</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>95001</v>
       </c>
@@ -9077,7 +9089,7 @@
         <v>0.53829981762612977</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>100001</v>
       </c>
@@ -9132,7 +9144,7 @@
         <v>0.51098361199410003</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>120001</v>
       </c>
@@ -9187,7 +9199,7 @@
         <v>0.41746359428731122</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>150001</v>
       </c>
@@ -9242,7 +9254,7 @@
         <v>0.31934277408279071</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>200001</v>
       </c>
@@ -9297,7 +9309,7 @@
         <v>0.21911126544004705</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>300001</v>
       </c>
@@ -9352,7 +9364,7 @@
         <v>0.13111553774928922</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>400001</v>
       </c>
@@ -9407,7 +9419,7 @@
         <v>9.3672071438295437E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>500001</v>
       </c>
@@ -9462,7 +9474,7 @@
         <v>7.334301748559964E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>1000001</v>
       </c>
@@ -9517,7 +9529,7 @@
         <v>3.9328314767224794E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>2000001</v>
       </c>
@@ -9572,7 +9584,7 @@
         <v>2.5873775570085945E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B30" t="s">
         <v>23</v>
       </c>
@@ -9593,7 +9605,7 @@
       <c r="J30" s="8"/>
       <c r="K30" s="8"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
       <c r="N31" t="s">
         <v>25</v>
       </c>
@@ -9602,7 +9614,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B32" t="s">
         <v>14</v>
       </c>
@@ -9629,7 +9641,7 @@
         <v>0.10901519963532298</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="I33" t="s">
         <v>19</v>
       </c>
@@ -9638,13 +9650,13 @@
         <v>0.53178096890676674</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A39" s="47" t="s">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A39" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="B39" s="47"/>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="B39" s="38"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>54</v>
       </c>
@@ -9652,9 +9664,9 @@
         <v>53</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41">
-        <f t="shared" ref="A41:A65" si="5">LOG(E4)</f>
+        <f>LOG(E4)</f>
         <v>3.7722955399279523</v>
       </c>
       <c r="B41">
@@ -9662,67 +9674,67 @@
         <v>-0.14348627768580327</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42">
+        <f>LOG(E5)</f>
+        <v>4.3556337674688406</v>
+      </c>
+      <c r="B42">
+        <f t="shared" ref="B42:B65" si="5" xml:space="preserve"> LOG(1-F5)</f>
+        <v>-0.16857623963281418</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <f>LOG(E6)</f>
+        <v>4.4411644681101272</v>
+      </c>
+      <c r="B43">
         <f t="shared" si="5"/>
-        <v>4.3556337674688406</v>
-      </c>
-      <c r="B42">
-        <f t="shared" ref="B42:B65" si="6" xml:space="preserve"> LOG(1-F5)</f>
-        <v>-0.16857623963281418</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A43">
+        <v>-0.19779924270011631</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <f t="shared" ref="A41:A65" si="6">LOG(E7)</f>
+        <v>4.5132945165813325</v>
+      </c>
+      <c r="B44">
         <f t="shared" si="5"/>
-        <v>4.4411644681101272</v>
-      </c>
-      <c r="B43">
+        <v>-0.22435184467592204</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A45">
         <f t="shared" si="6"/>
-        <v>-0.19779924270011631</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A44">
+        <v>4.5754529919949274</v>
+      </c>
+      <c r="B45">
+        <f xml:space="preserve"> LOG(1-F8)</f>
+        <v>-0.25392300720752736</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <f t="shared" si="6"/>
+        <v>4.6293191283530346</v>
+      </c>
+      <c r="B46">
         <f t="shared" si="5"/>
-        <v>4.5132945165813325</v>
-      </c>
-      <c r="B44">
+        <v>-0.28671436190716915</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A47">
         <f t="shared" si="6"/>
-        <v>-0.22435184467592204</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A45">
+        <v>4.6777428199808533</v>
+      </c>
+      <c r="B47">
         <f t="shared" si="5"/>
-        <v>4.5754529919949274</v>
-      </c>
-      <c r="B45">
-        <f t="shared" si="6"/>
-        <v>-0.25392300720752736</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A46">
-        <f t="shared" si="5"/>
-        <v>4.6293191283530346</v>
-      </c>
-      <c r="B46">
-        <f t="shared" si="6"/>
-        <v>-0.28671436190716915</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A47">
-        <f t="shared" si="5"/>
-        <v>4.6777428199808533</v>
-      </c>
-      <c r="B47">
-        <f t="shared" si="6"/>
         <v>-0.32247658683007402</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48">
         <f>LOG(E11)</f>
         <v>4.7206670746380448</v>
@@ -9735,13 +9747,13 @@
       <c r="I48" s="25"/>
       <c r="J48" s="25"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A49">
+        <f t="shared" si="6"/>
+        <v>4.7602077624282391</v>
+      </c>
+      <c r="B49">
         <f t="shared" si="5"/>
-        <v>4.7602077624282391</v>
-      </c>
-      <c r="B49">
-        <f t="shared" si="6"/>
         <v>-0.40271968167192423</v>
       </c>
       <c r="H49" t="s">
@@ -9754,13 +9766,13 @@
         <v>61</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50">
+        <f>LOG(E13)</f>
+        <v>4.7962260987499015</v>
+      </c>
+      <c r="B50">
         <f t="shared" si="5"/>
-        <v>4.7962260987499015</v>
-      </c>
-      <c r="B50">
-        <f t="shared" si="6"/>
         <v>-0.44523318400886275</v>
       </c>
       <c r="F50" s="25" t="s">
@@ -9780,13 +9792,13 @@
         <v>1236582250.9790702</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A51">
+        <f t="shared" si="6"/>
+        <v>4.8294456902556702</v>
+      </c>
+      <c r="B51">
         <f t="shared" si="5"/>
-        <v>4.8294456902556702</v>
-      </c>
-      <c r="B51">
-        <f t="shared" si="6"/>
         <v>-0.48873371805696725</v>
       </c>
       <c r="F51" t="s">
@@ -9800,13 +9812,13 @@
         <v>7.6737016090931601E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A52">
+        <f t="shared" si="6"/>
+        <v>4.8604106341962865</v>
+      </c>
+      <c r="B52">
         <f t="shared" si="5"/>
-        <v>4.8604106341962865</v>
-      </c>
-      <c r="B52">
-        <f t="shared" si="6"/>
         <v>-0.53355581515285122</v>
       </c>
       <c r="F52">
@@ -9818,143 +9830,143 @@
         <v>1.4136378942653307</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A53">
+        <f t="shared" si="6"/>
+        <v>4.8894698346845153</v>
+      </c>
+      <c r="B53">
         <f t="shared" si="5"/>
-        <v>4.8894698346845153</v>
-      </c>
-      <c r="B53">
+        <v>-0.5775706703629786</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A54">
         <f t="shared" si="6"/>
-        <v>-0.5775706703629786</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A54">
+        <v>4.9165395418021651</v>
+      </c>
+      <c r="B54">
         <f t="shared" si="5"/>
-        <v>4.9165395418021651</v>
-      </c>
-      <c r="B54">
+        <v>-0.6214935843787982</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A55">
         <f t="shared" si="6"/>
-        <v>-0.6214935843787982</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A55">
+        <v>4.9422183364895664</v>
+      </c>
+      <c r="B55">
         <f t="shared" si="5"/>
-        <v>4.9422183364895664</v>
-      </c>
-      <c r="B55">
+        <v>-0.66528184659785017</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A56">
         <f t="shared" si="6"/>
-        <v>-0.66528184659785017</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A56">
+        <v>4.9660900441380562</v>
+      </c>
+      <c r="B56">
         <f t="shared" si="5"/>
-        <v>4.9660900441380562</v>
-      </c>
-      <c r="B56">
+        <v>-0.70811319938648543</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A57">
         <f t="shared" si="6"/>
-        <v>-0.70811319938648543</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A57">
+        <v>4.9891731407867042</v>
+      </c>
+      <c r="B57">
         <f t="shared" si="5"/>
-        <v>4.9891731407867042</v>
-      </c>
-      <c r="B57">
+        <v>-0.75001421149432579</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A58">
         <f t="shared" si="6"/>
-        <v>-0.75001421149432579</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A58">
+        <v>5.0388419486119664</v>
+      </c>
+      <c r="B58">
         <f t="shared" si="5"/>
-        <v>5.0388419486119664</v>
-      </c>
-      <c r="B58">
+        <v>-0.9107223451647557</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A59">
         <f t="shared" si="6"/>
-        <v>-0.9107223451647557</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A59">
+        <v>5.1252609204754087</v>
+      </c>
+      <c r="B59">
         <f t="shared" si="5"/>
-        <v>5.1252609204754087</v>
-      </c>
-      <c r="B59">
+        <v>-1.1218845185959989</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A60">
         <f t="shared" si="6"/>
-        <v>-1.1218845185959989</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A60">
+        <v>5.2336646233210313</v>
+      </c>
+      <c r="B60">
         <f t="shared" si="5"/>
-        <v>5.2336646233210313</v>
-      </c>
-      <c r="B60">
+        <v>-1.4214711793857677</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A61">
         <f t="shared" si="6"/>
-        <v>-1.4214711793857677</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A61">
+        <v>5.3774547831689601</v>
+      </c>
+      <c r="B61">
         <f t="shared" si="5"/>
-        <v>5.3774547831689601</v>
-      </c>
-      <c r="B61">
+        <v>-1.8489367956084217</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A62">
         <f t="shared" si="6"/>
-        <v>-1.8489367956084217</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A62">
+        <v>5.5336034482383756</v>
+      </c>
+      <c r="B62">
         <f t="shared" si="5"/>
-        <v>5.5336034482383756</v>
-      </c>
-      <c r="B62">
+        <v>-2.148012707067251</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A63">
         <f t="shared" si="6"/>
-        <v>-2.148012707067251</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A63">
+        <v>5.6472789075972889</v>
+      </c>
+      <c r="B63">
         <f t="shared" si="5"/>
-        <v>5.6472789075972889</v>
-      </c>
-      <c r="B63">
+        <v>-2.380219908101866</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A64">
         <f t="shared" si="6"/>
-        <v>-2.380219908101866</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A64">
+        <v>5.8245416234964953</v>
+      </c>
+      <c r="B64">
         <f t="shared" si="5"/>
-        <v>5.8245416234964953</v>
-      </c>
-      <c r="B64">
+        <v>-3.0506155437199589</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A65">
         <f t="shared" si="6"/>
-        <v>-3.0506155437199589</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A65">
+        <v>6.1265719146621898</v>
+      </c>
+      <c r="B65">
         <f t="shared" si="5"/>
-        <v>6.1265719146621898</v>
-      </c>
-      <c r="B65">
-        <f t="shared" si="6"/>
         <v>-3.6135905717572601</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B69" s="47" t="s">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B69" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="C69" s="47"/>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C69" s="38"/>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B70" t="s">
         <v>54</v>
       </c>
@@ -9962,7 +9974,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B71">
         <f>LOG(A5)</f>
         <v>4.3010517098452263</v>
@@ -9972,7 +9984,7 @@
         <v>-0.16857623963281418</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B72">
         <f t="shared" ref="B72:B94" si="7">LOG(A6)</f>
         <v>4.3979573801038878</v>
@@ -9982,7 +9994,7 @@
         <v>-0.19779924270011631</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B73">
         <f t="shared" si="7"/>
         <v>4.4771357309611233</v>
@@ -9992,7 +10004,7 @@
         <v>-0.22435184467592204</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B74">
         <f t="shared" si="7"/>
         <v>4.5440804525867851</v>
@@ -10002,7 +10014,7 @@
         <v>-0.25392300720752736</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B75">
         <f t="shared" si="7"/>
         <v>4.6020708485542956</v>
@@ -10012,7 +10024,7 @@
         <v>-0.28671436190716915</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B76">
         <f t="shared" si="7"/>
         <v>4.653222164656599</v>
@@ -10022,7 +10034,7 @@
         <v>-0.32247658683007402</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B77">
         <f t="shared" si="7"/>
         <v>4.6989786901387989</v>
@@ -10032,7 +10044,7 @@
         <v>-0.36019297580706788</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B78">
         <f t="shared" si="7"/>
         <v>4.7403705856857679</v>
@@ -10042,7 +10054,7 @@
         <v>-0.40271968167192423</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B79">
         <f t="shared" si="7"/>
         <v>4.7781584885646904</v>
@@ -10052,7 +10064,7 @@
         <v>-0.44523318400886275</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B80">
         <f t="shared" si="7"/>
         <v>4.8129200380450277</v>
@@ -10062,7 +10074,7 @@
         <v>-0.48873371805696725</v>
       </c>
     </row>
-    <row r="81" spans="2:3" x14ac:dyDescent="0.45">
+    <row r="81" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B81">
         <f t="shared" si="7"/>
         <v>4.8451042441768255</v>
@@ -10072,7 +10084,7 @@
         <v>-0.53355581515285122</v>
       </c>
     </row>
-    <row r="82" spans="2:3" x14ac:dyDescent="0.45">
+    <row r="82" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B82">
         <f t="shared" si="7"/>
         <v>4.8750670539461884</v>
@@ -10082,7 +10094,7 @@
         <v>-0.5775706703629786</v>
       </c>
     </row>
-    <row r="83" spans="2:3" x14ac:dyDescent="0.45">
+    <row r="83" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B83">
         <f t="shared" si="7"/>
         <v>4.9030954156390383</v>
@@ -10092,7 +10104,7 @@
         <v>-0.6214935843787982</v>
       </c>
     </row>
-    <row r="84" spans="2:3" x14ac:dyDescent="0.45">
+    <row r="84" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B84">
         <f t="shared" si="7"/>
         <v>4.9294240350310838</v>
@@ -10102,7 +10114,7 @@
         <v>-0.66528184659785017</v>
       </c>
     </row>
-    <row r="85" spans="2:3" x14ac:dyDescent="0.45">
+    <row r="85" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B85">
         <f t="shared" si="7"/>
         <v>4.9542473349067597</v>
@@ -10112,7 +10124,7 @@
         <v>-0.70811319938648543</v>
       </c>
     </row>
-    <row r="86" spans="2:3" x14ac:dyDescent="0.45">
+    <row r="86" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B86">
         <f t="shared" si="7"/>
         <v>4.9777281767856492</v>
@@ -10122,7 +10134,7 @@
         <v>-0.75001421149432579</v>
       </c>
     </row>
-    <row r="87" spans="2:3" x14ac:dyDescent="0.45">
+    <row r="87" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B87">
         <f t="shared" si="7"/>
         <v>5.0000043429231047</v>
@@ -10132,7 +10144,7 @@
         <v>-0.9107223451647557</v>
       </c>
     </row>
-    <row r="88" spans="2:3" x14ac:dyDescent="0.45">
+    <row r="88" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B88">
         <f t="shared" si="7"/>
         <v>5.0791848651532279</v>
@@ -10142,7 +10154,7 @@
         <v>-1.1218845185959989</v>
       </c>
     </row>
-    <row r="89" spans="2:3" x14ac:dyDescent="0.45">
+    <row r="89" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B89">
         <f t="shared" si="7"/>
         <v>5.176094154342576</v>
@@ -10152,7 +10164,7 @@
         <v>-1.4214711793857677</v>
       </c>
     </row>
-    <row r="90" spans="2:3" x14ac:dyDescent="0.45">
+    <row r="90" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B90">
         <f t="shared" si="7"/>
         <v>5.3010321671309617</v>
@@ -10162,7 +10174,7 @@
         <v>-1.8489367956084217</v>
       </c>
     </row>
-    <row r="91" spans="2:3" x14ac:dyDescent="0.45">
+    <row r="91" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B91">
         <f t="shared" si="7"/>
         <v>5.4771227023655227</v>
@@ -10172,7 +10184,7 @@
         <v>-2.148012707067251</v>
       </c>
     </row>
-    <row r="92" spans="2:3" x14ac:dyDescent="0.45">
+    <row r="92" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B92">
         <f t="shared" si="7"/>
         <v>5.6020610770628103</v>
@@ -10182,7 +10194,7 @@
         <v>-2.380219908101866</v>
       </c>
     </row>
-    <row r="93" spans="2:3" x14ac:dyDescent="0.45">
+    <row r="93" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B93">
         <f t="shared" si="7"/>
         <v>5.6989708729241144</v>
@@ -10192,7 +10204,7 @@
         <v>-3.0506155437199589</v>
       </c>
     </row>
-    <row r="94" spans="2:3" x14ac:dyDescent="0.45">
+    <row r="94" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B94">
         <f t="shared" si="7"/>
         <v>6.0000004342942646</v>
@@ -10202,7 +10214,7 @@
         <v>-3.6135905717572601</v>
       </c>
     </row>
-    <row r="95" spans="2:3" x14ac:dyDescent="0.45">
+    <row r="95" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B95">
         <f>LOG(A29)</f>
         <v>6.3010302128111677</v>
@@ -10229,21 +10241,21 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C100B010-F934-41A3-88FF-308B180726C1}">
   <dimension ref="A1:I49"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="24" t="s">
         <v>29</v>
       </c>
       <c r="B3" s="24"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>30</v>
       </c>
@@ -10251,7 +10263,7 @@
         <v>0.92313721029489104</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -10259,7 +10271,7 @@
         <v>0.85218230903103387</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>31</v>
       </c>
@@ -10267,7 +10279,7 @@
         <v>0.84575545290194842</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>32</v>
       </c>
@@ -10275,7 +10287,7 @@
         <v>0.37116301518184985</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="22" t="s">
         <v>33</v>
       </c>
@@ -10283,12 +10295,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="23"/>
       <c r="B11" s="23" t="s">
         <v>39</v>
@@ -10306,7 +10318,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>35</v>
       </c>
@@ -10326,7 +10338,7 @@
         <v>5.0116133691544345E-11</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -10340,7 +10352,7 @@
         <v>0.13776198383888211</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="22" t="s">
         <v>37</v>
       </c>
@@ -10354,8 +10366,8 @@
       <c r="E14" s="22"/>
       <c r="F14" s="22"/>
     </row>
-    <row r="15" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" s="23"/>
       <c r="B16" s="23" t="s">
         <v>44</v>
@@ -10382,7 +10394,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -10411,7 +10423,7 @@
         <v>9.2977414194617349</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="22" t="s">
         <v>51</v>
       </c>
@@ -10440,13 +10452,13 @@
         <v>-1.4404650823910896</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" s="23" t="s">
         <v>56</v>
       </c>
@@ -10457,7 +10469,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>1</v>
       </c>
@@ -10468,7 +10480,7 @@
         <v>-1.2510329258531978</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>2</v>
       </c>
@@ -10479,7 +10491,7 @@
         <v>-0.25183327226711361</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>3</v>
       </c>
@@ -10490,7 +10502,7 @@
         <v>-0.1308720351459072</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>4</v>
       </c>
@@ -10501,7 +10513,7 @@
         <v>-3.0770740413433612E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>5</v>
       </c>
@@ -10512,7 +10524,7 @@
         <v>4.8802805694943885E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>6</v>
       </c>
@@ -10523,7 +10535,7 @@
         <v>0.11059555588603043</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>7</v>
       </c>
@@ -10534,7 +10546,7 @@
         <v>0.15986099096964451</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>8</v>
       </c>
@@ -10545,7 +10557,7 @@
         <v>0.19751574385181736</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>9</v>
       </c>
@@ -10556,7 +10568,7 @@
         <v>0.2244189398558441</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>10</v>
       </c>
@@ -10567,7 +10579,7 @@
         <v>0.24515040608299948</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>11</v>
       </c>
@@ -10578,7 +10590,7 @@
         <v>0.2599804956853487</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>12</v>
       </c>
@@ -10589,7 +10601,7 @@
         <v>0.26953006330556528</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>13</v>
       </c>
@@ -10600,7 +10612,7 @@
         <v>0.27654055821052248</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>14</v>
       </c>
@@ -10611,7 +10623,7 @@
         <v>0.28014962236287089</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>15</v>
       </c>
@@ -10622,7 +10634,7 @@
         <v>0.28145102081733919</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>16</v>
       </c>
@@ -10633,7 +10645,7 @@
         <v>0.28053624591606019</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>17</v>
       </c>
@@ -10644,7 +10656,7 @@
         <v>0.27916708150013259</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>18</v>
       </c>
@@ -10655,7 +10667,7 @@
         <v>0.20567292022063155</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>19</v>
       </c>
@@ -10666,7 +10678,7 @@
         <v>0.14625471158649428</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>20</v>
       </c>
@@ -10677,7 +10689,7 @@
         <v>3.7015231673575899E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>21</v>
       </c>
@@ -10688,7 +10700,7 @@
         <v>-0.13796775852787468</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>22</v>
       </c>
@@ -10699,7 +10711,7 @@
         <v>-0.16286061707038124</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>23</v>
       </c>
@@ -10710,7 +10722,7 @@
         <v>-0.1954639055461751</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>24</v>
       </c>
@@ -10721,7 +10733,7 @@
         <v>-0.55460210843580215</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="49" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A49" s="22">
         <v>25</v>
       </c>

--- a/exercices/exercices_gini_afc2022.xlsx
+++ b/exercices/exercices_gini_afc2022.xlsx
@@ -1,23 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gueney\Documents\GitHub\les-mesures-de-l-conomie\exercices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F616831B-DB21-4BDD-B3CC-3A76C685CFC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41C6AE36-9A7C-4079-AEAE-6428B3B88B1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{0A857FEE-5B62-478B-B26F-1439DD0DBBE3}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="3" xr2:uid="{0A857FEE-5B62-478B-B26F-1439DD0DBBE3}"/>
   </bookViews>
   <sheets>
     <sheet name="source" sheetId="2" r:id="rId1"/>
     <sheet name="CH" sheetId="1" r:id="rId2"/>
     <sheet name="CH theil" sheetId="7" r:id="rId3"/>
     <sheet name="GE" sheetId="3" r:id="rId4"/>
-    <sheet name="alpha coef GE" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="43">
   <si>
     <t>seuil inférieur du groupe</t>
   </si>
@@ -66,12 +65,6 @@
     <t>ligne égalité parfaite y</t>
   </si>
   <si>
-    <t>Aire des triangles sous la courbe</t>
-  </si>
-  <si>
-    <t>Aire des rectangles sous la courbe</t>
-  </si>
-  <si>
     <t>Nombre de contribuables ayant un revenu supérieur au seuil inférieur du groupe</t>
   </si>
   <si>
@@ -85,18 +78,6 @@
   </si>
   <si>
     <t>TOTAL</t>
-  </si>
-  <si>
-    <t>Somme aires triangles</t>
-  </si>
-  <si>
-    <t>Somme aires rectangles</t>
-  </si>
-  <si>
-    <t>Part du 1%</t>
-  </si>
-  <si>
-    <t>Somme totale</t>
   </si>
   <si>
     <t>Coefficient de Gini</t>
@@ -117,85 +98,10 @@
     <t>revenu total du groupe</t>
   </si>
   <si>
-    <t>Part du 0.1%</t>
-  </si>
-  <si>
     <t>source: administration fédérale des contributions, période fiscale 2022, contribuables avec et sans versement d'un impot fédéral direct</t>
   </si>
   <si>
     <t>https://www.estv.admin.ch/fr/statistiques-personnes-physiques-cantons-1983-a-aujourdhui</t>
-  </si>
-  <si>
-    <t>RAPPORT DÉTAILLÉ</t>
-  </si>
-  <si>
-    <t>Statistiques de la régression</t>
-  </si>
-  <si>
-    <t>Coefficient de détermination multiple</t>
-  </si>
-  <si>
-    <t>Coefficient de détermination R^2</t>
-  </si>
-  <si>
-    <t>Erreur-type</t>
-  </si>
-  <si>
-    <t>Observations</t>
-  </si>
-  <si>
-    <t>ANALYSE DE VARIANCE</t>
-  </si>
-  <si>
-    <t>Régression</t>
-  </si>
-  <si>
-    <t>Résidus</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>Constante</t>
-  </si>
-  <si>
-    <t>Degré de liberté</t>
-  </si>
-  <si>
-    <t>Somme des carrés</t>
-  </si>
-  <si>
-    <t>Moyenne des carrés</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>Valeur critique de F</t>
-  </si>
-  <si>
-    <t>Coefficients</t>
-  </si>
-  <si>
-    <t>Statistique t</t>
-  </si>
-  <si>
-    <t>Probabilité</t>
-  </si>
-  <si>
-    <t>Limite inférieure pour seuil de confiance = 95%</t>
-  </si>
-  <si>
-    <t>Limite supérieure pour seuil de confiance = 95%</t>
-  </si>
-  <si>
-    <t>Limite inférieure pour seuil de confiance =  95,0%</t>
-  </si>
-  <si>
-    <t>Limite supérieure pour seuil de confiance =  95,0%</t>
-  </si>
-  <si>
-    <t>Variable X 1</t>
   </si>
   <si>
     <t>Distribution empirique de Parto</t>
@@ -205,15 +111,6 @@
   </si>
   <si>
     <t>Log du revenu moyen</t>
-  </si>
-  <si>
-    <t>ANALYSE DES RÉSIDUS</t>
-  </si>
-  <si>
-    <t>Observation</t>
-  </si>
-  <si>
-    <t>Prévisions pour Y</t>
   </si>
   <si>
     <t>b = y_bar / s</t>
@@ -260,6 +157,21 @@
   <si>
     <t>Somme aires trapèzes</t>
   </si>
+  <si>
+    <t xml:space="preserve">Coefficient de Gini </t>
+  </si>
+  <si>
+    <t>Aire des trapèzes sous la courbe de Lorenz</t>
+  </si>
+  <si>
+    <t>Part des 10%</t>
+  </si>
+  <si>
+    <t>Part des 1%</t>
+  </si>
+  <si>
+    <t>Interpolation linéaire</t>
+  </si>
 </sst>
 </file>
 
@@ -269,7 +181,7 @@
     <numFmt numFmtId="164" formatCode="0.0000%"/>
     <numFmt numFmtId="165" formatCode="0.000%"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -300,16 +212,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -358,8 +262,44 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="14">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -374,26 +314,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -516,7 +436,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -535,7 +455,6 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -557,39 +476,30 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -605,23 +515,46 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="10" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="11" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="12" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="13" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2469,513 +2402,6 @@
       <a:endParaRPr lang="LID4096"/>
     </a:p>
   </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="fr-FR"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="fr-CH"/>
-              <a:t>Variable X 1 Courbe de régression</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:v>Y</c:v>
-          </c:tx>
-          <c:cat>
-            <c:numRef>
-              <c:f>GE!$A$41:$A$65</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
-                <c:pt idx="0">
-                  <c:v>3.7722955399279523</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4.3556337674688406</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4.4411644681101272</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4.5132945165813325</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>4.5754529919949274</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>4.6293191283530346</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>4.6777428199808533</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>4.7206670746380448</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>4.7602077624282391</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>4.7962260987499015</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>4.8294456902556702</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>4.8604106341962865</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>4.8894698346845153</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>4.9165395418021651</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>4.9422183364895664</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>4.9660900441380562</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>4.9891731407867042</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>5.0388419486119664</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>5.1252609204754087</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>5.2336646233210313</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>5.3774547831689601</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>5.5336034482383756</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>5.6472789075972889</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>5.8245416234964953</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>6.1265719146621898</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>GE!$B$41:$B$65</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
-                <c:pt idx="0">
-                  <c:v>-0.14348627768580327</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-0.16857623963281418</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>-0.19779924270011631</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>-0.22435184467592204</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>-0.25392300720752736</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>-0.28671436190716915</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>-0.32247658683007402</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>-0.36019297580706788</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>-0.40271968167192423</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>-0.44523318400886275</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>-0.48873371805696725</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>-0.53355581515285122</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>-0.5775706703629786</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>-0.6214935843787982</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>-0.66528184659785017</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>-0.70811319938648543</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>-0.75001421149432579</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>-0.9107223451647557</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>-1.1218845185959989</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>-1.4214711793857677</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>-1.8489367956084217</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>-2.148012707067251</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>-2.380219908101866</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>-3.0506155437199589</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>-3.6135905717572601</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-D531-4565-A490-D1D3594E58FD}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:v>Prévisions pour Y</c:v>
-          </c:tx>
-          <c:cat>
-            <c:numRef>
-              <c:f>GE!$A$41:$A$65</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
-                <c:pt idx="0">
-                  <c:v>3.7722955399279523</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4.3556337674688406</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4.4411644681101272</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4.5132945165813325</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>4.5754529919949274</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>4.6293191283530346</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>4.6777428199808533</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>4.7206670746380448</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>4.7602077624282391</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>4.7962260987499015</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>4.8294456902556702</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>4.8604106341962865</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>4.8894698346845153</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>4.9165395418021651</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>4.9422183364895664</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>4.9660900441380562</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>4.9891731407867042</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>5.0388419486119664</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>5.1252609204754087</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>5.2336646233210313</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>5.3774547831689601</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>5.5336034482383756</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>5.6472789075972889</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>5.8245416234964953</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>6.1265719146621898</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'alpha coef GE'!$B$25:$B$49</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
-                <c:pt idx="0">
-                  <c:v>1.1075466481673946</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>8.3257032634299399E-2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>-6.6927207554209112E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>-0.19358110426248842</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>-0.30272581290247125</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>-0.39730991779319957</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>-0.48233757779971853</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>-0.55770871965888524</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>-0.62713862152776834</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>-0.69038359009186223</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>-0.74871421374231595</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>-0.8030858784584165</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>-0.85411122857350108</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>-0.90164320674166909</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>-0.94673286741518936</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>-0.98864944530254562</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>-1.0291812929944584</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>-1.1163952653853872</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>-1.2681392301824932</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>-1.4584864110593436</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>-1.710969037080547</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>-1.9851520899968698</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>-2.1847560025556909</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>-2.4960134352841568</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>-3.0263515413973447</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-D531-4565-A490-D1D3594E58FD}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:marker val="1"/>
-        <c:smooth val="0"/>
-        <c:axId val="239571519"/>
-        <c:axId val="239578239"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="239571519"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="fr-CH"/>
-                  <a:t>Variable X 1</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="low"/>
-        <c:crossAx val="239578239"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:tickMarkSkip val="1"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="239578239"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="fr-CH"/>
-                  <a:t>Y</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="239571519"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
@@ -4657,15 +4083,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>616742</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>238124</xdr:rowOff>
+      <xdr:colOff>534619</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>184433</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>616742</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>76199</xdr:rowOff>
+      <xdr:colOff>534619</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>33549</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4734,15 +4160,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>896937</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:colOff>1082550</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>130994</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>481012</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:colOff>666640</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>175442</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4762,47 +4188,6 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>409575</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>109537</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>600075</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>23812</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Graphique 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{545652EF-6576-48D0-EA9B-A5AA556031AB}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5113,12 +4498,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A2" s="19" t="s">
-        <v>27</v>
+      <c r="A2" s="18" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -5131,40 +4516,41 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CB256E1-B0FC-48AE-8D60-3C9A253EE1A6}">
-  <dimension ref="A1:Q35"/>
+  <dimension ref="A1:Q32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="25.36328125" customWidth="1"/>
-    <col min="5" max="5" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.453125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="29.6328125" customWidth="1"/>
     <col min="7" max="7" width="39.36328125" customWidth="1"/>
-    <col min="8" max="8" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.453125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="22.6328125" customWidth="1"/>
     <col min="10" max="10" width="20.26953125" customWidth="1"/>
-    <col min="12" max="12" width="67.36328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="67.453125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10.36328125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="27.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="F1" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="40" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1" s="41"/>
-      <c r="L1" s="42" t="s">
-        <v>21</v>
-      </c>
-      <c r="M1" s="43"/>
-      <c r="N1" s="43"/>
-      <c r="O1" s="43"/>
-      <c r="P1" s="43"/>
-      <c r="Q1" s="43"/>
+      <c r="F1" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="K1" s="37"/>
+      <c r="L1" s="38" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="39"/>
+      <c r="N1" s="39"/>
+      <c r="O1" s="39"/>
+      <c r="P1" s="39"/>
+      <c r="Q1" s="39"/>
     </row>
     <row r="2" spans="1:17" ht="174" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -5174,7 +4560,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>2</v>
@@ -5195,22 +4581,20 @@
         <v>7</v>
       </c>
       <c r="J2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="2"/>
+      <c r="L2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="N2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.35">
@@ -5233,7 +4617,7 @@
       </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
-      <c r="L3" s="12"/>
+      <c r="L3" s="11"/>
       <c r="M3" s="2"/>
       <c r="N3" s="5"/>
       <c r="O3" s="2"/>
@@ -5245,7 +4629,7 @@
       <c r="B4" s="1">
         <v>20000</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="10">
         <v>6349766510</v>
       </c>
       <c r="D4" s="1">
@@ -5263,24 +4647,24 @@
         <f>SUM($C$4:C4)/$C$32</f>
         <v>1.9104146904600303E-2</v>
       </c>
-      <c r="H4" s="13">
+      <c r="H4" s="12">
         <f>H3+1/26</f>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="I4" s="13">
+      <c r="I4" s="12">
         <f>I3+1/26</f>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="J4" s="13">
-        <f>F4*G4/2</f>
+      <c r="J4" s="12">
+        <f>((G4+G3)*(F4-F3))/2</f>
         <v>1.6520606133099216E-3</v>
       </c>
-      <c r="K4" s="14"/>
-      <c r="L4" s="15">
+      <c r="K4" s="13"/>
+      <c r="L4" s="14">
         <f>SUM(D4:$D$29)</f>
         <v>4798463</v>
       </c>
-      <c r="M4" s="16">
+      <c r="M4" s="15">
         <f>L4/$D$32</f>
         <v>1</v>
       </c>
@@ -5288,7 +4672,7 @@
         <f>SUM(C4:$C$29)</f>
         <v>332376344346</v>
       </c>
-      <c r="O4" s="17">
+      <c r="O4" s="16">
         <f>N4/C$32</f>
         <v>1</v>
       </c>
@@ -5318,36 +4702,33 @@
         <f>SUM($C$4:C5)/$C$32</f>
         <v>3.1595535818481547E-2</v>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="12">
         <f t="shared" ref="H5:H29" si="0">H4+1/26</f>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="I5" s="13">
+      <c r="I5" s="12">
         <f t="shared" ref="I5:I29" si="1">I4+1/26</f>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="J5" s="8">
-        <f>((F5-F4)*(G5-G4))/2</f>
-        <v>2.3916046379885401E-4</v>
-      </c>
-      <c r="K5" s="8">
-        <f>(F5-F4)*G4</f>
-        <v>7.315370077235091E-4</v>
-      </c>
-      <c r="L5" s="18">
+      <c r="J5" s="12">
+        <f t="shared" ref="J5:J28" si="2">((G5+G4)*(F5-F4))/2</f>
+        <v>9.7069747152236311E-4</v>
+      </c>
+      <c r="K5" s="8"/>
+      <c r="L5" s="17">
         <f>SUM(D5:$D$29)</f>
         <v>3968554</v>
       </c>
-      <c r="M5" s="16">
-        <f t="shared" ref="M5:M29" si="2">L5/$D$32</f>
+      <c r="M5" s="15">
+        <f t="shared" ref="M5:M29" si="3">L5/$D$32</f>
         <v>0.82704691064617986</v>
       </c>
       <c r="N5" s="9">
         <f>SUM(C5:$C$29)</f>
         <v>326026577836</v>
       </c>
-      <c r="O5" s="17">
-        <f t="shared" ref="O5:O29" si="3">N5/C$32</f>
+      <c r="O5" s="16">
+        <f t="shared" ref="O5:O29" si="4">N5/C$32</f>
         <v>0.98089585309539973</v>
       </c>
     </row>
@@ -5376,36 +4757,33 @@
         <f>SUM($C$4:C6)/$C$32</f>
         <v>4.7517082050698198E-2</v>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="12">
         <f t="shared" si="0"/>
         <v>0.11538461538461539</v>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="12">
         <f t="shared" si="1"/>
         <v>0.11538461538461539</v>
       </c>
-      <c r="J6" s="8">
-        <f t="shared" ref="J6:J28" si="4">((F6-F5)*(G6-G5))/2</f>
-        <v>3.1861255477063629E-4</v>
-      </c>
-      <c r="K6" s="8">
-        <f t="shared" ref="K6:K29" si="5">(F6-F5)*G5</f>
-        <v>1.2645423050813864E-3</v>
-      </c>
-      <c r="L6" s="18">
+      <c r="J6" s="12">
+        <f t="shared" si="2"/>
+        <v>1.5831548598520227E-3</v>
+      </c>
+      <c r="K6" s="8"/>
+      <c r="L6" s="17">
         <f>SUM(D6:$D$29)</f>
         <v>3784811</v>
       </c>
-      <c r="M6" s="16">
-        <f t="shared" si="2"/>
+      <c r="M6" s="15">
+        <f t="shared" si="3"/>
         <v>0.78875485754500974</v>
       </c>
       <c r="N6" s="9">
         <f>SUM(C6:$C$29)</f>
         <v>321874735653</v>
       </c>
-      <c r="O6" s="17">
-        <f t="shared" si="3"/>
+      <c r="O6" s="16">
+        <f t="shared" si="4"/>
         <v>0.96840446418151849</v>
       </c>
     </row>
@@ -5423,7 +4801,7 @@
         <v>187369</v>
       </c>
       <c r="E7" s="7">
-        <f t="shared" ref="E7:E29" si="6">C7/D7</f>
+        <f t="shared" ref="E7:E29" si="5">C7/D7</f>
         <v>32598.407319247046</v>
       </c>
       <c r="F7" s="8">
@@ -5434,36 +4812,33 @@
         <f>SUM($C$4:C7)/$C$32</f>
         <v>6.5893633465686122E-2</v>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="12">
         <f t="shared" si="0"/>
         <v>0.15384615384615385</v>
       </c>
-      <c r="I7" s="13">
+      <c r="I7" s="12">
         <f t="shared" si="1"/>
         <v>0.15384615384615385</v>
       </c>
-      <c r="J7" s="8">
-        <f t="shared" si="4"/>
-        <v>3.5878114117738062E-4</v>
-      </c>
-      <c r="K7" s="8">
-        <f t="shared" si="5"/>
-        <v>1.855433322452893E-3</v>
-      </c>
-      <c r="L7" s="18">
+      <c r="J7" s="12">
+        <f t="shared" si="2"/>
+        <v>2.2142144636302739E-3</v>
+      </c>
+      <c r="K7" s="8"/>
+      <c r="L7" s="17">
         <f>SUM(D7:$D$29)</f>
         <v>3592763</v>
       </c>
-      <c r="M7" s="16">
-        <f t="shared" si="2"/>
+      <c r="M7" s="15">
+        <f t="shared" si="3"/>
         <v>0.74873204190591858</v>
       </c>
       <c r="N7" s="9">
         <f>SUM(C7:$C$29)</f>
         <v>316582790320</v>
       </c>
-      <c r="O7" s="17">
-        <f t="shared" si="3"/>
+      <c r="O7" s="16">
+        <f t="shared" si="4"/>
         <v>0.95248291794930184</v>
       </c>
     </row>
@@ -5481,7 +4856,7 @@
         <v>212579</v>
       </c>
       <c r="E8" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>37613.401013270362</v>
       </c>
       <c r="F8" s="8">
@@ -5492,36 +4867,33 @@
         <f>SUM($C$4:C8)/$C$32</f>
         <v>8.9950156470453402E-2</v>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="12">
         <f t="shared" si="0"/>
         <v>0.19230769230769232</v>
       </c>
-      <c r="I8" s="13">
+      <c r="I8" s="12">
         <f t="shared" si="1"/>
         <v>0.19230769230769232</v>
       </c>
-      <c r="J8" s="8">
-        <f t="shared" si="4"/>
-        <v>5.328697547350499E-4</v>
-      </c>
-      <c r="K8" s="8">
-        <f t="shared" si="5"/>
-        <v>2.9191853117346307E-3</v>
-      </c>
-      <c r="L8" s="18">
+      <c r="J8" s="12">
+        <f t="shared" si="2"/>
+        <v>3.4520550664696803E-3</v>
+      </c>
+      <c r="K8" s="8"/>
+      <c r="L8" s="17">
         <f>SUM(D8:$D$29)</f>
         <v>3405394</v>
       </c>
-      <c r="M8" s="16">
-        <f t="shared" si="2"/>
+      <c r="M8" s="15">
+        <f t="shared" si="3"/>
         <v>0.70968433016988985</v>
       </c>
       <c r="N8" s="9">
         <f>SUM(C8:$C$29)</f>
         <v>310474859339</v>
       </c>
-      <c r="O8" s="17">
-        <f t="shared" si="3"/>
+      <c r="O8" s="16">
+        <f t="shared" si="4"/>
         <v>0.93410636653431389</v>
       </c>
     </row>
@@ -5550,36 +4922,33 @@
         <f>SUM($C$4:C9)/$C$32</f>
         <v>0.12155531081640955</v>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="12">
         <f t="shared" si="0"/>
         <v>0.23076923076923078</v>
       </c>
-      <c r="I9" s="13">
+      <c r="I9" s="12">
         <f t="shared" si="1"/>
         <v>0.23076923076923078</v>
       </c>
-      <c r="J9" s="8">
-        <f t="shared" si="4"/>
-        <v>8.123348040715968E-4</v>
-      </c>
-      <c r="K9" s="8">
-        <f t="shared" si="5"/>
-        <v>4.6239067167842783E-3</v>
-      </c>
-      <c r="L9" s="18">
+      <c r="J9" s="12">
+        <f t="shared" si="2"/>
+        <v>5.4362415208558754E-3</v>
+      </c>
+      <c r="K9" s="8"/>
+      <c r="L9" s="17">
         <f>SUM(D9:$D$29)</f>
         <v>3192815</v>
       </c>
-      <c r="M9" s="16">
-        <f t="shared" si="2"/>
+      <c r="M9" s="15">
+        <f t="shared" si="3"/>
         <v>0.66538285280099063</v>
       </c>
       <c r="N9" s="9">
         <f>SUM(C9:$C$29)</f>
         <v>302479040165</v>
       </c>
-      <c r="O9" s="17">
-        <f t="shared" si="3"/>
+      <c r="O9" s="16">
+        <f t="shared" si="4"/>
         <v>0.91004984352954654</v>
       </c>
     </row>
@@ -5597,7 +4966,7 @@
         <v>265973</v>
       </c>
       <c r="E10" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>47570.903358611591</v>
       </c>
       <c r="F10" s="8">
@@ -5608,36 +4977,33 @@
         <f>SUM($C$4:C10)/$C$32</f>
         <v>0.15962232760093983</v>
       </c>
-      <c r="H10" s="13">
+      <c r="H10" s="12">
         <f t="shared" si="0"/>
         <v>0.26923076923076927</v>
       </c>
-      <c r="I10" s="13">
+      <c r="I10" s="12">
         <f t="shared" si="1"/>
         <v>0.26923076923076927</v>
       </c>
-      <c r="J10" s="8">
-        <f t="shared" si="4"/>
-        <v>1.0550043477705134E-3</v>
-      </c>
-      <c r="K10" s="8">
-        <f t="shared" si="5"/>
-        <v>6.7376638485642021E-3</v>
-      </c>
-      <c r="L10" s="18">
+      <c r="J10" s="12">
+        <f t="shared" si="2"/>
+        <v>7.7926681963347158E-3</v>
+      </c>
+      <c r="K10" s="8"/>
+      <c r="L10" s="17">
         <f>SUM(D10:$D$29)</f>
         <v>2946149</v>
       </c>
-      <c r="M10" s="16">
-        <f t="shared" si="2"/>
+      <c r="M10" s="15">
+        <f t="shared" si="3"/>
         <v>0.61397764242425124</v>
       </c>
       <c r="N10" s="9">
         <f>SUM(C10:$C$29)</f>
         <v>291974234501</v>
       </c>
-      <c r="O10" s="17">
-        <f t="shared" si="3"/>
+      <c r="O10" s="16">
+        <f t="shared" si="4"/>
         <v>0.87844468918359042</v>
       </c>
     </row>
@@ -5655,7 +5021,7 @@
         <v>264066</v>
       </c>
       <c r="E11" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>52524.612759688869</v>
       </c>
       <c r="F11" s="8">
@@ -5666,36 +5032,33 @@
         <f>SUM($C$4:C11)/$C$32</f>
         <v>0.20135202536355054</v>
       </c>
-      <c r="H11" s="13">
+      <c r="H11" s="12">
         <f t="shared" si="0"/>
         <v>0.30769230769230771</v>
       </c>
-      <c r="I11" s="13">
+      <c r="I11" s="12">
         <f t="shared" si="1"/>
         <v>0.30769230769230771</v>
       </c>
-      <c r="J11" s="8">
-        <f t="shared" si="4"/>
-        <v>1.1482212501567229E-3</v>
-      </c>
-      <c r="K11" s="8">
-        <f t="shared" si="5"/>
-        <v>8.7842356105006496E-3</v>
-      </c>
-      <c r="L11" s="18">
+      <c r="J11" s="12">
+        <f t="shared" si="2"/>
+        <v>9.932456860657371E-3</v>
+      </c>
+      <c r="K11" s="8"/>
+      <c r="L11" s="17">
         <f>SUM(D11:$D$29)</f>
         <v>2680176</v>
       </c>
-      <c r="M11" s="16">
-        <f t="shared" si="2"/>
+      <c r="M11" s="15">
+        <f t="shared" si="3"/>
         <v>0.55854885199698323</v>
       </c>
       <c r="N11" s="9">
         <f>SUM(C11:$C$29)</f>
         <v>279321658622</v>
       </c>
-      <c r="O11" s="17">
-        <f t="shared" si="3"/>
+      <c r="O11" s="16">
+        <f t="shared" si="4"/>
         <v>0.84037767239906014</v>
       </c>
     </row>
@@ -5713,7 +5076,7 @@
         <v>248279</v>
       </c>
       <c r="E12" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>57520.93284973759</v>
       </c>
       <c r="F12" s="8">
@@ -5724,36 +5087,33 @@
         <f>SUM($C$4:C12)/$C$32</f>
         <v>0.24431910148053615</v>
       </c>
-      <c r="H12" s="13">
+      <c r="H12" s="12">
         <f t="shared" si="0"/>
         <v>0.34615384615384615</v>
       </c>
-      <c r="I12" s="13">
+      <c r="I12" s="12">
         <f t="shared" si="1"/>
         <v>0.34615384615384615</v>
       </c>
-      <c r="J12" s="8">
-        <f t="shared" si="4"/>
-        <v>1.1115874699095384E-3</v>
-      </c>
-      <c r="K12" s="8">
-        <f t="shared" si="5"/>
-        <v>1.0418227566876508E-2</v>
-      </c>
-      <c r="L12" s="18">
+      <c r="J12" s="12">
+        <f t="shared" si="2"/>
+        <v>1.1529815036786047E-2</v>
+      </c>
+      <c r="K12" s="8"/>
+      <c r="L12" s="17">
         <f>SUM(D12:$D$29)</f>
         <v>2416110</v>
       </c>
-      <c r="M12" s="16">
-        <f t="shared" si="2"/>
+      <c r="M12" s="15">
+        <f t="shared" si="3"/>
         <v>0.50351748049323297</v>
       </c>
       <c r="N12" s="9">
         <f>SUM(C12:$C$29)</f>
         <v>265451694229</v>
       </c>
-      <c r="O12" s="17">
-        <f t="shared" si="3"/>
+      <c r="O12" s="16">
+        <f t="shared" si="4"/>
         <v>0.79864797463644943</v>
       </c>
     </row>
@@ -5771,7 +5131,7 @@
         <v>224425</v>
       </c>
       <c r="E13" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>62499.12064609558</v>
       </c>
       <c r="F13" s="8">
@@ -5782,36 +5142,33 @@
         <f>SUM($C$4:C13)/$C$32</f>
         <v>0.28651935245988597</v>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="12">
         <f t="shared" si="0"/>
         <v>0.38461538461538458</v>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="12">
         <f t="shared" si="1"/>
         <v>0.38461538461538458</v>
       </c>
-      <c r="J13" s="8">
-        <f t="shared" si="4"/>
-        <v>9.8685676288850989E-4</v>
-      </c>
-      <c r="K13" s="8">
-        <f t="shared" si="5"/>
-        <v>1.1426849461956733E-2</v>
-      </c>
-      <c r="L13" s="18">
+      <c r="J13" s="12">
+        <f t="shared" si="2"/>
+        <v>1.2413706224845241E-2</v>
+      </c>
+      <c r="K13" s="8"/>
+      <c r="L13" s="17">
         <f>SUM(D13:$D$29)</f>
         <v>2167831</v>
       </c>
-      <c r="M13" s="16">
-        <f t="shared" si="2"/>
+      <c r="M13" s="15">
+        <f t="shared" si="3"/>
         <v>0.45177612081201834</v>
       </c>
       <c r="N13" s="9">
         <f>SUM(C13:$C$29)</f>
         <v>251170454542</v>
       </c>
-      <c r="O13" s="17">
-        <f t="shared" si="3"/>
+      <c r="O13" s="16">
+        <f t="shared" si="4"/>
         <v>0.75568089851946385</v>
       </c>
     </row>
@@ -5829,7 +5186,7 @@
         <v>201115</v>
       </c>
       <c r="E14" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>67493.293463938549</v>
       </c>
       <c r="F14" s="8">
@@ -5840,36 +5197,33 @@
         <f>SUM($C$4:C14)/$C$32</f>
         <v>0.32735834099172234</v>
       </c>
-      <c r="H14" s="13">
+      <c r="H14" s="12">
         <f t="shared" si="0"/>
         <v>0.42307692307692302</v>
       </c>
-      <c r="I14" s="13">
+      <c r="I14" s="12">
         <f t="shared" si="1"/>
         <v>0.42307692307692302</v>
       </c>
-      <c r="J14" s="8">
-        <f t="shared" si="4"/>
-        <v>8.5582958319990006E-4</v>
-      </c>
-      <c r="K14" s="8">
-        <f t="shared" si="5"/>
-        <v>1.2008707698688111E-2</v>
-      </c>
-      <c r="L14" s="18">
+      <c r="J14" s="12">
+        <f t="shared" si="2"/>
+        <v>1.2864537281888013E-2</v>
+      </c>
+      <c r="K14" s="8"/>
+      <c r="L14" s="17">
         <f>SUM(D14:$D$29)</f>
         <v>1943406</v>
       </c>
-      <c r="M14" s="16">
-        <f t="shared" si="2"/>
+      <c r="M14" s="15">
+        <f t="shared" si="3"/>
         <v>0.40500593627584497</v>
       </c>
       <c r="N14" s="9">
         <f>SUM(C14:$C$29)</f>
         <v>237144089391</v>
       </c>
-      <c r="O14" s="17">
-        <f t="shared" si="3"/>
+      <c r="O14" s="16">
+        <f t="shared" si="4"/>
         <v>0.71348064754011409</v>
       </c>
     </row>
@@ -5887,7 +5241,7 @@
         <v>178545</v>
       </c>
       <c r="E15" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>72494.92566019771</v>
       </c>
       <c r="F15" s="8">
@@ -5898,36 +5252,33 @@
         <f>SUM($C$4:C15)/$C$32</f>
         <v>0.36630096348030072</v>
       </c>
-      <c r="H15" s="13">
+      <c r="H15" s="12">
         <f t="shared" si="0"/>
         <v>0.46153846153846145</v>
       </c>
-      <c r="I15" s="13">
+      <c r="I15" s="12">
         <f t="shared" si="1"/>
         <v>0.46153846153846145</v>
       </c>
-      <c r="J15" s="8">
-        <f t="shared" si="4"/>
-        <v>7.2450392263347964E-4</v>
-      </c>
-      <c r="K15" s="8">
-        <f t="shared" si="5"/>
-        <v>1.2180607622142148E-2</v>
-      </c>
-      <c r="L15" s="18">
+      <c r="J15" s="12">
+        <f t="shared" si="2"/>
+        <v>1.2905111544775628E-2</v>
+      </c>
+      <c r="K15" s="8"/>
+      <c r="L15" s="17">
         <f>SUM(D15:$D$29)</f>
         <v>1742291</v>
       </c>
-      <c r="M15" s="16">
-        <f t="shared" si="2"/>
+      <c r="M15" s="15">
+        <f>L15/$D$32</f>
         <v>0.36309355724947762</v>
       </c>
       <c r="N15" s="9">
         <f>SUM(C15:$C$29)</f>
         <v>223570175676</v>
       </c>
-      <c r="O15" s="17">
-        <f t="shared" si="3"/>
+      <c r="O15" s="16">
+        <f t="shared" si="4"/>
         <v>0.67264165900827766</v>
       </c>
     </row>
@@ -5945,7 +5296,7 @@
         <v>159615</v>
       </c>
       <c r="E16" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>77495.903323622464</v>
       </c>
       <c r="F16" s="8">
@@ -5956,36 +5307,33 @@
         <f>SUM($C$4:C16)/$C$32</f>
         <v>0.40351633340483267</v>
       </c>
-      <c r="H16" s="13">
+      <c r="H16" s="12">
         <f t="shared" si="0"/>
         <v>0.49999999999999989</v>
       </c>
-      <c r="I16" s="13">
+      <c r="I16" s="12">
         <f t="shared" si="1"/>
         <v>0.49999999999999989</v>
       </c>
-      <c r="J16" s="8">
-        <f t="shared" si="4"/>
-        <v>6.189618707598825E-4</v>
-      </c>
-      <c r="K16" s="8">
-        <f t="shared" si="5"/>
-        <v>1.2184553321742418E-2</v>
-      </c>
-      <c r="L16" s="18">
+      <c r="J16" s="12">
+        <f t="shared" si="2"/>
+        <v>1.28035151925023E-2</v>
+      </c>
+      <c r="K16" s="8"/>
+      <c r="L16" s="17">
         <f>SUM(D16:$D$29)</f>
         <v>1563746</v>
       </c>
-      <c r="M16" s="16">
-        <f t="shared" si="2"/>
+      <c r="M16" s="15">
+        <f t="shared" si="3"/>
         <v>0.32588476768498581</v>
       </c>
       <c r="N16" s="9">
         <f>SUM(C16:$C$29)</f>
         <v>210626569174</v>
       </c>
-      <c r="O16" s="17">
-        <f t="shared" si="3"/>
+      <c r="O16" s="16">
+        <f t="shared" si="4"/>
         <v>0.63369903651969928</v>
       </c>
     </row>
@@ -6003,7 +5351,7 @@
         <v>143150</v>
       </c>
       <c r="E17" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>82492.98265455816</v>
       </c>
       <c r="F17" s="8">
@@ -6014,36 +5362,33 @@
         <f>SUM($C$4:C17)/$C$32</f>
         <v>0.43904494627960178</v>
       </c>
-      <c r="H17" s="13">
+      <c r="H17" s="12">
         <f t="shared" si="0"/>
         <v>0.53846153846153832</v>
       </c>
-      <c r="I17" s="13">
+      <c r="I17" s="12">
         <f t="shared" si="1"/>
         <v>0.53846153846153832</v>
       </c>
-      <c r="J17" s="8">
-        <f t="shared" si="4"/>
-        <v>5.2995312593044966E-4</v>
-      </c>
-      <c r="K17" s="8">
-        <f t="shared" si="5"/>
-        <v>1.2037888617022138E-2</v>
-      </c>
-      <c r="L17" s="18">
+      <c r="J17" s="12">
+        <f t="shared" si="2"/>
+        <v>1.2567841742952588E-2</v>
+      </c>
+      <c r="K17" s="8"/>
+      <c r="L17" s="17">
         <f>SUM(D17:$D$29)</f>
         <v>1404131</v>
       </c>
-      <c r="M17" s="16">
-        <f t="shared" si="2"/>
+      <c r="M17" s="15">
+        <f t="shared" si="3"/>
         <v>0.29262099134660413</v>
       </c>
       <c r="N17" s="9">
         <f>SUM(C17:$C$29)</f>
         <v>198257060565</v>
       </c>
-      <c r="O17" s="17">
-        <f t="shared" si="3"/>
+      <c r="O17" s="16">
+        <f t="shared" si="4"/>
         <v>0.59648366659516738</v>
       </c>
     </row>
@@ -6061,7 +5406,7 @@
         <v>128672</v>
       </c>
       <c r="E18" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>87498.106814225321</v>
       </c>
       <c r="F18" s="8">
@@ -6072,36 +5417,33 @@
         <f>SUM($C$4:C18)/$C$32</f>
         <v>0.47291786350586495</v>
       </c>
-      <c r="H18" s="13">
+      <c r="H18" s="12">
         <f t="shared" si="0"/>
         <v>0.57692307692307676</v>
       </c>
-      <c r="I18" s="13">
+      <c r="I18" s="12">
         <f t="shared" si="1"/>
         <v>0.57692307692307676</v>
       </c>
-      <c r="J18" s="8">
-        <f t="shared" si="4"/>
-        <v>4.5415542490769771E-4</v>
-      </c>
-      <c r="K18" s="8">
-        <f t="shared" si="5"/>
-        <v>1.1773101371770267E-2</v>
-      </c>
-      <c r="L18" s="18">
+      <c r="J18" s="12">
+        <f t="shared" si="2"/>
+        <v>1.2227256796677964E-2</v>
+      </c>
+      <c r="K18" s="8"/>
+      <c r="L18" s="17">
         <f>SUM(D18:$D$29)</f>
         <v>1260981</v>
       </c>
-      <c r="M18" s="16">
-        <f t="shared" si="2"/>
+      <c r="M18" s="15">
+        <f t="shared" si="3"/>
         <v>0.26278852207467268</v>
       </c>
       <c r="N18" s="9">
         <f>SUM(C18:$C$29)</f>
         <v>186448190098</v>
       </c>
-      <c r="O18" s="17">
-        <f t="shared" si="3"/>
+      <c r="O18" s="16">
+        <f t="shared" si="4"/>
         <v>0.56095505372039822</v>
       </c>
     </row>
@@ -6119,7 +5461,7 @@
         <v>117057</v>
       </c>
       <c r="E19" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>92490.804351726081</v>
       </c>
       <c r="F19" s="8">
@@ -6130,36 +5472,33 @@
         <f>SUM($C$4:C19)/$C$32</f>
         <v>0.50549146950752899</v>
       </c>
-      <c r="H19" s="13">
+      <c r="H19" s="12">
         <f t="shared" si="0"/>
         <v>0.6153846153846152</v>
       </c>
-      <c r="I19" s="13">
+      <c r="I19" s="12">
         <f t="shared" si="1"/>
         <v>0.6153846153846152</v>
       </c>
-      <c r="J19" s="8">
-        <f t="shared" si="4"/>
-        <v>3.973114513685715E-4</v>
-      </c>
-      <c r="K19" s="8">
-        <f t="shared" si="5"/>
-        <v>1.1536682964608861E-2</v>
-      </c>
-      <c r="L19" s="18">
+      <c r="J19" s="12">
+        <f t="shared" si="2"/>
+        <v>1.1933994415977431E-2</v>
+      </c>
+      <c r="K19" s="8"/>
+      <c r="L19" s="17">
         <f>SUM(D19:$D$29)</f>
         <v>1132309</v>
       </c>
-      <c r="M19" s="16">
-        <f t="shared" si="2"/>
+      <c r="M19" s="15">
+        <f t="shared" si="3"/>
         <v>0.23597326894049198</v>
       </c>
       <c r="N19" s="9">
         <f>SUM(C19:$C$29)</f>
         <v>175189633698</v>
       </c>
-      <c r="O19" s="17">
-        <f t="shared" si="3"/>
+      <c r="O19" s="16">
+        <f t="shared" si="4"/>
         <v>0.52708213649413505</v>
       </c>
     </row>
@@ -6177,7 +5516,7 @@
         <v>105622</v>
       </c>
       <c r="E20" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>97494.50684516484</v>
       </c>
       <c r="F20" s="8">
@@ -6188,36 +5527,33 @@
         <f>SUM($C$4:C20)/$C$32</f>
         <v>0.5364731111832084</v>
       </c>
-      <c r="H20" s="13">
+      <c r="H20" s="12">
         <f t="shared" si="0"/>
         <v>0.65384615384615363</v>
       </c>
-      <c r="I20" s="13">
+      <c r="I20" s="12">
         <f t="shared" si="1"/>
         <v>0.65384615384615363</v>
       </c>
-      <c r="J20" s="8">
-        <f t="shared" si="4"/>
-        <v>3.4097824210258681E-4</v>
-      </c>
-      <c r="K20" s="8">
-        <f t="shared" si="5"/>
-        <v>1.112669202457625E-2</v>
-      </c>
-      <c r="L20" s="18">
+      <c r="J20" s="12">
+        <f t="shared" si="2"/>
+        <v>1.1467670266678836E-2</v>
+      </c>
+      <c r="K20" s="8"/>
+      <c r="L20" s="17">
         <f>SUM(D20:$D$29)</f>
         <v>1015252</v>
       </c>
-      <c r="M20" s="16">
-        <f t="shared" si="2"/>
+      <c r="M20" s="15">
+        <f t="shared" si="3"/>
         <v>0.21157858255862347</v>
       </c>
       <c r="N20" s="9">
         <f>SUM(C20:$C$29)</f>
         <v>164362937613</v>
       </c>
-      <c r="O20" s="17">
-        <f t="shared" si="3"/>
+      <c r="O20" s="16">
+        <f t="shared" si="4"/>
         <v>0.49450853049247107</v>
       </c>
     </row>
@@ -6235,7 +5571,7 @@
         <v>322166</v>
       </c>
       <c r="E21" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>109254.29067623524</v>
       </c>
       <c r="F21" s="8">
@@ -6246,36 +5582,33 @@
         <f>SUM($C$4:C21)/$C$32</f>
         <v>0.64237119451178382</v>
       </c>
-      <c r="H21" s="13">
+      <c r="H21" s="12">
         <f t="shared" si="0"/>
         <v>0.69230769230769207</v>
       </c>
-      <c r="I21" s="13">
+      <c r="I21" s="12">
         <f t="shared" si="1"/>
         <v>0.69230769230769207</v>
       </c>
-      <c r="J21" s="8">
-        <f t="shared" si="4"/>
-        <v>3.5549676962846094E-3</v>
-      </c>
-      <c r="K21" s="8">
-        <f t="shared" si="5"/>
-        <v>3.6018490991271523E-2</v>
-      </c>
-      <c r="L21" s="18">
+      <c r="J21" s="12">
+        <f t="shared" si="2"/>
+        <v>3.9573458687556136E-2</v>
+      </c>
+      <c r="K21" s="8"/>
+      <c r="L21" s="17">
         <f>SUM(D21:$D$29)</f>
         <v>909630</v>
       </c>
-      <c r="M21" s="16">
-        <f t="shared" si="2"/>
+      <c r="M21" s="15">
+        <f t="shared" si="3"/>
         <v>0.18956695091740836</v>
       </c>
       <c r="N21" s="9">
         <f>SUM(C21:$C$29)</f>
         <v>154065372811</v>
       </c>
-      <c r="O21" s="17">
-        <f t="shared" si="3"/>
+      <c r="O21" s="16">
+        <f t="shared" si="4"/>
         <v>0.46352688881679166</v>
       </c>
     </row>
@@ -6293,7 +5626,7 @@
         <v>261644</v>
       </c>
       <c r="E22" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>133176.33598706638</v>
       </c>
       <c r="F22" s="8">
@@ -6304,36 +5637,33 @@
         <f>SUM($C$4:C22)/$C$32</f>
         <v>0.74720654108725182</v>
       </c>
-      <c r="H22" s="13">
+      <c r="H22" s="12">
         <f t="shared" si="0"/>
         <v>0.7307692307692305</v>
       </c>
-      <c r="I22" s="13">
+      <c r="I22" s="12">
         <f t="shared" si="1"/>
         <v>0.7307692307692305</v>
       </c>
-      <c r="J22" s="8">
-        <f t="shared" si="4"/>
-        <v>2.8581588958164011E-3</v>
-      </c>
-      <c r="K22" s="8">
-        <f t="shared" si="5"/>
-        <v>3.5026334227614329E-2</v>
-      </c>
-      <c r="L22" s="18">
+      <c r="J22" s="12">
+        <f t="shared" si="2"/>
+        <v>3.7884493123430729E-2</v>
+      </c>
+      <c r="K22" s="8"/>
+      <c r="L22" s="17">
         <f>SUM(D22:$D$29)</f>
         <v>587464</v>
       </c>
-      <c r="M22" s="16">
-        <f t="shared" si="2"/>
+      <c r="M22" s="47">
+        <f t="shared" si="3"/>
         <v>0.12242753565047808</v>
       </c>
-      <c r="N22" s="9">
+      <c r="N22" s="55">
         <f>SUM(C22:$C$29)</f>
         <v>118867355001</v>
       </c>
-      <c r="O22" s="17">
-        <f t="shared" si="3"/>
+      <c r="O22" s="48">
+        <f t="shared" si="4"/>
         <v>0.35762880548821618</v>
       </c>
     </row>
@@ -6351,7 +5681,7 @@
         <v>176681</v>
       </c>
       <c r="E23" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>170511.66484228638</v>
       </c>
       <c r="F23" s="8">
@@ -6362,36 +5692,33 @@
         <f>SUM($C$4:C23)/$C$32</f>
         <v>0.83784527626943728</v>
       </c>
-      <c r="H23" s="13">
+      <c r="H23" s="12">
         <f t="shared" si="0"/>
         <v>0.76923076923076894</v>
       </c>
-      <c r="I23" s="13">
+      <c r="I23" s="12">
         <f t="shared" si="1"/>
         <v>0.76923076923076894</v>
       </c>
-      <c r="J23" s="8">
-        <f t="shared" si="4"/>
-        <v>1.6686741536533409E-3</v>
-      </c>
-      <c r="K23" s="8">
-        <f t="shared" si="5"/>
-        <v>2.7512392798660114E-2</v>
-      </c>
-      <c r="L23" s="18">
+      <c r="J23" s="12">
+        <f t="shared" si="2"/>
+        <v>2.9181066952313452E-2</v>
+      </c>
+      <c r="K23" s="8"/>
+      <c r="L23" s="17">
         <f>SUM(D23:$D$29)</f>
         <v>325820</v>
       </c>
-      <c r="M23" s="16">
-        <f t="shared" si="2"/>
+      <c r="M23" s="47">
+        <f t="shared" si="3"/>
         <v>6.7900909103602552E-2</v>
       </c>
-      <c r="N23" s="9">
+      <c r="N23" s="55">
         <f>SUM(C23:$C$29)</f>
         <v>84022565748</v>
       </c>
-      <c r="O23" s="17">
-        <f t="shared" si="3"/>
+      <c r="O23" s="48">
+        <f t="shared" si="4"/>
         <v>0.25279345891274818</v>
       </c>
     </row>
@@ -6409,7 +5736,7 @@
         <v>95219</v>
       </c>
       <c r="E24" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>237705.86106764406</v>
       </c>
       <c r="F24" s="8">
@@ -6420,36 +5747,33 @@
         <f>SUM($C$4:C24)/$C$32</f>
         <v>0.90594312610148842</v>
       </c>
-      <c r="H24" s="13">
+      <c r="H24" s="12">
         <f t="shared" si="0"/>
         <v>0.80769230769230738</v>
       </c>
-      <c r="I24" s="13">
+      <c r="I24" s="12">
         <f t="shared" si="1"/>
         <v>0.80769230769230738</v>
       </c>
-      <c r="J24" s="8">
-        <f t="shared" si="4"/>
-        <v>6.7565480479458311E-4</v>
-      </c>
-      <c r="K24" s="8">
-        <f t="shared" si="5"/>
-        <v>1.6625904870184335E-2</v>
-      </c>
-      <c r="L24" s="18">
+      <c r="J24" s="12">
+        <f t="shared" si="2"/>
+        <v>1.7301559674978918E-2</v>
+      </c>
+      <c r="K24" s="8"/>
+      <c r="L24" s="17">
         <f>SUM(D24:$D$29)</f>
         <v>149139</v>
       </c>
-      <c r="M24" s="16">
-        <f t="shared" si="2"/>
+      <c r="M24" s="15">
+        <f t="shared" si="3"/>
         <v>3.1080577259843412E-2</v>
       </c>
-      <c r="N24" s="9">
+      <c r="N24" s="55">
         <f>SUM(C24:$C$29)</f>
         <v>53896394292</v>
       </c>
-      <c r="O24" s="17">
-        <f t="shared" si="3"/>
+      <c r="O24" s="16">
+        <f t="shared" si="4"/>
         <v>0.16215472373056269</v>
       </c>
     </row>
@@ -6467,7 +5791,7 @@
         <v>26610</v>
       </c>
       <c r="E25" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>341609.32333709131</v>
       </c>
       <c r="F25" s="8">
@@ -6478,36 +5802,33 @@
         <f>SUM($C$4:C25)/$C$32</f>
         <v>0.93329231700701554</v>
       </c>
-      <c r="H25" s="13">
+      <c r="H25" s="12">
         <f t="shared" si="0"/>
         <v>0.84615384615384581</v>
       </c>
-      <c r="I25" s="13">
+      <c r="I25" s="12">
         <f t="shared" si="1"/>
         <v>0.84615384615384581</v>
       </c>
-      <c r="J25" s="8">
-        <f t="shared" si="4"/>
-        <v>7.5832820842431747E-5</v>
-      </c>
-      <c r="K25" s="8">
-        <f t="shared" si="5"/>
-        <v>5.0239309098685462E-3</v>
-      </c>
-      <c r="L25" s="18">
+      <c r="J25" s="12">
+        <f t="shared" si="2"/>
+        <v>5.099763730710978E-3</v>
+      </c>
+      <c r="K25" s="8"/>
+      <c r="L25" s="17">
         <f>SUM(D25:$D$29)</f>
         <v>53920</v>
       </c>
-      <c r="M25" s="16">
-        <f t="shared" si="2"/>
+      <c r="M25" s="51">
+        <f t="shared" si="3"/>
         <v>1.1236931492438307E-2</v>
       </c>
-      <c r="N25" s="9">
+      <c r="N25" s="55">
         <f>SUM(C25:$C$29)</f>
         <v>31262279907</v>
       </c>
-      <c r="O25" s="17">
-        <f t="shared" si="3"/>
+      <c r="O25" s="52">
+        <f t="shared" si="4"/>
         <v>9.4056873898511625E-2</v>
       </c>
     </row>
@@ -6525,7 +5846,7 @@
         <v>10859</v>
       </c>
       <c r="E26" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>443446.19854498573</v>
       </c>
       <c r="F26" s="8">
@@ -6536,36 +5857,33 @@
         <f>SUM($C$4:C26)/$C$32</f>
         <v>0.9477800576417319</v>
       </c>
-      <c r="H26" s="13">
+      <c r="H26" s="12">
         <f t="shared" si="0"/>
         <v>0.88461538461538425</v>
       </c>
-      <c r="I26" s="13">
+      <c r="I26" s="12">
         <f t="shared" si="1"/>
         <v>0.88461538461538425</v>
       </c>
-      <c r="J26" s="8">
-        <f>((F26-F25)*(G26-G25))/2</f>
-        <v>1.6392996627501861E-5</v>
-      </c>
-      <c r="K26" s="8">
-        <f t="shared" si="5"/>
-        <v>2.1120557291739415E-3</v>
-      </c>
-      <c r="L26" s="18">
+      <c r="J26" s="12">
+        <f t="shared" si="2"/>
+        <v>2.1284487258014435E-3</v>
+      </c>
+      <c r="K26" s="8"/>
+      <c r="L26" s="17">
         <f>SUM(D26:$D$29)</f>
         <v>27310</v>
       </c>
-      <c r="M26" s="16">
-        <f t="shared" si="2"/>
+      <c r="M26" s="51">
+        <f t="shared" si="3"/>
         <v>5.6914057688889127E-3</v>
       </c>
-      <c r="N26" s="9">
+      <c r="N26" s="55">
         <f>SUM(C26:$C$29)</f>
         <v>22172055813</v>
       </c>
-      <c r="O26" s="17">
-        <f t="shared" si="3"/>
+      <c r="O26" s="52">
+        <f t="shared" si="4"/>
         <v>6.6707682992984421E-2</v>
       </c>
     </row>
@@ -6583,7 +5901,7 @@
         <v>12535</v>
       </c>
       <c r="E27" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>659861.43581970478</v>
       </c>
       <c r="F27" s="8">
@@ -6594,36 +5912,33 @@
         <f>SUM($C$4:C27)/$C$32</f>
         <v>0.97266559248409601</v>
       </c>
-      <c r="H27" s="13">
+      <c r="H27" s="12">
         <f t="shared" si="0"/>
         <v>0.92307692307692268</v>
       </c>
-      <c r="I27" s="13">
+      <c r="I27" s="12">
         <f t="shared" si="1"/>
         <v>0.92307692307692268</v>
       </c>
-      <c r="J27" s="8">
-        <f t="shared" si="4"/>
-        <v>3.2504176780048193E-5</v>
-      </c>
-      <c r="K27" s="8">
-        <f t="shared" si="5"/>
-        <v>2.4758809274009956E-3</v>
-      </c>
-      <c r="L27" s="18">
+      <c r="J27" s="12">
+        <f t="shared" si="2"/>
+        <v>2.5083851041810437E-3</v>
+      </c>
+      <c r="K27" s="8"/>
+      <c r="L27" s="17">
         <f>SUM(D27:$D$29)</f>
         <v>16451</v>
       </c>
-      <c r="M27" s="16">
-        <f t="shared" si="2"/>
+      <c r="M27" s="15">
+        <f t="shared" si="3"/>
         <v>3.4283894655434458E-3</v>
       </c>
       <c r="N27" s="9">
         <f>SUM(C27:$C$29)</f>
         <v>17356673543</v>
       </c>
-      <c r="O27" s="17">
-        <f t="shared" si="3"/>
+      <c r="O27" s="16">
+        <f>N27/C$32</f>
         <v>5.2219942358268129E-2</v>
       </c>
     </row>
@@ -6641,7 +5956,7 @@
         <v>2797</v>
       </c>
       <c r="E28" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1338182.8208795139</v>
       </c>
       <c r="F28" s="8">
@@ -6652,36 +5967,33 @@
         <f>SUM($C$4:C28)/$C$32</f>
         <v>0.98392661455642405</v>
       </c>
-      <c r="H28" s="13">
+      <c r="H28" s="12">
         <f t="shared" si="0"/>
         <v>0.96153846153846112</v>
       </c>
-      <c r="I28" s="13">
+      <c r="I28" s="12">
         <f t="shared" si="1"/>
         <v>0.96153846153846112</v>
       </c>
-      <c r="J28" s="8">
-        <f t="shared" si="4"/>
-        <v>3.2819966243668675E-6</v>
-      </c>
-      <c r="K28" s="8">
-        <f t="shared" si="5"/>
-        <v>5.6696189220960236E-4</v>
-      </c>
-      <c r="L28" s="18">
+      <c r="J28" s="12">
+        <f t="shared" si="2"/>
+        <v>5.7024388883396922E-4</v>
+      </c>
+      <c r="K28" s="8"/>
+      <c r="L28" s="17">
         <f>SUM(D28:$D$29)</f>
         <v>3916</v>
       </c>
-      <c r="M28" s="16">
-        <f t="shared" si="2"/>
+      <c r="M28" s="15">
+        <f t="shared" si="3"/>
         <v>8.1609465364221832E-4</v>
       </c>
       <c r="N28" s="9">
         <f>SUM(C28:$C$29)</f>
         <v>9085310445</v>
       </c>
-      <c r="O28" s="17">
-        <f t="shared" si="3"/>
+      <c r="O28" s="16">
+        <f t="shared" si="4"/>
         <v>2.7334407515904005E-2</v>
       </c>
     </row>
@@ -6690,7 +6002,7 @@
         <v>2000001</v>
       </c>
       <c r="B29" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C29" s="6">
         <v>5342413095</v>
@@ -6699,7 +6011,7 @@
         <v>1119</v>
       </c>
       <c r="E29" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>4774274.4369973186</v>
       </c>
       <c r="F29" s="8">
@@ -6710,42 +6022,39 @@
         <f>SUM($C$4:C29)/$C$32</f>
         <v>1</v>
       </c>
-      <c r="H29" s="13">
+      <c r="H29" s="12">
         <f t="shared" si="0"/>
         <v>0.99999999999999956</v>
       </c>
-      <c r="I29" s="13">
+      <c r="I29" s="12">
         <f t="shared" si="1"/>
         <v>0.99999999999999956</v>
       </c>
-      <c r="J29" s="8">
-        <f>((F29-F28)*(G29-G28))/2</f>
-        <v>1.8741541105311322E-6</v>
-      </c>
-      <c r="K29" s="8">
-        <f t="shared" si="5"/>
-        <v>2.294513642574168E-4</v>
-      </c>
-      <c r="L29" s="18">
+      <c r="J29" s="12">
+        <f>((G29+G28)*(F29-F28))/2</f>
+        <v>2.3132551836794793E-4</v>
+      </c>
+      <c r="K29" s="8"/>
+      <c r="L29" s="17">
         <f>SUM(D29:$D$29)</f>
         <v>1119</v>
       </c>
-      <c r="M29" s="16">
-        <f t="shared" si="2"/>
+      <c r="M29" s="15">
+        <f t="shared" si="3"/>
         <v>2.3319967247845821E-4</v>
       </c>
       <c r="N29" s="9">
         <f>SUM(C29:$C$29)</f>
         <v>5342413095</v>
       </c>
-      <c r="O29" s="17">
-        <f t="shared" si="3"/>
+      <c r="O29" s="16">
+        <f t="shared" si="4"/>
         <v>1.6073385443575998E-2</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B30" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C30" s="6">
         <v>332376344346</v>
@@ -6759,23 +6068,23 @@
       </c>
       <c r="F30" s="8"/>
       <c r="G30" s="8"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="13"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
       <c r="J30" s="8"/>
       <c r="K30" s="8"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="N31" t="s">
-        <v>25</v>
-      </c>
-      <c r="O31" s="10" t="e">
-        <f>#REF!+((#REF!-#REF!)*(0.001-#REF!)/(#REF!-#REF!))</f>
-        <v>#REF!</v>
+      <c r="N31" s="49" t="s">
+        <v>40</v>
+      </c>
+      <c r="O31" s="50">
+        <f>O23+((O22-O23)*(0.1-M23)/(M22-M23))</f>
+        <v>0.31450861592852919</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B32" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C32" s="9">
         <f>SUM(C4:C29)</f>
@@ -6785,46 +6094,19 @@
         <f>SUM(D4:D29)</f>
         <v>4798463</v>
       </c>
-      <c r="I32" t="s">
-        <v>15</v>
-      </c>
-      <c r="J32" s="8">
-        <f>SUM(J5:J30)</f>
-        <v>1.9372463865715183E-2</v>
-      </c>
-      <c r="N32" t="s">
-        <v>17</v>
-      </c>
-      <c r="O32" s="10">
-        <f>O27+((O26-O27)*(0.01-M27)/(M26-M27))</f>
-        <v>9.4291132404414987E-2</v>
-      </c>
-    </row>
-    <row r="33" spans="9:10" x14ac:dyDescent="0.35">
-      <c r="I33" t="s">
-        <v>16</v>
-      </c>
-      <c r="J33" s="8">
-        <f>SUM(K5:K30)</f>
-        <v>0.25720121848286576</v>
-      </c>
-    </row>
-    <row r="34" spans="9:10" x14ac:dyDescent="0.35">
-      <c r="I34" t="s">
-        <v>18</v>
-      </c>
-      <c r="J34" s="8">
-        <f>J32+J33</f>
-        <v>0.27657368234858093</v>
-      </c>
-    </row>
-    <row r="35" spans="9:10" x14ac:dyDescent="0.35">
-      <c r="I35" t="s">
-        <v>19</v>
-      </c>
-      <c r="J35" s="8">
-        <f>1-(2*J34)</f>
-        <v>0.44685263530283814</v>
+      <c r="I32" s="34" t="s">
+        <v>38</v>
+      </c>
+      <c r="J32" s="34">
+        <f>1-2*SUM(J4:J29)</f>
+        <v>0.4435485140762182</v>
+      </c>
+      <c r="N32" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="O32" s="54">
+        <f>O26+((O25-O26)*(0.01-M26)/(M25-M26))</f>
+        <v>8.7956627103136245E-2</v>
       </c>
     </row>
   </sheetData>
@@ -6842,9 +6124,14 @@
   <dimension ref="A1:X32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="14.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.36328125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19.6328125" customWidth="1"/>
-    <col min="9" max="9" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -6855,7 +6142,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -6863,11 +6150,11 @@
       <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="46" t="s">
-        <v>67</v>
-      </c>
-      <c r="H1" s="47"/>
-      <c r="I1" s="48"/>
+      <c r="G1" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1" s="41"/>
+      <c r="I1" s="42"/>
     </row>
     <row r="2" spans="1:24" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1"/>
@@ -6875,27 +6162,27 @@
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
-      <c r="G2" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="H2" s="32" t="s">
-        <v>65</v>
-      </c>
-      <c r="I2" s="33" t="s">
-        <v>66</v>
-      </c>
-      <c r="K2" s="28" t="s">
-        <v>69</v>
-      </c>
-      <c r="R2" s="49" t="s">
-        <v>68</v>
-      </c>
-      <c r="S2" s="49"/>
-      <c r="T2" s="49"/>
-      <c r="U2" s="49"/>
-      <c r="V2" s="49"/>
-      <c r="W2" s="49"/>
-      <c r="X2" s="49"/>
+      <c r="G2" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="H2" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="K2" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="R2" s="43" t="s">
+        <v>34</v>
+      </c>
+      <c r="S2" s="43"/>
+      <c r="T2" s="43"/>
+      <c r="U2" s="43"/>
+      <c r="V2" s="43"/>
+      <c r="W2" s="43"/>
+      <c r="X2" s="43"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
@@ -6904,7 +6191,7 @@
       <c r="B3" s="1">
         <v>20000</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="10">
         <v>6349766510</v>
       </c>
       <c r="D3" s="1">
@@ -6914,15 +6201,15 @@
         <f>C3/D3</f>
         <v>7651.1599585014746</v>
       </c>
-      <c r="G3" s="35">
+      <c r="G3" s="31">
         <f>D3/D$29</f>
         <v>0.17295308935382017</v>
       </c>
-      <c r="H3" s="35">
+      <c r="H3" s="31">
         <f>C3/C$29</f>
         <v>1.9104146904600303E-2</v>
       </c>
-      <c r="I3" s="34">
+      <c r="I3" s="30">
         <f>H3*(LN(H3)- LN(G3))</f>
         <v>-4.2088632053942511E-2</v>
       </c>
@@ -6934,13 +6221,13 @@
         <f>I3</f>
         <v>-4.2088632053942511E-2</v>
       </c>
-      <c r="R3" s="49"/>
-      <c r="S3" s="49"/>
-      <c r="T3" s="49"/>
-      <c r="U3" s="49"/>
-      <c r="V3" s="49"/>
-      <c r="W3" s="49"/>
-      <c r="X3" s="49"/>
+      <c r="R3" s="43"/>
+      <c r="S3" s="43"/>
+      <c r="T3" s="43"/>
+      <c r="U3" s="43"/>
+      <c r="V3" s="43"/>
+      <c r="W3" s="43"/>
+      <c r="X3" s="43"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4">
@@ -6959,15 +6246,15 @@
         <f>C4/D4</f>
         <v>22595.920296283395</v>
       </c>
-      <c r="G4" s="36">
+      <c r="G4" s="32">
         <f>D4/D$29</f>
         <v>3.8292053101170107E-2</v>
       </c>
-      <c r="H4" s="36">
+      <c r="H4" s="32">
         <f t="shared" ref="H4:H27" si="0">C4/C$29</f>
         <v>1.2491388913881246E-2</v>
       </c>
-      <c r="I4" s="29">
+      <c r="I4" s="25">
         <f t="shared" ref="I4:I28" si="1">H4*(LN(H4)- LN(G4))</f>
         <v>-1.3992889634159102E-2</v>
       </c>
@@ -6979,13 +6266,13 @@
         <f>SUM($I$3:I4)</f>
         <v>-5.6081521688101613E-2</v>
       </c>
-      <c r="R4" s="49"/>
-      <c r="S4" s="49"/>
-      <c r="T4" s="49"/>
-      <c r="U4" s="49"/>
-      <c r="V4" s="49"/>
-      <c r="W4" s="49"/>
-      <c r="X4" s="49"/>
+      <c r="R4" s="43"/>
+      <c r="S4" s="43"/>
+      <c r="T4" s="43"/>
+      <c r="U4" s="43"/>
+      <c r="V4" s="43"/>
+      <c r="W4" s="43"/>
+      <c r="X4" s="43"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A5">
@@ -7004,15 +6291,15 @@
         <f>C5/D5</f>
         <v>27555.326444430561</v>
       </c>
-      <c r="G5" s="36">
+      <c r="G5" s="32">
         <f t="shared" ref="G5:G27" si="2">D5/D$29</f>
         <v>4.0022815639091103E-2</v>
       </c>
-      <c r="H5" s="36">
+      <c r="H5" s="32">
         <f t="shared" si="0"/>
         <v>1.592154623221665E-2</v>
       </c>
-      <c r="I5" s="29">
+      <c r="I5" s="25">
         <f>H5*(LN(H5)- LN(G5))</f>
         <v>-1.4676105276062229E-2</v>
       </c>
@@ -7024,13 +6311,13 @@
         <f>SUM($I$3:I5)</f>
         <v>-7.0757626964163836E-2</v>
       </c>
-      <c r="R5" s="49"/>
-      <c r="S5" s="49"/>
-      <c r="T5" s="49"/>
-      <c r="U5" s="49"/>
-      <c r="V5" s="49"/>
-      <c r="W5" s="49"/>
-      <c r="X5" s="49"/>
+      <c r="R5" s="43"/>
+      <c r="S5" s="43"/>
+      <c r="T5" s="43"/>
+      <c r="U5" s="43"/>
+      <c r="V5" s="43"/>
+      <c r="W5" s="43"/>
+      <c r="X5" s="43"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6">
@@ -7049,15 +6336,15 @@
         <f t="shared" ref="E6:E28" si="3">C6/D6</f>
         <v>32598.407319247046</v>
       </c>
-      <c r="G6" s="36">
+      <c r="G6" s="32">
         <f t="shared" si="2"/>
         <v>3.9047711736028806E-2</v>
       </c>
-      <c r="H6" s="36">
+      <c r="H6" s="32">
         <f t="shared" si="0"/>
         <v>1.8376551414987924E-2</v>
       </c>
-      <c r="I6" s="29">
+      <c r="I6" s="25">
         <f t="shared" si="1"/>
         <v>-1.3850568588215303E-2</v>
       </c>
@@ -7069,13 +6356,13 @@
         <f>SUM($I$3:I6)</f>
         <v>-8.460819555237914E-2</v>
       </c>
-      <c r="R6" s="49"/>
-      <c r="S6" s="49"/>
-      <c r="T6" s="49"/>
-      <c r="U6" s="49"/>
-      <c r="V6" s="49"/>
-      <c r="W6" s="49"/>
-      <c r="X6" s="49"/>
+      <c r="R6" s="43"/>
+      <c r="S6" s="43"/>
+      <c r="T6" s="43"/>
+      <c r="U6" s="43"/>
+      <c r="V6" s="43"/>
+      <c r="W6" s="43"/>
+      <c r="X6" s="43"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7">
@@ -7094,15 +6381,15 @@
         <f t="shared" si="3"/>
         <v>37613.401013270362</v>
       </c>
-      <c r="G7" s="36">
+      <c r="G7" s="32">
         <f t="shared" si="2"/>
         <v>4.4301477368899167E-2</v>
       </c>
-      <c r="H7" s="36">
+      <c r="H7" s="32">
         <f t="shared" si="0"/>
         <v>2.405652300476728E-2</v>
       </c>
-      <c r="I7" s="29">
+      <c r="I7" s="25">
         <f t="shared" si="1"/>
         <v>-1.4689197754153411E-2</v>
       </c>
@@ -7114,13 +6401,13 @@
         <f>SUM($I$3:I7)</f>
         <v>-9.9297393306532547E-2</v>
       </c>
-      <c r="R7" s="49"/>
-      <c r="S7" s="49"/>
-      <c r="T7" s="49"/>
-      <c r="U7" s="49"/>
-      <c r="V7" s="49"/>
-      <c r="W7" s="49"/>
-      <c r="X7" s="49"/>
+      <c r="R7" s="43"/>
+      <c r="S7" s="43"/>
+      <c r="T7" s="43"/>
+      <c r="U7" s="43"/>
+      <c r="V7" s="43"/>
+      <c r="W7" s="43"/>
+      <c r="X7" s="43"/>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A8">
@@ -7139,15 +6426,15 @@
         <f>C8/D8</f>
         <v>42587.165089635375</v>
       </c>
-      <c r="G8" s="36">
+      <c r="G8" s="32">
         <f t="shared" si="2"/>
         <v>5.1405210376739383E-2</v>
       </c>
-      <c r="H8" s="36">
+      <c r="H8" s="32">
         <f t="shared" si="0"/>
         <v>3.1605154345956149E-2</v>
       </c>
-      <c r="I8" s="29">
+      <c r="I8" s="25">
         <f t="shared" si="1"/>
         <v>-1.5373357591131214E-2</v>
       </c>
@@ -7159,13 +6446,13 @@
         <f>SUM($I$3:I8)</f>
         <v>-0.11467075089766376</v>
       </c>
-      <c r="R8" s="49"/>
-      <c r="S8" s="49"/>
-      <c r="T8" s="49"/>
-      <c r="U8" s="49"/>
-      <c r="V8" s="49"/>
-      <c r="W8" s="49"/>
-      <c r="X8" s="49"/>
+      <c r="R8" s="43"/>
+      <c r="S8" s="43"/>
+      <c r="T8" s="43"/>
+      <c r="U8" s="43"/>
+      <c r="V8" s="43"/>
+      <c r="W8" s="43"/>
+      <c r="X8" s="43"/>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A9">
@@ -7184,15 +6471,15 @@
         <f t="shared" si="3"/>
         <v>47570.903358611591</v>
       </c>
-      <c r="G9" s="36">
+      <c r="G9" s="32">
         <f t="shared" si="2"/>
         <v>5.5428790427268067E-2</v>
       </c>
-      <c r="H9" s="36">
+      <c r="H9" s="32">
         <f t="shared" si="0"/>
         <v>3.8067016784530283E-2</v>
       </c>
-      <c r="I9" s="29">
+      <c r="I9" s="25">
         <f t="shared" si="1"/>
         <v>-1.4303717170918728E-2</v>
       </c>
@@ -7204,13 +6491,13 @@
         <f>SUM($I$3:I9)</f>
         <v>-0.12897446806858248</v>
       </c>
-      <c r="R9" s="49"/>
-      <c r="S9" s="49"/>
-      <c r="T9" s="49"/>
-      <c r="U9" s="49"/>
-      <c r="V9" s="49"/>
-      <c r="W9" s="49"/>
-      <c r="X9" s="49"/>
+      <c r="R9" s="43"/>
+      <c r="S9" s="43"/>
+      <c r="T9" s="43"/>
+      <c r="U9" s="43"/>
+      <c r="V9" s="43"/>
+      <c r="W9" s="43"/>
+      <c r="X9" s="43"/>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10">
@@ -7229,15 +6516,15 @@
         <f t="shared" si="3"/>
         <v>52524.612759688869</v>
       </c>
-      <c r="G10" s="36">
+      <c r="G10" s="32">
         <f t="shared" si="2"/>
         <v>5.5031371503750266E-2</v>
       </c>
-      <c r="H10" s="36">
+      <c r="H10" s="32">
         <f t="shared" si="0"/>
         <v>4.17296977626107E-2</v>
       </c>
-      <c r="I10" s="29">
+      <c r="I10" s="25">
         <f t="shared" si="1"/>
         <v>-1.1546205167980323E-2</v>
       </c>
@@ -7249,13 +6536,13 @@
         <f>SUM($I$3:I10)</f>
         <v>-0.14052067323656281</v>
       </c>
-      <c r="R10" s="49"/>
-      <c r="S10" s="49"/>
-      <c r="T10" s="49"/>
-      <c r="U10" s="49"/>
-      <c r="V10" s="49"/>
-      <c r="W10" s="49"/>
-      <c r="X10" s="49"/>
+      <c r="R10" s="43"/>
+      <c r="S10" s="43"/>
+      <c r="T10" s="43"/>
+      <c r="U10" s="43"/>
+      <c r="V10" s="43"/>
+      <c r="W10" s="43"/>
+      <c r="X10" s="43"/>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A11">
@@ -7274,15 +6561,15 @@
         <f t="shared" si="3"/>
         <v>57520.93284973759</v>
       </c>
-      <c r="G11" s="36">
+      <c r="G11" s="32">
         <f t="shared" si="2"/>
         <v>5.1741359681214592E-2</v>
       </c>
-      <c r="H11" s="36">
+      <c r="H11" s="32">
         <f t="shared" si="0"/>
         <v>4.2967076116985602E-2</v>
       </c>
-      <c r="I11" s="29">
+      <c r="I11" s="25">
         <f t="shared" si="1"/>
         <v>-7.9842840818468257E-3</v>
       </c>
@@ -7294,13 +6581,13 @@
         <f>SUM($I$3:I11)</f>
         <v>-0.14850495731840962</v>
       </c>
-      <c r="R11" s="49"/>
-      <c r="S11" s="49"/>
-      <c r="T11" s="49"/>
-      <c r="U11" s="49"/>
-      <c r="V11" s="49"/>
-      <c r="W11" s="49"/>
-      <c r="X11" s="49"/>
+      <c r="R11" s="43"/>
+      <c r="S11" s="43"/>
+      <c r="T11" s="43"/>
+      <c r="U11" s="43"/>
+      <c r="V11" s="43"/>
+      <c r="W11" s="43"/>
+      <c r="X11" s="43"/>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A12">
@@ -7319,15 +6606,15 @@
         <f t="shared" si="3"/>
         <v>62499.12064609558</v>
       </c>
-      <c r="G12" s="36">
+      <c r="G12" s="32">
         <f t="shared" si="2"/>
         <v>4.6770184536173355E-2</v>
       </c>
-      <c r="H12" s="36">
+      <c r="H12" s="32">
         <f t="shared" si="0"/>
         <v>4.2200250979349818E-2</v>
       </c>
-      <c r="I12" s="29">
+      <c r="I12" s="25">
         <f t="shared" si="1"/>
         <v>-4.3390192108020186E-3</v>
       </c>
@@ -7339,13 +6626,13 @@
         <f>SUM($I$3:I12)</f>
         <v>-0.15284397652921164</v>
       </c>
-      <c r="R12" s="49"/>
-      <c r="S12" s="49"/>
-      <c r="T12" s="49"/>
-      <c r="U12" s="49"/>
-      <c r="V12" s="49"/>
-      <c r="W12" s="49"/>
-      <c r="X12" s="49"/>
+      <c r="R12" s="43"/>
+      <c r="S12" s="43"/>
+      <c r="T12" s="43"/>
+      <c r="U12" s="43"/>
+      <c r="V12" s="43"/>
+      <c r="W12" s="43"/>
+      <c r="X12" s="43"/>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A13">
@@ -7364,15 +6651,15 @@
         <f t="shared" si="3"/>
         <v>67493.293463938549</v>
       </c>
-      <c r="G13" s="36">
+      <c r="G13" s="32">
         <f t="shared" si="2"/>
         <v>4.1912379026367401E-2</v>
       </c>
-      <c r="H13" s="36">
+      <c r="H13" s="32">
         <f t="shared" si="0"/>
         <v>4.0838988531836401E-2</v>
       </c>
-      <c r="I13" s="29">
+      <c r="I13" s="25">
         <f t="shared" si="1"/>
         <v>-1.0595266803264201E-3</v>
       </c>
@@ -7384,13 +6671,13 @@
         <f>SUM($I$3:I13)</f>
         <v>-0.15390350320953805</v>
       </c>
-      <c r="R13" s="49"/>
-      <c r="S13" s="49"/>
-      <c r="T13" s="49"/>
-      <c r="U13" s="49"/>
-      <c r="V13" s="49"/>
-      <c r="W13" s="49"/>
-      <c r="X13" s="49"/>
+      <c r="R13" s="43"/>
+      <c r="S13" s="43"/>
+      <c r="T13" s="43"/>
+      <c r="U13" s="43"/>
+      <c r="V13" s="43"/>
+      <c r="W13" s="43"/>
+      <c r="X13" s="43"/>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A14">
@@ -7409,15 +6696,15 @@
         <f t="shared" si="3"/>
         <v>72494.92566019771</v>
       </c>
-      <c r="G14" s="36">
+      <c r="G14" s="32">
         <f t="shared" si="2"/>
         <v>3.72087895644918E-2</v>
       </c>
-      <c r="H14" s="36">
+      <c r="H14" s="32">
         <f t="shared" si="0"/>
         <v>3.8942622488578348E-2</v>
       </c>
-      <c r="I14" s="29">
+      <c r="I14" s="25">
         <f t="shared" si="1"/>
         <v>1.7736157508887016E-3</v>
       </c>
@@ -7429,13 +6716,13 @@
         <f>SUM($I$3:I14)</f>
         <v>-0.15212988745864936</v>
       </c>
-      <c r="R14" s="49"/>
-      <c r="S14" s="49"/>
-      <c r="T14" s="49"/>
-      <c r="U14" s="49"/>
-      <c r="V14" s="49"/>
-      <c r="W14" s="49"/>
-      <c r="X14" s="49"/>
+      <c r="R14" s="43"/>
+      <c r="S14" s="43"/>
+      <c r="T14" s="43"/>
+      <c r="U14" s="43"/>
+      <c r="V14" s="43"/>
+      <c r="W14" s="43"/>
+      <c r="X14" s="43"/>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A15">
@@ -7454,15 +6741,15 @@
         <f t="shared" si="3"/>
         <v>77495.903323622464</v>
       </c>
-      <c r="G15" s="36">
+      <c r="G15" s="32">
         <f t="shared" si="2"/>
         <v>3.3263776338381686E-2</v>
       </c>
-      <c r="H15" s="36">
+      <c r="H15" s="32">
         <f t="shared" si="0"/>
         <v>3.7215369924531942E-2</v>
       </c>
-      <c r="I15" s="29">
+      <c r="I15" s="25">
         <f t="shared" si="1"/>
         <v>4.1775309174201074E-3</v>
       </c>
@@ -7474,13 +6761,13 @@
         <f>SUM($I$3:I15)</f>
         <v>-0.14795235654122926</v>
       </c>
-      <c r="R15" s="49"/>
-      <c r="S15" s="49"/>
-      <c r="T15" s="49"/>
-      <c r="U15" s="49"/>
-      <c r="V15" s="49"/>
-      <c r="W15" s="49"/>
-      <c r="X15" s="49"/>
+      <c r="R15" s="43"/>
+      <c r="S15" s="43"/>
+      <c r="T15" s="43"/>
+      <c r="U15" s="43"/>
+      <c r="V15" s="43"/>
+      <c r="W15" s="43"/>
+      <c r="X15" s="43"/>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A16">
@@ -7499,15 +6786,15 @@
         <f t="shared" si="3"/>
         <v>82492.98265455816</v>
       </c>
-      <c r="G16" s="36">
+      <c r="G16" s="32">
         <f t="shared" si="2"/>
         <v>2.983246927193145E-2</v>
       </c>
-      <c r="H16" s="36">
+      <c r="H16" s="32">
         <f t="shared" si="0"/>
         <v>3.5528612874769147E-2</v>
       </c>
-      <c r="I16" s="29">
+      <c r="I16" s="25">
         <f t="shared" si="1"/>
         <v>6.2083051672566624E-3</v>
       </c>
@@ -7519,13 +6806,13 @@
         <f>SUM($I$3:I16)</f>
         <v>-0.14174405137397261</v>
       </c>
-      <c r="R16" s="49"/>
-      <c r="S16" s="49"/>
-      <c r="T16" s="49"/>
-      <c r="U16" s="49"/>
-      <c r="V16" s="49"/>
-      <c r="W16" s="49"/>
-      <c r="X16" s="49"/>
+      <c r="R16" s="43"/>
+      <c r="S16" s="43"/>
+      <c r="T16" s="43"/>
+      <c r="U16" s="43"/>
+      <c r="V16" s="43"/>
+      <c r="W16" s="43"/>
+      <c r="X16" s="43"/>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A17">
@@ -7544,15 +6831,15 @@
         <f t="shared" si="3"/>
         <v>87498.106814225321</v>
       </c>
-      <c r="G17" s="36">
+      <c r="G17" s="32">
         <f t="shared" si="2"/>
         <v>2.6815253134180674E-2</v>
       </c>
-      <c r="H17" s="36">
+      <c r="H17" s="32">
         <f t="shared" si="0"/>
         <v>3.3872917226263163E-2</v>
       </c>
-      <c r="I17" s="29">
+      <c r="I17" s="25">
         <f t="shared" si="1"/>
         <v>7.9142350626663863E-3</v>
       </c>
@@ -7564,13 +6851,13 @@
         <f>SUM($I$3:I17)</f>
         <v>-0.13382981631130622</v>
       </c>
-      <c r="R17" s="49"/>
-      <c r="S17" s="49"/>
-      <c r="T17" s="49"/>
-      <c r="U17" s="49"/>
-      <c r="V17" s="49"/>
-      <c r="W17" s="49"/>
-      <c r="X17" s="49"/>
+      <c r="R17" s="43"/>
+      <c r="S17" s="43"/>
+      <c r="T17" s="43"/>
+      <c r="U17" s="43"/>
+      <c r="V17" s="43"/>
+      <c r="W17" s="43"/>
+      <c r="X17" s="43"/>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A18">
@@ -7589,15 +6876,15 @@
         <f t="shared" si="3"/>
         <v>92490.804351726081</v>
       </c>
-      <c r="G18" s="36">
+      <c r="G18" s="32">
         <f t="shared" si="2"/>
         <v>2.4394686381868529E-2</v>
       </c>
-      <c r="H18" s="36">
+      <c r="H18" s="32">
         <f t="shared" si="0"/>
         <v>3.2573606001663979E-2</v>
       </c>
-      <c r="I18" s="29">
+      <c r="I18" s="25">
         <f t="shared" si="1"/>
         <v>9.4182344332991354E-3</v>
       </c>
@@ -7609,13 +6896,13 @@
         <f>SUM($I$3:I18)</f>
         <v>-0.12441158187800709</v>
       </c>
-      <c r="R18" s="49"/>
-      <c r="S18" s="49"/>
-      <c r="T18" s="49"/>
-      <c r="U18" s="49"/>
-      <c r="V18" s="49"/>
-      <c r="W18" s="49"/>
-      <c r="X18" s="49"/>
+      <c r="R18" s="43"/>
+      <c r="S18" s="43"/>
+      <c r="T18" s="43"/>
+      <c r="U18" s="43"/>
+      <c r="V18" s="43"/>
+      <c r="W18" s="43"/>
+      <c r="X18" s="43"/>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A19">
@@ -7634,15 +6921,15 @@
         <f t="shared" si="3"/>
         <v>97494.50684516484</v>
       </c>
-      <c r="G19" s="36">
+      <c r="G19" s="32">
         <f>D19/D$29</f>
         <v>2.2011631641215113E-2</v>
       </c>
-      <c r="H19" s="36">
+      <c r="H19" s="32">
         <f t="shared" si="0"/>
         <v>3.0981641675679399E-2</v>
       </c>
-      <c r="I19" s="29">
+      <c r="I19" s="25">
         <f t="shared" si="1"/>
         <v>1.0590262501714576E-2</v>
       </c>
@@ -7654,13 +6941,13 @@
         <f>SUM($I$3:I19)</f>
         <v>-0.11382131937629252</v>
       </c>
-      <c r="R19" s="49"/>
-      <c r="S19" s="49"/>
-      <c r="T19" s="49"/>
-      <c r="U19" s="49"/>
-      <c r="V19" s="49"/>
-      <c r="W19" s="49"/>
-      <c r="X19" s="49"/>
+      <c r="R19" s="43"/>
+      <c r="S19" s="43"/>
+      <c r="T19" s="43"/>
+      <c r="U19" s="43"/>
+      <c r="V19" s="43"/>
+      <c r="W19" s="43"/>
+      <c r="X19" s="43"/>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A20">
@@ -7679,15 +6966,15 @@
         <f t="shared" si="3"/>
         <v>109254.29067623524</v>
       </c>
-      <c r="G20" s="36">
+      <c r="G20" s="32">
         <f t="shared" si="2"/>
         <v>6.7139415266930264E-2</v>
       </c>
-      <c r="H20" s="36">
+      <c r="H20" s="32">
         <f t="shared" si="0"/>
         <v>0.10589808332857546</v>
       </c>
-      <c r="I20" s="29">
+      <c r="I20" s="25">
         <f t="shared" si="1"/>
         <v>4.8258378322750033E-2</v>
       </c>
@@ -7717,15 +7004,15 @@
         <f t="shared" si="3"/>
         <v>133176.33598706638</v>
       </c>
-      <c r="G21" s="36">
+      <c r="G21" s="32">
         <f t="shared" si="2"/>
         <v>5.4526626546875533E-2</v>
       </c>
-      <c r="H21" s="36">
+      <c r="H21" s="32">
         <f t="shared" si="0"/>
         <v>0.10483534657546799</v>
       </c>
-      <c r="I21" s="29">
+      <c r="I21" s="25">
         <f t="shared" si="1"/>
         <v>6.8531059860244811E-2</v>
       </c>
@@ -7755,15 +7042,15 @@
         <f t="shared" si="3"/>
         <v>170511.66484228638</v>
       </c>
-      <c r="G22" s="36">
+      <c r="G22" s="32">
         <f t="shared" si="2"/>
         <v>3.6820331843759137E-2</v>
       </c>
-      <c r="H22" s="36">
+      <c r="H22" s="32">
         <f t="shared" si="0"/>
         <v>9.0638735182185529E-2</v>
       </c>
-      <c r="I22" s="29">
+      <c r="I22" s="25">
         <f t="shared" si="1"/>
         <v>8.1650225412226426E-2</v>
       </c>
@@ -7793,15 +7080,15 @@
         <f t="shared" si="3"/>
         <v>237705.86106764406</v>
       </c>
-      <c r="G23" s="36">
+      <c r="G23" s="32">
         <f t="shared" si="2"/>
         <v>1.9843645767405105E-2</v>
       </c>
-      <c r="H23" s="36">
+      <c r="H23" s="32">
         <f t="shared" si="0"/>
         <v>6.8097849832051055E-2</v>
       </c>
-      <c r="I23" s="29">
+      <c r="I23" s="25">
         <f t="shared" si="1"/>
         <v>8.3968856987618093E-2</v>
       </c>
@@ -7831,15 +7118,15 @@
         <f t="shared" si="3"/>
         <v>341609.32333709131</v>
       </c>
-      <c r="G24" s="36">
+      <c r="G24" s="32">
         <f t="shared" si="2"/>
         <v>5.5455257235493948E-3</v>
       </c>
-      <c r="H24" s="36">
+      <c r="H24" s="32">
         <f t="shared" si="0"/>
         <v>2.7349190905527201E-2</v>
       </c>
-      <c r="I24" s="29">
+      <c r="I24" s="25">
         <f t="shared" si="1"/>
         <v>4.3640981369792477E-2</v>
       </c>
@@ -7869,15 +7156,15 @@
         <f t="shared" si="3"/>
         <v>443446.19854498573</v>
       </c>
-      <c r="G25" s="36">
+      <c r="G25" s="32">
         <f t="shared" si="2"/>
         <v>2.2630163033454669E-3</v>
       </c>
-      <c r="H25" s="36">
+      <c r="H25" s="32">
         <f t="shared" si="0"/>
         <v>1.4487740634716296E-2</v>
       </c>
-      <c r="I25" s="29">
+      <c r="I25" s="25">
         <f t="shared" si="1"/>
         <v>2.6898000797825308E-2</v>
       </c>
@@ -7907,15 +7194,15 @@
         <f t="shared" si="3"/>
         <v>659861.43581970478</v>
       </c>
-      <c r="G26" s="36">
+      <c r="G26" s="32">
         <f t="shared" si="2"/>
         <v>2.6122948119012275E-3</v>
       </c>
-      <c r="H26" s="36">
+      <c r="H26" s="32">
         <f t="shared" si="0"/>
         <v>2.4885534842364127E-2</v>
       </c>
-      <c r="I26" s="29">
+      <c r="I26" s="25">
         <f t="shared" si="1"/>
         <v>5.6093429721222138E-2</v>
       </c>
@@ -7945,15 +7232,15 @@
         <f t="shared" si="3"/>
         <v>1338182.8208795139</v>
       </c>
-      <c r="G27" s="36">
+      <c r="G27" s="32">
         <f t="shared" si="2"/>
         <v>5.8289498116376019E-4</v>
       </c>
-      <c r="H27" s="36">
+      <c r="H27" s="32">
         <f t="shared" si="0"/>
         <v>1.1261022072328007E-2</v>
       </c>
-      <c r="I27" s="29">
+      <c r="I27" s="25">
         <f t="shared" si="1"/>
         <v>3.3344963279958083E-2</v>
       </c>
@@ -7971,7 +7258,7 @@
         <v>2000001</v>
       </c>
       <c r="B28" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C28" s="6">
         <v>5342413095</v>
@@ -7983,15 +7270,15 @@
         <f t="shared" si="3"/>
         <v>4774274.4369973186</v>
       </c>
-      <c r="G28" s="37">
+      <c r="G28" s="33">
         <f>D28/D$29</f>
         <v>2.3319967247845821E-4</v>
       </c>
-      <c r="H28" s="37">
+      <c r="H28" s="33">
         <f>C28/C$29</f>
         <v>1.6073385443575998E-2</v>
       </c>
-      <c r="I28" s="30">
+      <c r="I28" s="26">
         <f t="shared" si="1"/>
         <v>6.8039043302673324E-2</v>
       </c>
@@ -8006,7 +7293,7 @@
     </row>
     <row r="29" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B29" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C29" s="6">
         <v>332376344346</v>
@@ -8020,14 +7307,14 @@
       </c>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="I30" s="26" t="s">
-        <v>67</v>
+      <c r="I30" s="22" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
-      <c r="I31" s="27">
+      <c r="I31" s="23">
         <f>SUM(I3:I28)</f>
         <v>0.39660361967801816</v>
       </c>
@@ -8054,35 +7341,39 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="58.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="58.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.36328125" customWidth="1"/>
-    <col min="5" max="5" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.453125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="19.26953125" customWidth="1"/>
     <col min="12" max="12" width="20.6328125" customWidth="1"/>
-    <col min="14" max="14" width="13.08984375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="F1" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="40" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1" s="41"/>
-      <c r="L1" s="42" t="s">
-        <v>21</v>
-      </c>
-      <c r="M1" s="43"/>
-      <c r="N1" s="43"/>
-      <c r="O1" s="43"/>
-      <c r="P1" s="43"/>
-      <c r="Q1" s="43"/>
+      <c r="F1" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="K1" s="37"/>
+      <c r="L1" s="38" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="39"/>
+      <c r="N1" s="39"/>
+      <c r="O1" s="39"/>
+      <c r="P1" s="39"/>
+      <c r="Q1" s="39"/>
     </row>
     <row r="2" spans="1:17" ht="203" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -8092,7 +7383,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>2</v>
@@ -8112,21 +7403,21 @@
       <c r="I2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="44" t="s">
-        <v>70</v>
-      </c>
-      <c r="K2" s="45"/>
+      <c r="J2" s="45" t="s">
+        <v>36</v>
+      </c>
+      <c r="K2" s="46"/>
       <c r="L2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="N2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.35">
@@ -8149,25 +7440,25 @@
       </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
-      <c r="L3" s="12"/>
+      <c r="L3" s="11"/>
       <c r="M3" s="2"/>
       <c r="N3" s="5"/>
       <c r="O3" s="2"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A4" s="20">
+      <c r="A4" s="19">
         <v>0</v>
       </c>
-      <c r="B4" s="20">
+      <c r="B4" s="19">
         <v>20000</v>
       </c>
-      <c r="C4" s="21">
+      <c r="C4" s="20">
         <v>417323015</v>
       </c>
-      <c r="D4" s="20">
+      <c r="D4" s="19">
         <v>70498</v>
       </c>
-      <c r="E4" s="20">
+      <c r="E4" s="19">
         <f>C4/D4</f>
         <v>5919.6433232148429</v>
       </c>
@@ -8179,24 +7470,24 @@
         <f>SUM($C$4:C4)/$C$32</f>
         <v>2.5897284949558209E-2</v>
       </c>
-      <c r="H4" s="13">
+      <c r="H4" s="12">
         <f>H3+1/26</f>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="I4" s="13">
+      <c r="I4" s="12">
         <f>I3+1/26</f>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="J4" s="13">
+      <c r="J4" s="12">
         <f>((G3+G4)*(F4-F3))/2</f>
         <v>3.6431800019435167E-3</v>
       </c>
-      <c r="K4" s="14"/>
-      <c r="L4" s="15">
+      <c r="K4" s="13"/>
+      <c r="L4" s="14">
         <f>SUM(D4:$D$29)</f>
         <v>250565</v>
       </c>
-      <c r="M4" s="16">
+      <c r="M4" s="15">
         <f>L4/$D$32</f>
         <v>1</v>
       </c>
@@ -8204,7 +7495,7 @@
         <f>SUM(C4:$C$29)</f>
         <v>16114546981</v>
       </c>
-      <c r="O4" s="17">
+      <c r="O4" s="16">
         <f t="shared" ref="O4:O29" si="0">N4/C$32</f>
         <v>1</v>
       </c>
@@ -8234,24 +7525,24 @@
         <f>SUM($C$4:C5)/$C$32</f>
         <v>4.0123222561722724E-2</v>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="12">
         <f>H4+1/26</f>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="I5" s="13">
+      <c r="I5" s="12">
         <f t="shared" ref="H5:I29" si="1">I4+1/26</f>
         <v>7.6923076923076927E-2</v>
       </c>
-      <c r="J5" s="13">
+      <c r="J5" s="12">
         <f>((G4+G5)*(F5-F4))/2</f>
         <v>1.3316610259294563E-3</v>
       </c>
-      <c r="K5" s="14"/>
-      <c r="L5" s="18">
+      <c r="K5" s="13"/>
+      <c r="L5" s="17">
         <f>SUM(D5:$D$29)</f>
         <v>180067</v>
       </c>
-      <c r="M5" s="16">
+      <c r="M5" s="15">
         <f t="shared" ref="M5:M29" si="2">L5/$D$32</f>
         <v>0.71864386486540421</v>
       </c>
@@ -8259,7 +7550,7 @@
         <f>SUM(C5:$C$29)</f>
         <v>15697223966</v>
       </c>
-      <c r="O5" s="17">
+      <c r="O5" s="16">
         <f t="shared" si="0"/>
         <v>0.97410271505044177</v>
       </c>
@@ -8289,24 +7580,24 @@
         <f>SUM($C$4:C6)/$C$32</f>
         <v>5.9077249526311083E-2</v>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="12">
         <f>H5+1/26</f>
         <v>0.11538461538461539</v>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="12">
         <f t="shared" si="1"/>
         <v>0.11538461538461539</v>
       </c>
-      <c r="J6" s="13">
+      <c r="J6" s="12">
         <f t="shared" ref="J6:J29" si="3">((G5+G6)*(F6-F5))/2</f>
         <v>2.189366474355265E-3</v>
       </c>
-      <c r="K6" s="14"/>
-      <c r="L6" s="18">
+      <c r="K6" s="13"/>
+      <c r="L6" s="17">
         <f>SUM(D6:$D$29)</f>
         <v>169959</v>
       </c>
-      <c r="M6" s="16">
+      <c r="M6" s="15">
         <f t="shared" si="2"/>
         <v>0.67830303514058232</v>
       </c>
@@ -8314,7 +7605,7 @@
         <f>SUM(C6:$C$29)</f>
         <v>15467979426</v>
       </c>
-      <c r="O6" s="17">
+      <c r="O6" s="16">
         <f t="shared" si="0"/>
         <v>0.95987677743827726</v>
       </c>
@@ -8344,24 +7635,24 @@
         <f>SUM($C$4:C7)/$C$32</f>
         <v>7.8145537102890031E-2</v>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="12">
         <f t="shared" si="1"/>
         <v>0.15384615384615385</v>
       </c>
-      <c r="I7" s="13">
+      <c r="I7" s="12">
         <f t="shared" si="1"/>
         <v>0.15384615384615385</v>
       </c>
-      <c r="J7" s="13">
+      <c r="J7" s="12">
         <f t="shared" si="3"/>
         <v>2.5805430550826956E-3</v>
       </c>
-      <c r="K7" s="14"/>
-      <c r="L7" s="18">
+      <c r="K7" s="13"/>
+      <c r="L7" s="17">
         <f>SUM(D7:$D$29)</f>
         <v>158899</v>
       </c>
-      <c r="M7" s="16">
+      <c r="M7" s="15">
         <f t="shared" si="2"/>
         <v>0.63416279208987691</v>
       </c>
@@ -8369,7 +7660,7 @@
         <f>SUM(C7:$C$29)</f>
         <v>15162543868</v>
       </c>
-      <c r="O7" s="17">
+      <c r="O7" s="16">
         <f t="shared" si="0"/>
         <v>0.9409227504736889</v>
       </c>
@@ -8388,7 +7679,7 @@
         <v>9839</v>
       </c>
       <c r="E8" s="7">
-        <f t="shared" ref="E7:E29" si="4">C8/D8</f>
+        <f t="shared" ref="E8:E29" si="4">C8/D8</f>
         <v>37622.962699461328</v>
       </c>
       <c r="F8" s="8">
@@ -8399,24 +7690,24 @@
         <f>SUM($C$4:C8)/$C$32</f>
         <v>0.10111685180608677</v>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="12">
         <f t="shared" si="1"/>
         <v>0.19230769230769232</v>
       </c>
-      <c r="I8" s="13">
+      <c r="I8" s="12">
         <f t="shared" si="1"/>
         <v>0.19230769230769232</v>
       </c>
-      <c r="J8" s="13">
+      <c r="J8" s="12">
         <f t="shared" si="3"/>
         <v>3.5195710583589509E-3</v>
       </c>
-      <c r="K8" s="14"/>
-      <c r="L8" s="18">
+      <c r="K8" s="13"/>
+      <c r="L8" s="17">
         <f>SUM(D8:$D$29)</f>
         <v>149475</v>
       </c>
-      <c r="M8" s="16">
+      <c r="M8" s="15">
         <f t="shared" si="2"/>
         <v>0.5965517929479377</v>
       </c>
@@ -8424,7 +7715,7 @@
         <f>SUM(C8:$C$29)</f>
         <v>14855267052</v>
       </c>
-      <c r="O8" s="17">
+      <c r="O8" s="16">
         <f t="shared" si="0"/>
         <v>0.92185446289710993</v>
       </c>
@@ -8454,24 +7745,24 @@
         <f>SUM($C$4:C9)/$C$32</f>
         <v>0.1279567556215622</v>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="12">
         <f t="shared" si="1"/>
         <v>0.23076923076923078</v>
       </c>
-      <c r="I9" s="13">
+      <c r="I9" s="12">
         <f t="shared" si="1"/>
         <v>0.23076923076923078</v>
       </c>
-      <c r="J9" s="13">
+      <c r="J9" s="12">
         <f t="shared" si="3"/>
         <v>4.6419940602793249E-3</v>
       </c>
-      <c r="K9" s="14"/>
-      <c r="L9" s="18">
+      <c r="K9" s="13"/>
+      <c r="L9" s="17">
         <f>SUM(D9:$D$29)</f>
         <v>139636</v>
       </c>
-      <c r="M9" s="16">
+      <c r="M9" s="15">
         <f t="shared" si="2"/>
         <v>0.55728453694650093</v>
       </c>
@@ -8479,7 +7770,7 @@
         <f>SUM(C9:$C$29)</f>
         <v>14485094722</v>
       </c>
-      <c r="O9" s="17">
+      <c r="O9" s="16">
         <f t="shared" si="0"/>
         <v>0.89888314819391324</v>
       </c>
@@ -8509,24 +7800,24 @@
         <f>SUM($C$4:C10)/$C$32</f>
         <v>0.15819889885863866</v>
       </c>
-      <c r="H10" s="13">
+      <c r="H10" s="12">
         <f t="shared" si="1"/>
         <v>0.26923076923076927</v>
       </c>
-      <c r="I10" s="13">
+      <c r="I10" s="12">
         <f t="shared" si="1"/>
         <v>0.26923076923076927</v>
       </c>
-      <c r="J10" s="13">
+      <c r="J10" s="12">
         <f t="shared" si="3"/>
         <v>5.8443979079377652E-3</v>
       </c>
-      <c r="K10" s="14"/>
-      <c r="L10" s="18">
+      <c r="K10" s="13"/>
+      <c r="L10" s="17">
         <f>SUM(D10:$D$29)</f>
         <v>129481</v>
       </c>
-      <c r="M10" s="16">
+      <c r="M10" s="15">
         <f t="shared" si="2"/>
         <v>0.5167561311436154</v>
       </c>
@@ -8534,7 +7825,7 @@
         <f>SUM(C10:$C$29)</f>
         <v>14052581831</v>
       </c>
-      <c r="O10" s="17">
+      <c r="O10" s="16">
         <f t="shared" si="0"/>
         <v>0.87204324437843783</v>
       </c>
@@ -8564,24 +7855,24 @@
         <f>SUM($C$4:C11)/$C$32</f>
         <v>0.19055207066140237</v>
       </c>
-      <c r="H11" s="13">
+      <c r="H11" s="12">
         <f t="shared" si="1"/>
         <v>0.30769230769230771</v>
       </c>
-      <c r="I11" s="13">
+      <c r="I11" s="12">
         <f t="shared" si="1"/>
         <v>0.30769230769230771</v>
       </c>
-      <c r="J11" s="13">
+      <c r="J11" s="12">
         <f t="shared" si="3"/>
         <v>6.9029211315812054E-3</v>
       </c>
-      <c r="K11" s="14"/>
-      <c r="L11" s="18">
+      <c r="K11" s="13"/>
+      <c r="L11" s="17">
         <f>SUM(D11:$D$29)</f>
         <v>119246</v>
       </c>
-      <c r="M11" s="16">
+      <c r="M11" s="15">
         <f t="shared" si="2"/>
         <v>0.47590844690998346</v>
       </c>
@@ -8589,7 +7880,7 @@
         <f>SUM(C11:$C$29)</f>
         <v>13565243393</v>
       </c>
-      <c r="O11" s="17">
+      <c r="O11" s="16">
         <f t="shared" si="0"/>
         <v>0.84180110114136131</v>
       </c>
@@ -8619,24 +7910,24 @@
         <f>SUM($C$4:C12)/$C$32</f>
         <v>0.22698588736703129</v>
       </c>
-      <c r="H12" s="13">
+      <c r="H12" s="12">
         <f t="shared" si="1"/>
         <v>0.34615384615384615</v>
       </c>
-      <c r="I12" s="13">
+      <c r="I12" s="12">
         <f t="shared" si="1"/>
         <v>0.34615384615384615</v>
       </c>
-      <c r="J12" s="13">
+      <c r="J12" s="12">
         <f t="shared" si="3"/>
         <v>8.4969011952466672E-3</v>
       </c>
-      <c r="K12" s="14"/>
-      <c r="L12" s="18">
+      <c r="K12" s="13"/>
+      <c r="L12" s="17">
         <f>SUM(D12:$D$29)</f>
         <v>109327</v>
       </c>
-      <c r="M12" s="16">
+      <c r="M12" s="15">
         <f t="shared" si="2"/>
         <v>0.43632191247780017</v>
       </c>
@@ -8644,7 +7935,7 @@
         <f>SUM(C12:$C$29)</f>
         <v>13043886686</v>
       </c>
-      <c r="O12" s="17">
+      <c r="O12" s="16">
         <f t="shared" si="0"/>
         <v>0.80944792933859766</v>
       </c>
@@ -8674,24 +7965,24 @@
         <f>SUM($C$4:C13)/$C$32</f>
         <v>0.26286716796907017</v>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="12">
         <f t="shared" si="1"/>
         <v>0.38461538461538458</v>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="12">
         <f t="shared" si="1"/>
         <v>0.38461538461538458</v>
       </c>
-      <c r="J13" s="13">
+      <c r="J13" s="12">
         <f t="shared" si="3"/>
         <v>9.0359819678066128E-3</v>
       </c>
-      <c r="K13" s="14"/>
-      <c r="L13" s="18">
+      <c r="K13" s="13"/>
+      <c r="L13" s="17">
         <f>SUM(D13:$D$29)</f>
         <v>99129</v>
       </c>
-      <c r="M13" s="16">
+      <c r="M13" s="15">
         <f t="shared" si="2"/>
         <v>0.39562189451838842</v>
       </c>
@@ -8699,7 +7990,7 @@
         <f>SUM(C13:$C$29)</f>
         <v>12456772235</v>
       </c>
-      <c r="O13" s="17">
+      <c r="O13" s="16">
         <f t="shared" si="0"/>
         <v>0.77301411263296871</v>
       </c>
@@ -8729,24 +8020,24 @@
         <f>SUM($C$4:C14)/$C$32</f>
         <v>0.2987640192849676</v>
       </c>
-      <c r="H14" s="13">
+      <c r="H14" s="12">
         <f t="shared" si="1"/>
         <v>0.42307692307692302</v>
       </c>
-      <c r="I14" s="13">
+      <c r="I14" s="12">
         <f t="shared" si="1"/>
         <v>0.42307692307692302</v>
       </c>
-      <c r="J14" s="13">
+      <c r="J14" s="12">
         <f t="shared" si="3"/>
         <v>9.6012898473556447E-3</v>
       </c>
-      <c r="K14" s="14"/>
-      <c r="L14" s="18">
+      <c r="K14" s="13"/>
+      <c r="L14" s="17">
         <f>SUM(D14:$D$29)</f>
         <v>89885</v>
       </c>
-      <c r="M14" s="16">
+      <c r="M14" s="15">
         <f t="shared" si="2"/>
         <v>0.35872927184562886</v>
       </c>
@@ -8754,7 +8045,7 @@
         <f>SUM(C14:$C$29)</f>
         <v>11878561653</v>
       </c>
-      <c r="O14" s="17">
+      <c r="O14" s="16">
         <f t="shared" si="0"/>
         <v>0.73713283203092983</v>
       </c>
@@ -8784,24 +8075,24 @@
         <f>SUM($C$4:C15)/$C$32</f>
         <v>0.33464536845858972</v>
       </c>
-      <c r="H15" s="13">
+      <c r="H15" s="12">
         <f t="shared" si="1"/>
         <v>0.46153846153846145</v>
       </c>
-      <c r="I15" s="13">
+      <c r="I15" s="12">
         <f t="shared" si="1"/>
         <v>0.46153846153846145</v>
       </c>
-      <c r="J15" s="13">
+      <c r="J15" s="12">
         <f t="shared" si="3"/>
         <v>1.0078834749201055E-2</v>
       </c>
-      <c r="K15" s="14"/>
-      <c r="L15" s="18">
+      <c r="K15" s="13"/>
+      <c r="L15" s="17">
         <f>SUM(D15:$D$29)</f>
         <v>81318</v>
       </c>
-      <c r="M15" s="16">
+      <c r="M15" s="15">
         <f t="shared" si="2"/>
         <v>0.32453854289306167</v>
       </c>
@@ -8809,7 +8100,7 @@
         <f>SUM(C15:$C$29)</f>
         <v>11300100156</v>
       </c>
-      <c r="O15" s="17">
+      <c r="O15" s="16">
         <f t="shared" si="0"/>
         <v>0.70123598071503246</v>
       </c>
@@ -8839,24 +8130,24 @@
         <f>SUM($C$4:C16)/$C$32</f>
         <v>0.36865560992837443</v>
       </c>
-      <c r="H16" s="13">
+      <c r="H16" s="12">
         <f t="shared" si="1"/>
         <v>0.49999999999999989</v>
       </c>
-      <c r="I16" s="13">
+      <c r="I16" s="12">
         <f t="shared" si="1"/>
         <v>0.49999999999999989</v>
       </c>
-      <c r="J16" s="13">
+      <c r="J16" s="12">
         <f t="shared" si="3"/>
         <v>9.9208481156934439E-3</v>
       </c>
-      <c r="K16" s="14"/>
-      <c r="L16" s="18">
+      <c r="K16" s="13"/>
+      <c r="L16" s="17">
         <f>SUM(D16:$D$29)</f>
         <v>73344</v>
       </c>
-      <c r="M16" s="16">
+      <c r="M16" s="15">
         <f t="shared" si="2"/>
         <v>0.292714465308403</v>
       </c>
@@ -8864,7 +8155,7 @@
         <f>SUM(C16:$C$29)</f>
         <v>10721888469</v>
       </c>
-      <c r="O16" s="17">
+      <c r="O16" s="16">
         <f t="shared" si="0"/>
         <v>0.66535463154141028</v>
       </c>
@@ -8894,24 +8185,24 @@
         <f>SUM($C$4:C17)/$C$32</f>
         <v>0.40129947919880654</v>
       </c>
-      <c r="H17" s="13">
+      <c r="H17" s="12">
         <f t="shared" si="1"/>
         <v>0.53846153846153832</v>
       </c>
-      <c r="I17" s="13">
+      <c r="I17" s="12">
         <f t="shared" si="1"/>
         <v>0.53846153846153832</v>
       </c>
-      <c r="J17" s="13">
+      <c r="J17" s="12">
         <f t="shared" si="3"/>
         <v>9.7947911583536676E-3</v>
       </c>
-      <c r="K17" s="14"/>
-      <c r="L17" s="18">
+      <c r="K17" s="13"/>
+      <c r="L17" s="17">
         <f>SUM(D17:$D$29)</f>
         <v>66275</v>
       </c>
-      <c r="M17" s="16">
+      <c r="M17" s="15">
         <f t="shared" si="2"/>
         <v>0.26450222497156428</v>
       </c>
@@ -8919,7 +8210,7 @@
         <f>SUM(C17:$C$29)</f>
         <v>10173828835</v>
       </c>
-      <c r="O17" s="17">
+      <c r="O17" s="16">
         <f t="shared" si="0"/>
         <v>0.63134439007162557</v>
       </c>
@@ -8949,24 +8240,24 @@
         <f>SUM($C$4:C18)/$C$32</f>
         <v>0.43250922766973687</v>
       </c>
-      <c r="H18" s="13">
+      <c r="H18" s="12">
         <f t="shared" si="1"/>
         <v>0.57692307692307676</v>
       </c>
-      <c r="I18" s="13">
+      <c r="I18" s="12">
         <f t="shared" si="1"/>
         <v>0.57692307692307676</v>
       </c>
-      <c r="J18" s="13">
+      <c r="J18" s="12">
         <f t="shared" si="3"/>
         <v>9.5588590205331718E-3</v>
       </c>
-      <c r="K18" s="14"/>
-      <c r="L18" s="18">
+      <c r="K18" s="13"/>
+      <c r="L18" s="17">
         <f>SUM(D18:$D$29)</f>
         <v>59900</v>
       </c>
-      <c r="M18" s="16">
+      <c r="M18" s="15">
         <f t="shared" si="2"/>
         <v>0.23905972502145151</v>
       </c>
@@ -8974,7 +8265,7 @@
         <f>SUM(C18:$C$29)</f>
         <v>9647787670</v>
       </c>
-      <c r="O18" s="17">
+      <c r="O18" s="16">
         <f t="shared" si="0"/>
         <v>0.59870052080119351</v>
       </c>
@@ -9004,24 +8295,24 @@
         <f>SUM($C$4:C19)/$C$32</f>
         <v>0.46170018237387023</v>
       </c>
-      <c r="H19" s="13">
+      <c r="H19" s="12">
         <f t="shared" si="1"/>
         <v>0.6153846153846152</v>
       </c>
-      <c r="I19" s="13">
+      <c r="I19" s="12">
         <f t="shared" si="1"/>
         <v>0.6153846153846152</v>
       </c>
-      <c r="J19" s="13">
+      <c r="J19" s="12">
         <f t="shared" si="3"/>
         <v>9.0753877426651731E-3</v>
       </c>
-      <c r="K19" s="14"/>
-      <c r="L19" s="18">
+      <c r="K19" s="13"/>
+      <c r="L19" s="17">
         <f>SUM(D19:$D$29)</f>
         <v>54155</v>
       </c>
-      <c r="M19" s="16">
+      <c r="M19" s="15">
         <f t="shared" si="2"/>
         <v>0.21613154271346757</v>
       </c>
@@ -9029,7 +8320,7 @@
         <f>SUM(C19:$C$29)</f>
         <v>9144856712</v>
       </c>
-      <c r="O19" s="17">
+      <c r="O19" s="16">
         <f t="shared" si="0"/>
         <v>0.56749077233026313</v>
       </c>
@@ -9059,24 +8350,24 @@
         <f>SUM($C$4:C20)/$C$32</f>
         <v>0.48901638800589997</v>
       </c>
-      <c r="H20" s="13">
+      <c r="H20" s="12">
         <f t="shared" si="1"/>
         <v>0.65384615384615363</v>
       </c>
-      <c r="I20" s="13">
+      <c r="I20" s="12">
         <f t="shared" si="1"/>
         <v>0.65384615384615363</v>
       </c>
-      <c r="J20" s="13">
+      <c r="J20" s="12">
         <f t="shared" si="3"/>
         <v>8.5618180554424654E-3</v>
       </c>
-      <c r="K20" s="14"/>
-      <c r="L20" s="18">
+      <c r="K20" s="13"/>
+      <c r="L20" s="17">
         <f>SUM(D20:$D$29)</f>
         <v>49069</v>
       </c>
-      <c r="M20" s="16">
+      <c r="M20" s="15">
         <f t="shared" si="2"/>
         <v>0.19583341647875802</v>
       </c>
@@ -9084,7 +8375,7 @@
         <f>SUM(C20:$C$29)</f>
         <v>8674457701</v>
       </c>
-      <c r="O20" s="17">
+      <c r="O20" s="16">
         <f t="shared" si="0"/>
         <v>0.53829981762612977</v>
       </c>
@@ -9114,24 +8405,24 @@
         <f>SUM($C$4:C21)/$C$32</f>
         <v>0.58253640571268872</v>
       </c>
-      <c r="H21" s="13">
+      <c r="H21" s="12">
         <f t="shared" si="1"/>
         <v>0.69230769230769207</v>
       </c>
-      <c r="I21" s="13">
+      <c r="I21" s="12">
         <f t="shared" si="1"/>
         <v>0.69230769230769207</v>
       </c>
-      <c r="J21" s="13">
+      <c r="J21" s="12">
         <f t="shared" si="3"/>
         <v>2.946754145677943E-2</v>
       </c>
-      <c r="K21" s="14"/>
-      <c r="L21" s="18">
+      <c r="K21" s="13"/>
+      <c r="L21" s="17">
         <f>SUM(D21:$D$29)</f>
         <v>44556</v>
       </c>
-      <c r="M21" s="16">
+      <c r="M21" s="15">
         <f t="shared" si="2"/>
         <v>0.17782212200427036</v>
       </c>
@@ -9139,7 +8430,7 @@
         <f>SUM(C21:$C$29)</f>
         <v>8234269422</v>
       </c>
-      <c r="O21" s="17">
+      <c r="O21" s="16">
         <f t="shared" si="0"/>
         <v>0.51098361199410003</v>
       </c>
@@ -9169,24 +8460,24 @@
         <f>SUM($C$4:C22)/$C$32</f>
         <v>0.68065722591720934</v>
       </c>
-      <c r="H22" s="13">
+      <c r="H22" s="12">
         <f t="shared" si="1"/>
         <v>0.7307692307692305</v>
       </c>
-      <c r="I22" s="13">
+      <c r="I22" s="12">
         <f t="shared" si="1"/>
         <v>0.7307692307692305</v>
       </c>
-      <c r="J22" s="13">
+      <c r="J22" s="12">
         <f t="shared" si="3"/>
         <v>2.9870182457275123E-2</v>
       </c>
-      <c r="K22" s="14"/>
-      <c r="L22" s="18">
+      <c r="K22" s="13"/>
+      <c r="L22" s="17">
         <f>SUM(D22:$D$29)</f>
         <v>30775</v>
       </c>
-      <c r="M22" s="16">
+      <c r="M22" s="56">
         <f t="shared" si="2"/>
         <v>0.12282242132779918</v>
       </c>
@@ -9194,7 +8485,7 @@
         <f>SUM(C22:$C$29)</f>
         <v>6727236703</v>
       </c>
-      <c r="O22" s="17">
+      <c r="O22" s="57">
         <f t="shared" si="0"/>
         <v>0.41746359428731122</v>
       </c>
@@ -9224,24 +8515,24 @@
         <f>SUM($C$4:C23)/$C$32</f>
         <v>0.78088873455995289</v>
       </c>
-      <c r="H23" s="13">
+      <c r="H23" s="12">
         <f t="shared" si="1"/>
         <v>0.76923076923076894</v>
       </c>
-      <c r="I23" s="13">
+      <c r="I23" s="12">
         <f t="shared" si="1"/>
         <v>0.76923076923076894</v>
       </c>
-      <c r="J23" s="13">
+      <c r="J23" s="12">
         <f t="shared" si="3"/>
         <v>2.7505517437112357E-2</v>
       </c>
-      <c r="K23" s="14"/>
-      <c r="L23" s="18">
+      <c r="K23" s="13"/>
+      <c r="L23" s="17">
         <f>SUM(D23:$D$29)</f>
         <v>18925</v>
       </c>
-      <c r="M23" s="16">
+      <c r="M23" s="56">
         <f t="shared" si="2"/>
         <v>7.5529303773471959E-2</v>
       </c>
@@ -9249,7 +8540,7 @@
         <f>SUM(C23:$C$29)</f>
         <v>5146064136</v>
       </c>
-      <c r="O23" s="17">
+      <c r="O23" s="57">
         <f t="shared" si="0"/>
         <v>0.31934277408279071</v>
       </c>
@@ -9279,24 +8570,24 @@
         <f>SUM($C$4:C24)/$C$32</f>
         <v>0.86888446225071081</v>
       </c>
-      <c r="H24" s="13">
+      <c r="H24" s="12">
         <f t="shared" si="1"/>
         <v>0.80769230769230738</v>
       </c>
-      <c r="I24" s="13">
+      <c r="I24" s="12">
         <f t="shared" si="1"/>
         <v>0.80769230769230738</v>
       </c>
-      <c r="J24" s="13">
+      <c r="J24" s="12">
         <f t="shared" si="3"/>
         <v>1.9574863664590506E-2</v>
       </c>
-      <c r="K24" s="14"/>
-      <c r="L24" s="18">
+      <c r="K24" s="13"/>
+      <c r="L24" s="17">
         <f>SUM(D24:$D$29)</f>
         <v>9494</v>
       </c>
-      <c r="M24" s="16">
+      <c r="M24" s="15">
         <f t="shared" si="2"/>
         <v>3.7890367768842415E-2</v>
       </c>
@@ -9304,7 +8595,7 @@
         <f>SUM(C24:$C$29)</f>
         <v>3530878781</v>
       </c>
-      <c r="O24" s="17">
+      <c r="O24" s="16">
         <f t="shared" si="0"/>
         <v>0.21911126544004705</v>
       </c>
@@ -9334,24 +8625,24 @@
         <f>SUM($C$4:C25)/$C$32</f>
         <v>0.90632792856170452</v>
       </c>
-      <c r="H25" s="13">
+      <c r="H25" s="12">
         <f t="shared" si="1"/>
         <v>0.84615384615384581</v>
       </c>
-      <c r="I25" s="13">
+      <c r="I25" s="12">
         <f t="shared" si="1"/>
         <v>0.84615384615384581</v>
       </c>
-      <c r="J25" s="13">
+      <c r="J25" s="12">
         <f t="shared" si="3"/>
         <v>6.2559118036730876E-3</v>
       </c>
-      <c r="K25" s="14"/>
-      <c r="L25" s="18">
+      <c r="K25" s="13"/>
+      <c r="L25" s="17">
         <f>SUM(D25:$D$29)</f>
         <v>3548</v>
       </c>
-      <c r="M25" s="16">
+      <c r="M25" s="60">
         <f t="shared" si="2"/>
         <v>1.4159998403607847E-2</v>
       </c>
@@ -9359,7 +8650,7 @@
         <f>SUM(C25:$C$29)</f>
         <v>2112867493</v>
       </c>
-      <c r="O25" s="17">
+      <c r="O25" s="61">
         <f t="shared" si="0"/>
         <v>0.13111553774928922</v>
       </c>
@@ -9389,24 +8680,24 @@
         <f>SUM($C$4:C26)/$C$32</f>
         <v>0.92665698251440032</v>
       </c>
-      <c r="H26" s="13">
+      <c r="H26" s="12">
         <f t="shared" si="1"/>
         <v>0.88461538461538425</v>
       </c>
-      <c r="I26" s="13">
+      <c r="I26" s="12">
         <f t="shared" si="1"/>
         <v>0.88461538461538425</v>
       </c>
-      <c r="J26" s="13">
+      <c r="J26" s="12">
         <f t="shared" si="3"/>
         <v>2.6993851183808289E-3</v>
       </c>
-      <c r="K26" s="14"/>
-      <c r="L26" s="18">
+      <c r="K26" s="13"/>
+      <c r="L26" s="17">
         <f>SUM(D26:$D$29)</f>
         <v>1782</v>
       </c>
-      <c r="M26" s="16">
+      <c r="M26" s="60">
         <f t="shared" si="2"/>
         <v>7.1119270448785745E-3</v>
       </c>
@@ -9414,7 +8705,7 @@
         <f>SUM(C26:$C$29)</f>
         <v>1509482996</v>
       </c>
-      <c r="O26" s="17">
+      <c r="O26" s="61">
         <f t="shared" si="0"/>
         <v>9.3672071438295437E-2</v>
       </c>
@@ -9444,24 +8735,24 @@
         <f>SUM($C$4:C27)/$C$32</f>
         <v>0.96067168523277524</v>
       </c>
-      <c r="H27" s="13">
+      <c r="H27" s="12">
         <f t="shared" si="1"/>
         <v>0.92307692307692268</v>
       </c>
-      <c r="I27" s="13">
+      <c r="I27" s="12">
         <f t="shared" si="1"/>
         <v>0.92307692307692268</v>
       </c>
-      <c r="J27" s="13">
+      <c r="J27" s="12">
         <f t="shared" si="3"/>
         <v>3.0920057394696822E-3</v>
       </c>
-      <c r="K27" s="14"/>
-      <c r="L27" s="18">
+      <c r="K27" s="13"/>
+      <c r="L27" s="17">
         <f>SUM(D27:$D$29)</f>
         <v>1044</v>
       </c>
-      <c r="M27" s="16">
+      <c r="M27" s="15">
         <f t="shared" si="2"/>
         <v>4.1665835212419929E-3</v>
       </c>
@@ -9469,7 +8760,7 @@
         <f>SUM(C27:$C$29)</f>
         <v>1181889501</v>
       </c>
-      <c r="O27" s="17">
+      <c r="O27" s="16">
         <f t="shared" si="0"/>
         <v>7.334301748559964E-2</v>
       </c>
@@ -9499,24 +8790,24 @@
         <f>SUM($C$4:C28)/$C$32</f>
         <v>0.97412622442991403</v>
       </c>
-      <c r="H28" s="13">
+      <c r="H28" s="12">
         <f t="shared" si="1"/>
         <v>0.96153846153846112</v>
       </c>
-      <c r="I28" s="13">
+      <c r="I28" s="12">
         <f t="shared" si="1"/>
         <v>0.96153846153846112</v>
       </c>
-      <c r="J28" s="13">
+      <c r="J28" s="12">
         <f t="shared" si="3"/>
         <v>6.2546098091378162E-4</v>
       </c>
-      <c r="K28" s="14"/>
-      <c r="L28" s="18">
+      <c r="K28" s="13"/>
+      <c r="L28" s="17">
         <f>SUM(D28:$D$29)</f>
         <v>223</v>
       </c>
-      <c r="M28" s="16">
+      <c r="M28" s="15">
         <f t="shared" si="2"/>
         <v>8.8998862570590471E-4</v>
       </c>
@@ -9524,7 +8815,7 @@
         <f>SUM(C28:$C$29)</f>
         <v>633757976</v>
       </c>
-      <c r="O28" s="17">
+      <c r="O28" s="16">
         <f t="shared" si="0"/>
         <v>3.9328314767224794E-2</v>
       </c>
@@ -9534,7 +8825,7 @@
         <v>2000001</v>
       </c>
       <c r="B29" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C29" s="6">
         <v>416944172</v>
@@ -9554,24 +8845,24 @@
         <f>SUM($C$4:C29)/$C$32</f>
         <v>1</v>
       </c>
-      <c r="H29" s="13">
+      <c r="H29" s="12">
         <f t="shared" si="1"/>
         <v>0.99999999999999956</v>
       </c>
-      <c r="I29" s="13">
+      <c r="I29" s="12">
         <f t="shared" si="1"/>
         <v>0.99999999999999956</v>
       </c>
-      <c r="J29" s="13">
+      <c r="J29" s="12">
         <f t="shared" si="3"/>
         <v>2.4030032065581306E-4</v>
       </c>
-      <c r="K29" s="14"/>
-      <c r="L29" s="18">
+      <c r="K29" s="13"/>
+      <c r="L29" s="17">
         <f>SUM(D29:$D$29)</f>
         <v>61</v>
       </c>
-      <c r="M29" s="16">
+      <c r="M29" s="15">
         <f t="shared" si="2"/>
         <v>2.4344980344421607E-4</v>
       </c>
@@ -9579,14 +8870,14 @@
         <f>SUM(C29:$C$29)</f>
         <v>416944172</v>
       </c>
-      <c r="O29" s="17">
+      <c r="O29" s="16">
         <f t="shared" si="0"/>
         <v>2.5873775570085945E-2</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B30" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C30" s="6">
         <v>16114546981</v>
@@ -9600,23 +8891,28 @@
       </c>
       <c r="F30" s="8"/>
       <c r="G30" s="8"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="13"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
       <c r="J30" s="8"/>
       <c r="K30" s="8"/>
+      <c r="M30" s="64" t="s">
+        <v>42</v>
+      </c>
+      <c r="N30" s="64"/>
+      <c r="O30" s="64"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="N31" t="s">
-        <v>25</v>
-      </c>
-      <c r="O31" s="10" t="e">
-        <f>#REF!+((#REF!-#REF!)*(0.001-#REF!)/(#REF!-#REF!))</f>
-        <v>#REF!</v>
+      <c r="N31" s="58" t="s">
+        <v>40</v>
+      </c>
+      <c r="O31" s="59">
+        <f>O23+((O22-O23)*(0.1-M23))/(M22-M23)</f>
+        <v>0.37011305333038713</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B32" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C32" s="9">
         <f>SUM(C4:C29)</f>
@@ -9627,23 +8923,23 @@
         <v>250565</v>
       </c>
       <c r="I32" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="J32" s="8">
         <f>SUM(J4:J29)</f>
         <v>0.23410951554661666</v>
       </c>
-      <c r="N32" t="s">
-        <v>17</v>
-      </c>
-      <c r="O32" s="10">
+      <c r="N32" s="62" t="s">
+        <v>41</v>
+      </c>
+      <c r="O32" s="63">
         <f>O26+((O25-O26)*(0.01-M26)/(M25-M26))</f>
         <v>0.10901519963532298</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="I33" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J33" s="8">
         <f>1-(2*J32)</f>
@@ -9651,17 +8947,17 @@
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A39" s="38" t="s">
-        <v>52</v>
-      </c>
-      <c r="B39" s="38"/>
+      <c r="A39" s="44" t="s">
+        <v>21</v>
+      </c>
+      <c r="B39" s="44"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="B40" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.35">
@@ -9696,7 +8992,7 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44">
-        <f t="shared" ref="A41:A65" si="6">LOG(E7)</f>
+        <f t="shared" ref="A44:A65" si="6">LOG(E7)</f>
         <v>4.5132945165813325</v>
       </c>
       <c r="B44">
@@ -9743,9 +9039,9 @@
         <f xml:space="preserve"> LOG(1-F11)</f>
         <v>-0.36019297580706788</v>
       </c>
-      <c r="H48" s="25"/>
-      <c r="I48" s="25"/>
-      <c r="J48" s="25"/>
+      <c r="H48" s="21"/>
+      <c r="I48" s="21"/>
+      <c r="J48" s="21"/>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A49">
@@ -9757,13 +9053,13 @@
         <v>-0.40271968167192423</v>
       </c>
       <c r="H49" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="I49" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="J49" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.35">
@@ -9775,10 +9071,10 @@
         <f t="shared" si="5"/>
         <v>-0.44523318400886275</v>
       </c>
-      <c r="F50" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="G50" s="25"/>
+      <c r="F50" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="G50" s="21"/>
       <c r="H50">
         <f>A29*((D29/D30)^(1/G52))</f>
         <v>5556.4227026976187</v>
@@ -9802,10 +9098,10 @@
         <v>-0.48873371805696725</v>
       </c>
       <c r="F51" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="G51" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="J51">
         <f>J50/C30</f>
@@ -9961,17 +9257,17 @@
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B69" s="38" t="s">
-        <v>52</v>
-      </c>
-      <c r="C69" s="38"/>
+      <c r="B69" s="44" t="s">
+        <v>21</v>
+      </c>
+      <c r="C69" s="44"/>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B70" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="C70" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">
@@ -10225,527 +9521,16 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="A39:B39"/>
     <mergeCell ref="F1:I1"/>
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="L1:Q1"/>
     <mergeCell ref="B69:C69"/>
     <mergeCell ref="J2:K2"/>
+    <mergeCell ref="M30:O30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C100B010-F934-41A3-88FF-308B180726C1}">
-  <dimension ref="A1:I49"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" s="24"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4">
-        <v>0.92313721029489104</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5">
-        <v>0.85218230903103387</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6">
-        <v>0.84575545290194842</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7">
-        <v>0.37116301518184985</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="22">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A11" s="23"/>
-      <c r="B11" s="23" t="s">
-        <v>39</v>
-      </c>
-      <c r="C11" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="E11" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="F11" s="23" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12">
-        <v>18.266835778883362</v>
-      </c>
-      <c r="D12">
-        <v>18.266835778883362</v>
-      </c>
-      <c r="E12">
-        <v>132.59707264557923</v>
-      </c>
-      <c r="F12">
-        <v>5.0116133691544345E-11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13">
-        <v>23</v>
-      </c>
-      <c r="C13">
-        <v>3.1685256282942884</v>
-      </c>
-      <c r="D13">
-        <v>0.13776198383888211</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="B14" s="22">
-        <v>24</v>
-      </c>
-      <c r="C14" s="22">
-        <v>21.435361407177652</v>
-      </c>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
-    </row>
-    <row r="15" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A16" s="23"/>
-      <c r="B16" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="D16" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="E16" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="F16" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="G16" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="H16" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="I16" s="23" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17">
-        <v>7.7313593280918838</v>
-      </c>
-      <c r="C17">
-        <v>0.75719736484209588</v>
-      </c>
-      <c r="D17">
-        <v>10.210494234490849</v>
-      </c>
-      <c r="E17">
-        <v>5.1526322468997036E-10</v>
-      </c>
-      <c r="F17">
-        <v>6.1649772367220326</v>
-      </c>
-      <c r="G17">
-        <v>9.2977414194617349</v>
-      </c>
-      <c r="H17">
-        <v>6.1649772367220326</v>
-      </c>
-      <c r="I17">
-        <v>9.2977414194617349</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="B18" s="22">
-        <v>-1.755910322988903</v>
-      </c>
-      <c r="C18" s="22">
-        <v>0.15248789311920663</v>
-      </c>
-      <c r="D18" s="22">
-        <v>-11.515080227492088</v>
-      </c>
-      <c r="E18" s="22">
-        <v>5.0116133691544164E-11</v>
-      </c>
-      <c r="F18" s="22">
-        <v>-2.0713555635867165</v>
-      </c>
-      <c r="G18" s="22">
-        <v>-1.4404650823910896</v>
-      </c>
-      <c r="H18" s="22">
-        <v>-2.0713555635867165</v>
-      </c>
-      <c r="I18" s="22">
-        <v>-1.4404650823910896</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A24" s="23" t="s">
-        <v>56</v>
-      </c>
-      <c r="B24" s="23" t="s">
-        <v>57</v>
-      </c>
-      <c r="C24" s="23" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A25">
-        <v>1</v>
-      </c>
-      <c r="B25">
-        <v>1.1075466481673946</v>
-      </c>
-      <c r="C25">
-        <v>-1.2510329258531978</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A26">
-        <v>2</v>
-      </c>
-      <c r="B26">
-        <v>8.3257032634299399E-2</v>
-      </c>
-      <c r="C26">
-        <v>-0.25183327226711361</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A27">
-        <v>3</v>
-      </c>
-      <c r="B27">
-        <v>-6.6927207554209112E-2</v>
-      </c>
-      <c r="C27">
-        <v>-0.1308720351459072</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A28">
-        <v>4</v>
-      </c>
-      <c r="B28">
-        <v>-0.19358110426248842</v>
-      </c>
-      <c r="C28">
-        <v>-3.0770740413433612E-2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A29">
-        <v>5</v>
-      </c>
-      <c r="B29">
-        <v>-0.30272581290247125</v>
-      </c>
-      <c r="C29">
-        <v>4.8802805694943885E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A30">
-        <v>6</v>
-      </c>
-      <c r="B30">
-        <v>-0.39730991779319957</v>
-      </c>
-      <c r="C30">
-        <v>0.11059555588603043</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A31">
-        <v>7</v>
-      </c>
-      <c r="B31">
-        <v>-0.48233757779971853</v>
-      </c>
-      <c r="C31">
-        <v>0.15986099096964451</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A32">
-        <v>8</v>
-      </c>
-      <c r="B32">
-        <v>-0.55770871965888524</v>
-      </c>
-      <c r="C32">
-        <v>0.19751574385181736</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A33">
-        <v>9</v>
-      </c>
-      <c r="B33">
-        <v>-0.62713862152776834</v>
-      </c>
-      <c r="C33">
-        <v>0.2244189398558441</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A34">
-        <v>10</v>
-      </c>
-      <c r="B34">
-        <v>-0.69038359009186223</v>
-      </c>
-      <c r="C34">
-        <v>0.24515040608299948</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A35">
-        <v>11</v>
-      </c>
-      <c r="B35">
-        <v>-0.74871421374231595</v>
-      </c>
-      <c r="C35">
-        <v>0.2599804956853487</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A36">
-        <v>12</v>
-      </c>
-      <c r="B36">
-        <v>-0.8030858784584165</v>
-      </c>
-      <c r="C36">
-        <v>0.26953006330556528</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A37">
-        <v>13</v>
-      </c>
-      <c r="B37">
-        <v>-0.85411122857350108</v>
-      </c>
-      <c r="C37">
-        <v>0.27654055821052248</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A38">
-        <v>14</v>
-      </c>
-      <c r="B38">
-        <v>-0.90164320674166909</v>
-      </c>
-      <c r="C38">
-        <v>0.28014962236287089</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A39">
-        <v>15</v>
-      </c>
-      <c r="B39">
-        <v>-0.94673286741518936</v>
-      </c>
-      <c r="C39">
-        <v>0.28145102081733919</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A40">
-        <v>16</v>
-      </c>
-      <c r="B40">
-        <v>-0.98864944530254562</v>
-      </c>
-      <c r="C40">
-        <v>0.28053624591606019</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A41">
-        <v>17</v>
-      </c>
-      <c r="B41">
-        <v>-1.0291812929944584</v>
-      </c>
-      <c r="C41">
-        <v>0.27916708150013259</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A42">
-        <v>18</v>
-      </c>
-      <c r="B42">
-        <v>-1.1163952653853872</v>
-      </c>
-      <c r="C42">
-        <v>0.20567292022063155</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A43">
-        <v>19</v>
-      </c>
-      <c r="B43">
-        <v>-1.2681392301824932</v>
-      </c>
-      <c r="C43">
-        <v>0.14625471158649428</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A44">
-        <v>20</v>
-      </c>
-      <c r="B44">
-        <v>-1.4584864110593436</v>
-      </c>
-      <c r="C44">
-        <v>3.7015231673575899E-2</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A45">
-        <v>21</v>
-      </c>
-      <c r="B45">
-        <v>-1.710969037080547</v>
-      </c>
-      <c r="C45">
-        <v>-0.13796775852787468</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A46">
-        <v>22</v>
-      </c>
-      <c r="B46">
-        <v>-1.9851520899968698</v>
-      </c>
-      <c r="C46">
-        <v>-0.16286061707038124</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A47">
-        <v>23</v>
-      </c>
-      <c r="B47">
-        <v>-2.1847560025556909</v>
-      </c>
-      <c r="C47">
-        <v>-0.1954639055461751</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A48">
-        <v>24</v>
-      </c>
-      <c r="B48">
-        <v>-2.4960134352841568</v>
-      </c>
-      <c r="C48">
-        <v>-0.55460210843580215</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="22">
-        <v>25</v>
-      </c>
-      <c r="B49" s="22">
-        <v>-3.0263515413973447</v>
-      </c>
-      <c r="C49" s="22">
-        <v>-0.58723903035991531</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
 </file>